--- a/Hedge Funds (1).xlsx
+++ b/Hedge Funds (1).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A5C0EAC-08A8-4856-BF62-E99B86F764C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6CB3134-4AE9-4413-B989-4F8624FE5C60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21060" xr2:uid="{18689D26-F1F3-46B4-82BE-041D095397EB}"/>
+    <workbookView xWindow="225" yWindow="3855" windowWidth="38175" windowHeight="15240" xr2:uid="{18689D26-F1F3-46B4-82BE-041D095397EB}"/>
   </bookViews>
   <sheets>
     <sheet name="Hedge" sheetId="1" r:id="rId1"/>
@@ -166,7 +166,7 @@
     210.9B with puts/calls</t>
       </text>
     </comment>
-    <comment ref="X4" authorId="6" shapeId="0" xr:uid="{C458FA31-CB9B-459E-B4D3-6F93CD9B9108}">
+    <comment ref="Y4" authorId="6" shapeId="0" xr:uid="{C458FA31-CB9B-459E-B4D3-6F93CD9B9108}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -393,7 +393,7 @@
 All Weather 12%</t>
       </text>
     </comment>
-    <comment ref="AD22" authorId="34" shapeId="0" xr:uid="{571E6B33-9F0B-402B-B6AF-3026724B96B6}">
+    <comment ref="AE22" authorId="34" shapeId="0" xr:uid="{571E6B33-9F0B-402B-B6AF-3026724B96B6}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -402,7 +402,7 @@
 Pure alpha 1991</t>
       </text>
     </comment>
-    <comment ref="AM22" authorId="35" shapeId="0" xr:uid="{65A0F6CF-356C-4A90-96D2-FFE35AFE2E62}">
+    <comment ref="AN22" authorId="35" shapeId="0" xr:uid="{65A0F6CF-356C-4A90-96D2-FFE35AFE2E62}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -410,7 +410,7 @@
     All Weather +16%</t>
       </text>
     </comment>
-    <comment ref="AN22" authorId="36" shapeId="0" xr:uid="{267E6B37-EE49-4656-A61F-E5E2C45BA32F}">
+    <comment ref="AO22" authorId="36" shapeId="0" xr:uid="{267E6B37-EE49-4656-A61F-E5E2C45BA32F}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -474,7 +474,7 @@
     Also notes 35.5B</t>
       </text>
     </comment>
-    <comment ref="AJ28" authorId="44" shapeId="0" xr:uid="{5F7F3924-A5F8-4D80-90C0-CA8CC6527A95}">
+    <comment ref="AK28" authorId="44" shapeId="0" xr:uid="{5F7F3924-A5F8-4D80-90C0-CA8CC6527A95}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -627,7 +627,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2260" uniqueCount="1568">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2261" uniqueCount="1569">
   <si>
     <t>Name</t>
   </si>
@@ -5331,6 +5331,9 @@
   </si>
   <si>
     <t>Q225</t>
+  </si>
+  <si>
+    <t>Q325</t>
   </si>
 </sst>
 </file>
@@ -5899,7 +5902,7 @@
   <threadedComment ref="S4" dT="2025-01-11T20:11:02.62" personId="{4F866D09-A2D3-41DA-A24C-20DE51662D93}" id="{B533632F-6233-41C2-A96C-9A84235E21C6}">
     <text>210.9B with puts/calls</text>
   </threadedComment>
-  <threadedComment ref="X4" dT="2025-04-05T10:22:31.39" personId="{C4A9F9C5-0550-4D3E-A9C0-F2F2E5238B0D}" id="{C458FA31-CB9B-459E-B4D3-6F93CD9B9108}">
+  <threadedComment ref="Y4" dT="2025-04-05T10:22:31.39" personId="{C4A9F9C5-0550-4D3E-A9C0-F2F2E5238B0D}" id="{C458FA31-CB9B-459E-B4D3-6F93CD9B9108}">
     <text xml:space="preserve">Pod shop = multi strategy </text>
   </threadedComment>
   <threadedComment ref="P5" dT="2024-03-24T23:23:21.67" personId="{4F866D09-A2D3-41DA-A24C-20DE51662D93}" id="{4762A1A1-5314-4304-962C-F1489B64BA4B}">
@@ -5986,14 +5989,14 @@
 Pure Alpha 18%
 All Weather 12%</text>
   </threadedComment>
-  <threadedComment ref="AD22" dT="2024-11-11T21:29:45.05" personId="{4F866D09-A2D3-41DA-A24C-20DE51662D93}" id="{571E6B33-9F0B-402B-B6AF-3026724B96B6}">
+  <threadedComment ref="AE22" dT="2024-11-11T21:29:45.05" personId="{4F866D09-A2D3-41DA-A24C-20DE51662D93}" id="{571E6B33-9F0B-402B-B6AF-3026724B96B6}">
     <text>All weather opened 1996
 Pure alpha 1991</text>
   </threadedComment>
-  <threadedComment ref="AM22" dT="2024-11-11T21:44:28.32" personId="{4F866D09-A2D3-41DA-A24C-20DE51662D93}" id="{65A0F6CF-356C-4A90-96D2-FFE35AFE2E62}">
+  <threadedComment ref="AN22" dT="2024-11-11T21:44:28.32" personId="{4F866D09-A2D3-41DA-A24C-20DE51662D93}" id="{65A0F6CF-356C-4A90-96D2-FFE35AFE2E62}">
     <text>All Weather +16%</text>
   </threadedComment>
-  <threadedComment ref="AN22" dT="2024-11-11T21:45:06.55" personId="{4F866D09-A2D3-41DA-A24C-20DE51662D93}" id="{267E6B37-EE49-4656-A61F-E5E2C45BA32F}">
+  <threadedComment ref="AO22" dT="2024-11-11T21:45:06.55" personId="{4F866D09-A2D3-41DA-A24C-20DE51662D93}" id="{267E6B37-EE49-4656-A61F-E5E2C45BA32F}">
     <text>All Weather -5.1%</text>
   </threadedComment>
   <threadedComment ref="C23" dT="2025-04-08T16:50:08.35" personId="{C4A9F9C5-0550-4D3E-A9C0-F2F2E5238B0D}" id="{3C8A7604-D0B1-4BD2-8EB5-1FC90AAA41A6}">
@@ -6017,7 +6020,7 @@
   <threadedComment ref="D28" dT="2023-01-28T20:34:58.21" personId="{4F866D09-A2D3-41DA-A24C-20DE51662D93}" id="{9F5197FC-413A-4526-8395-DB7D8217FC78}">
     <text>Also notes 35.5B</text>
   </threadedComment>
-  <threadedComment ref="AJ28" dT="2023-01-28T20:41:18.37" personId="{4F866D09-A2D3-41DA-A24C-20DE51662D93}" id="{5F7F3924-A5F8-4D80-90C0-CA8CC6527A95}">
+  <threadedComment ref="AK28" dT="2023-01-28T20:41:18.37" personId="{4F866D09-A2D3-41DA-A24C-20DE51662D93}" id="{5F7F3924-A5F8-4D80-90C0-CA8CC6527A95}">
     <text>https://www.bloomberg.com/news/articles/2022-08-26/lone-pine-assets-shrivel-as-hedge-fund-reels-from-record-losses?leadSource=uverify%20wall</text>
     <extLst>
       <x:ext xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
@@ -6095,7 +6098,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E8001A6-1B33-4EEE-B2A7-E66E0A0975B5}">
-  <dimension ref="A1:BQ242"/>
+  <dimension ref="A1:BR242"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.140625" bestFit="1" customWidth="1"/>
@@ -6106,20 +6109,20 @@
     <col min="9" max="14" width="9.28515625" style="3"/>
     <col min="15" max="15" width="8.7109375" style="3"/>
     <col min="16" max="16" width="9.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="17" max="22" width="9.28515625" style="3" customWidth="1"/>
-    <col min="23" max="23" width="12" style="6" customWidth="1"/>
-    <col min="24" max="24" width="10.5703125" style="6" customWidth="1"/>
-    <col min="25" max="25" width="12" style="8" customWidth="1"/>
-    <col min="27" max="28" width="10.7109375" customWidth="1"/>
+    <col min="17" max="23" width="9.28515625" style="3" customWidth="1"/>
+    <col min="24" max="24" width="12" style="6" customWidth="1"/>
+    <col min="25" max="25" width="10.5703125" style="6" customWidth="1"/>
+    <col min="26" max="26" width="12" style="8" customWidth="1"/>
+    <col min="28" max="29" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:69" x14ac:dyDescent="0.2">
-      <c r="AB1">
-        <f>SUM(AB3:AB276)</f>
+    <row r="1" spans="1:70" x14ac:dyDescent="0.2">
+      <c r="AC1">
+        <f>SUM(AC3:AC276)</f>
         <v>30724</v>
       </c>
     </row>
-    <row r="2" spans="1:69" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:70" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -6183,159 +6186,162 @@
       <c r="V2" s="3" t="s">
         <v>1567</v>
       </c>
-      <c r="W2" s="5" t="s">
+      <c r="W2" s="3" t="s">
+        <v>1568</v>
+      </c>
+      <c r="X2" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="X2" s="5" t="s">
+      <c r="Y2" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="Y2" s="7" t="s">
+      <c r="Z2" s="7" t="s">
         <v>214</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AA2" t="s">
         <v>225</v>
       </c>
-      <c r="AA2" t="s">
+      <c r="AB2" t="s">
         <v>226</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="AC2" t="s">
         <v>723</v>
       </c>
-      <c r="AC2" t="s">
+      <c r="AD2" t="s">
         <v>229</v>
       </c>
-      <c r="AD2" t="s">
+      <c r="AE2" t="s">
         <v>228</v>
       </c>
-      <c r="AE2" t="s">
+      <c r="AF2" t="s">
         <v>714</v>
       </c>
-      <c r="AF2" t="s">
+      <c r="AG2" t="s">
         <v>715</v>
       </c>
-      <c r="AG2" t="s">
+      <c r="AH2" t="s">
         <v>713</v>
       </c>
-      <c r="AH2">
+      <c r="AI2">
         <v>2024</v>
       </c>
-      <c r="AI2">
+      <c r="AJ2">
         <v>2023</v>
       </c>
-      <c r="AJ2">
+      <c r="AK2">
         <v>2022</v>
       </c>
-      <c r="AK2">
+      <c r="AL2">
         <v>2021</v>
       </c>
-      <c r="AL2">
+      <c r="AM2">
         <v>2020</v>
       </c>
-      <c r="AM2">
+      <c r="AN2">
         <v>2019</v>
       </c>
-      <c r="AN2">
+      <c r="AO2">
         <v>2018</v>
       </c>
-      <c r="AO2">
+      <c r="AP2">
         <v>2017</v>
       </c>
-      <c r="AP2">
+      <c r="AQ2">
         <v>2016</v>
       </c>
-      <c r="AQ2">
+      <c r="AR2">
         <v>2015</v>
       </c>
-      <c r="AR2">
+      <c r="AS2">
         <v>2014</v>
       </c>
-      <c r="AS2">
+      <c r="AT2">
         <v>2013</v>
       </c>
-      <c r="AT2">
+      <c r="AU2">
         <v>2012</v>
       </c>
-      <c r="AU2">
+      <c r="AV2">
         <v>2011</v>
       </c>
-      <c r="AV2">
-        <f>+AU2-1</f>
+      <c r="AW2">
+        <f>+AV2-1</f>
         <v>2010</v>
       </c>
-      <c r="AW2">
-        <f t="shared" ref="AW2:BK2" si="0">+AV2-1</f>
+      <c r="AX2">
+        <f t="shared" ref="AX2:BL2" si="0">+AW2-1</f>
         <v>2009</v>
       </c>
-      <c r="AX2">
+      <c r="AY2">
         <f t="shared" si="0"/>
         <v>2008</v>
       </c>
-      <c r="AY2">
+      <c r="AZ2">
         <f t="shared" si="0"/>
         <v>2007</v>
       </c>
-      <c r="AZ2">
+      <c r="BA2">
         <f t="shared" si="0"/>
         <v>2006</v>
       </c>
-      <c r="BA2">
+      <c r="BB2">
         <f t="shared" si="0"/>
         <v>2005</v>
       </c>
-      <c r="BB2">
+      <c r="BC2">
         <f t="shared" si="0"/>
         <v>2004</v>
       </c>
-      <c r="BC2">
+      <c r="BD2">
         <f t="shared" si="0"/>
         <v>2003</v>
       </c>
-      <c r="BD2">
+      <c r="BE2">
         <f t="shared" si="0"/>
         <v>2002</v>
       </c>
-      <c r="BE2">
+      <c r="BF2">
         <f t="shared" si="0"/>
         <v>2001</v>
       </c>
-      <c r="BF2">
+      <c r="BG2">
         <f t="shared" si="0"/>
         <v>2000</v>
       </c>
-      <c r="BG2">
+      <c r="BH2">
         <f t="shared" si="0"/>
         <v>1999</v>
       </c>
-      <c r="BH2">
+      <c r="BI2">
         <f t="shared" si="0"/>
         <v>1998</v>
       </c>
-      <c r="BI2">
+      <c r="BJ2">
         <f t="shared" si="0"/>
         <v>1997</v>
       </c>
-      <c r="BJ2">
+      <c r="BK2">
         <f t="shared" si="0"/>
         <v>1996</v>
       </c>
-      <c r="BK2">
+      <c r="BL2">
         <f t="shared" si="0"/>
         <v>1995</v>
       </c>
-      <c r="BL2">
+      <c r="BM2">
         <v>1994</v>
       </c>
-      <c r="BM2">
+      <c r="BN2">
         <v>1993</v>
       </c>
-      <c r="BN2">
+      <c r="BO2">
         <v>1992</v>
       </c>
-      <c r="BO2">
+      <c r="BP2">
         <v>1991</v>
       </c>
     </row>
-    <row r="3" spans="1:69" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:70" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1</v>
       </c>
@@ -6384,20 +6390,23 @@
       <c r="V3" s="4">
         <v>257521.77692500001</v>
       </c>
-      <c r="W3" s="6" t="s">
+      <c r="W3" s="4">
+        <v>267334.50195499999</v>
+      </c>
+      <c r="X3" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="X3" s="6" t="s">
+      <c r="Y3" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="Y3" s="8" t="s">
+      <c r="Z3" s="8" t="s">
         <v>217</v>
       </c>
-      <c r="Z3">
+      <c r="AA3">
         <v>1965</v>
       </c>
     </row>
-    <row r="4" spans="1:69" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:70" x14ac:dyDescent="0.2">
       <c r="A4">
         <f>+A3+1</f>
         <v>2</v>
@@ -6453,87 +6462,90 @@
       <c r="V4" s="4">
         <v>207076.08522000001</v>
       </c>
-      <c r="W4" s="6" t="s">
+      <c r="W4" s="4">
+        <v>234292.490467</v>
+      </c>
+      <c r="X4" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="X4" s="6" t="s">
+      <c r="Y4" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="Y4" s="8" t="s">
+      <c r="Z4" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="Z4">
+      <c r="AA4">
         <v>1989</v>
       </c>
-      <c r="AB4">
+      <c r="AC4">
         <v>5500</v>
       </c>
-      <c r="AE4" t="s">
+      <c r="AF4" t="s">
         <v>722</v>
       </c>
-      <c r="AH4" s="9">
+      <c r="AI4" s="9">
         <v>0.15</v>
       </c>
-      <c r="AI4" s="9">
+      <c r="AJ4" s="9">
         <v>0.1</v>
       </c>
-      <c r="AJ4" s="9">
+      <c r="AK4" s="9">
         <v>0.12</v>
       </c>
-      <c r="AK4" s="9">
+      <c r="AL4" s="9">
         <v>0.1361</v>
       </c>
-      <c r="AL4" s="9">
+      <c r="AM4" s="9">
         <v>0.25800000000000001</v>
       </c>
-      <c r="AM4" s="9">
+      <c r="AN4" s="9">
         <v>9.8000000000000004E-2</v>
       </c>
-      <c r="AN4" s="9">
+      <c r="AO4" s="9">
         <v>4.9000000000000002E-2</v>
       </c>
-      <c r="AO4" s="9">
+      <c r="AP4" s="9">
         <v>7.1199999999999999E-2</v>
       </c>
-      <c r="AP4" s="9">
+      <c r="AQ4" s="9">
         <v>3.3799999999999997E-2</v>
       </c>
-      <c r="AQ4" s="9">
+      <c r="AR4" s="9">
         <v>0.12540000000000001</v>
       </c>
-      <c r="AR4" s="9">
+      <c r="AS4" s="9">
         <v>0.12089999999999999</v>
       </c>
-      <c r="AS4" s="9">
+      <c r="AT4" s="9">
         <v>0.13270000000000001</v>
       </c>
-      <c r="AT4" s="9">
+      <c r="AU4" s="9">
         <v>6.3200000000000006E-2</v>
       </c>
-      <c r="AU4" s="9">
+      <c r="AV4" s="9">
         <v>8.3900000000000002E-2</v>
       </c>
-      <c r="AV4" s="9">
+      <c r="AW4" s="9">
         <v>0.13400000000000001</v>
       </c>
-      <c r="AW4" s="9">
+      <c r="AX4" s="9">
         <v>0.17199999999999999</v>
       </c>
-      <c r="AX4" s="9">
+      <c r="AY4" s="9">
         <v>-0.03</v>
       </c>
-      <c r="AY4" s="9"/>
-      <c r="AZ4" s="9">
+      <c r="AZ4" s="9"/>
+      <c r="BA4" s="9">
         <v>0.17</v>
       </c>
-      <c r="BA4" s="9">
+      <c r="BB4" s="9">
         <v>0.08</v>
       </c>
-      <c r="BB4" s="9">
+      <c r="BC4" s="9">
         <v>0.35</v>
       </c>
     </row>
-    <row r="5" spans="1:69" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:70" x14ac:dyDescent="0.2">
       <c r="A5">
         <f t="shared" ref="A5:A84" si="1">+A4+1</f>
         <v>3</v>
@@ -6589,101 +6601,104 @@
       <c r="V5" s="4">
         <v>575955.91866600001</v>
       </c>
-      <c r="W5" s="6" t="s">
+      <c r="W5" s="4">
+        <v>657149.09227400005</v>
+      </c>
+      <c r="X5" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="X5" s="6" t="s">
+      <c r="Y5" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="Y5" s="8" t="s">
+      <c r="Z5" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="Z5">
+      <c r="AA5">
         <v>1990</v>
       </c>
-      <c r="AA5" t="s">
+      <c r="AB5" t="s">
         <v>235</v>
       </c>
-      <c r="AB5">
+      <c r="AC5">
         <v>2932</v>
       </c>
-      <c r="AH5" s="9">
+      <c r="AI5" s="9">
         <v>0.15</v>
       </c>
-      <c r="AI5" s="9">
+      <c r="AJ5" s="9">
         <v>0.153</v>
       </c>
-      <c r="AJ5" s="9">
+      <c r="AK5" s="9">
         <v>0.38</v>
       </c>
-      <c r="AK5" s="9">
+      <c r="AL5" s="9">
         <v>0.26</v>
       </c>
-      <c r="AL5" s="9">
+      <c r="AM5" s="9">
         <v>0.24399999999999999</v>
       </c>
-      <c r="AM5" s="9">
+      <c r="AN5" s="9">
         <v>0.19400000000000001</v>
       </c>
-      <c r="AN5" s="9">
+      <c r="AO5" s="9">
         <v>9.0999999999999998E-2</v>
       </c>
-      <c r="AO5" s="9">
+      <c r="AP5" s="9">
         <v>0.13100000000000001</v>
       </c>
-      <c r="AP5" s="9">
+      <c r="AQ5" s="9">
         <v>5.0999999999999997E-2</v>
       </c>
-      <c r="AQ5" s="9">
+      <c r="AR5" s="9">
         <v>0.14299999999999999</v>
       </c>
-      <c r="AR5" s="9">
+      <c r="AS5" s="9">
         <v>0.17899999999999999</v>
       </c>
-      <c r="AS5" s="9">
+      <c r="AT5" s="9">
         <v>0.19400000000000001</v>
       </c>
-      <c r="AT5" s="9">
+      <c r="AU5" s="9">
         <v>0.25900000000000001</v>
       </c>
-      <c r="AU5" s="9">
+      <c r="AV5" s="9">
         <v>0.2</v>
       </c>
-      <c r="AV5" s="9">
+      <c r="AW5" s="9">
         <v>0.1</v>
       </c>
-      <c r="AW5" s="9">
+      <c r="AX5" s="9">
         <v>0.62</v>
       </c>
-      <c r="AX5" s="9">
+      <c r="AY5" s="9">
         <v>-0.55000000000000004</v>
-      </c>
-      <c r="AY5" s="9">
-        <v>0.3</v>
       </c>
       <c r="AZ5" s="9">
         <v>0.3</v>
       </c>
       <c r="BA5" s="9">
+        <v>0.3</v>
+      </c>
+      <c r="BB5" s="9">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="BG5" s="9">
+      <c r="BH5" s="9">
         <v>0.45</v>
       </c>
-      <c r="BL5" s="9">
+      <c r="BM5" s="9">
         <v>-4.2999999999999997E-2</v>
       </c>
-      <c r="BN5" s="9">
+      <c r="BO5" s="9">
         <v>0.4</v>
       </c>
-      <c r="BO5" s="9">
+      <c r="BP5" s="9">
         <v>0.43</v>
       </c>
-      <c r="BQ5" t="s">
+      <c r="BR5" t="s">
         <v>1498</v>
       </c>
     </row>
-    <row r="6" spans="1:69" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:70" x14ac:dyDescent="0.2">
       <c r="A6">
         <f t="shared" si="1"/>
         <v>4</v>
@@ -6730,23 +6745,24 @@
       <c r="V6" s="4">
         <v>505635.20840800001</v>
       </c>
-      <c r="W6" s="6" t="s">
+      <c r="W6" s="4"/>
+      <c r="X6" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="X6" s="6" t="s">
+      <c r="Y6" s="6" t="s">
         <v>1477</v>
       </c>
-      <c r="Y6" s="8" t="s">
+      <c r="Z6" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="Z6">
+      <c r="AA6">
         <v>2000</v>
       </c>
-      <c r="AB6">
+      <c r="AC6">
         <v>2600</v>
       </c>
     </row>
-    <row r="7" spans="1:69" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:70" x14ac:dyDescent="0.2">
       <c r="A7">
         <f t="shared" si="1"/>
         <v>5</v>
@@ -6781,38 +6797,39 @@
       <c r="V7" s="4">
         <v>88778.648031000004</v>
       </c>
-      <c r="W7" s="6" t="s">
+      <c r="W7" s="4"/>
+      <c r="X7" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="X7" s="6" t="s">
+      <c r="Y7" s="6" t="s">
         <v>1476</v>
       </c>
-      <c r="Y7" s="8" t="s">
+      <c r="Z7" s="8" t="s">
         <v>673</v>
       </c>
-      <c r="Z7">
+      <c r="AA7">
         <v>1997</v>
       </c>
-      <c r="AB7">
+      <c r="AC7">
         <v>650</v>
       </c>
-      <c r="AE7" t="s">
+      <c r="AF7" t="s">
         <v>717</v>
       </c>
-      <c r="AF7" t="s">
+      <c r="AG7" t="s">
         <v>716</v>
       </c>
-      <c r="AG7" t="s">
+      <c r="AH7" t="s">
         <v>1487</v>
       </c>
-      <c r="AI7" s="36">
+      <c r="AJ7" s="36">
         <v>7.5999999999999998E-2</v>
       </c>
-      <c r="AT7" s="36">
+      <c r="AU7" s="36">
         <v>6.83E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:69" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:70" x14ac:dyDescent="0.2">
       <c r="A8">
         <f t="shared" si="1"/>
         <v>6</v>
@@ -6853,29 +6870,30 @@
       <c r="V8" s="4">
         <v>120883.773328</v>
       </c>
-      <c r="W8" s="6" t="s">
+      <c r="W8" s="4"/>
+      <c r="X8" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="X8" s="6" t="s">
+      <c r="Y8" s="6" t="s">
         <v>939</v>
       </c>
-      <c r="Y8" s="8" t="s">
+      <c r="Z8" s="8" t="s">
         <v>1478</v>
       </c>
-      <c r="Z8">
+      <c r="AA8">
         <v>1998</v>
       </c>
-      <c r="AB8">
+      <c r="AC8">
         <v>573</v>
       </c>
-      <c r="AQ8" s="9">
+      <c r="AR8" s="9">
         <v>0.14699999999999999</v>
       </c>
-      <c r="AR8" s="9">
+      <c r="AS8" s="9">
         <v>5.8000000000000003E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:69" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:70" x14ac:dyDescent="0.2">
       <c r="A9">
         <f t="shared" si="1"/>
         <v>7</v>
@@ -6928,29 +6946,30 @@
       <c r="V9" s="4">
         <v>75171.481593000004</v>
       </c>
-      <c r="W9" s="6" t="s">
+      <c r="W9" s="4"/>
+      <c r="X9" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="X9" s="6" t="s">
+      <c r="Y9" s="6" t="s">
         <v>219</v>
       </c>
-      <c r="Y9" s="8" t="s">
+      <c r="Z9" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="Z9">
+      <c r="AA9">
         <v>1978</v>
       </c>
-      <c r="AB9">
+      <c r="AC9">
         <v>310</v>
       </c>
-      <c r="AW9" s="9">
+      <c r="AX9" s="9">
         <v>0.38</v>
       </c>
-      <c r="BB9" s="9">
+      <c r="BC9" s="9">
         <v>0.25</v>
       </c>
     </row>
-    <row r="10" spans="1:69" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:70" x14ac:dyDescent="0.2">
       <c r="A10">
         <f t="shared" si="1"/>
         <v>8</v>
@@ -7003,20 +7022,21 @@
       <c r="V10" s="4">
         <v>719810.28665300005</v>
       </c>
-      <c r="W10" s="6" t="s">
+      <c r="W10" s="4"/>
+      <c r="X10" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="X10" s="6" t="s">
+      <c r="Y10" s="6" t="s">
         <v>1130</v>
       </c>
-      <c r="Y10" s="8" t="s">
+      <c r="Z10" s="8" t="s">
         <v>664</v>
       </c>
-      <c r="AB10">
+      <c r="AC10">
         <v>3000</v>
       </c>
     </row>
-    <row r="11" spans="1:69" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:70" x14ac:dyDescent="0.2">
       <c r="A11">
         <f t="shared" si="1"/>
         <v>9</v>
@@ -7048,17 +7068,18 @@
       <c r="V11" s="4">
         <v>98415.069591000007</v>
       </c>
-      <c r="W11" s="6" t="s">
+      <c r="W11" s="4"/>
+      <c r="X11" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="X11" s="6" t="s">
+      <c r="Y11" s="6" t="s">
         <v>219</v>
       </c>
-      <c r="AB11">
+      <c r="AC11">
         <v>1100</v>
       </c>
     </row>
-    <row r="12" spans="1:69" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:70" x14ac:dyDescent="0.2">
       <c r="A12">
         <f t="shared" si="1"/>
         <v>10</v>
@@ -7102,39 +7123,40 @@
       <c r="V12" s="4">
         <v>48800.428701999997</v>
       </c>
-      <c r="W12" s="6" t="s">
+      <c r="W12" s="4"/>
+      <c r="X12" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="X12" s="6" t="s">
+      <c r="Y12" s="6" t="s">
         <v>219</v>
       </c>
-      <c r="Y12" s="8" t="s">
+      <c r="Z12" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="Z12">
+      <c r="AA12">
         <v>2001</v>
       </c>
-      <c r="AB12">
+      <c r="AC12">
         <v>2100</v>
       </c>
-      <c r="AI12" s="9">
+      <c r="AJ12" s="9">
         <v>0.12</v>
       </c>
-      <c r="AQ12" s="9">
+      <c r="AR12" s="9">
         <v>0.15</v>
       </c>
-      <c r="AR12" s="9">
+      <c r="AS12" s="9">
         <v>0.10100000000000001</v>
       </c>
-      <c r="AW12" s="9">
+      <c r="AX12" s="9">
         <v>0.20230000000000001</v>
       </c>
-      <c r="AX12" s="9"/>
       <c r="AY12" s="9"/>
       <c r="AZ12" s="9"/>
       <c r="BA12" s="9"/>
-    </row>
-    <row r="13" spans="1:69" x14ac:dyDescent="0.2">
+      <c r="BB12" s="9"/>
+    </row>
+    <row r="13" spans="1:70" x14ac:dyDescent="0.2">
       <c r="A13">
         <f t="shared" si="1"/>
         <v>11</v>
@@ -7181,42 +7203,43 @@
       <c r="V13" s="4">
         <v>141059.27600700001</v>
       </c>
-      <c r="W13" s="6" t="s">
+      <c r="W13" s="4"/>
+      <c r="X13" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="X13" s="6" t="s">
+      <c r="Y13" s="6" t="s">
         <v>219</v>
       </c>
-      <c r="Y13" s="8" t="s">
+      <c r="Z13" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="AB13">
+      <c r="AC13">
         <v>2500</v>
       </c>
-      <c r="AI13" s="9">
+      <c r="AJ13" s="9">
         <v>9.6000000000000002E-2</v>
       </c>
-      <c r="AK13" s="9">
+      <c r="AL13" s="9">
         <v>0.185</v>
       </c>
-      <c r="AQ13" s="9">
+      <c r="AR13" s="9">
         <v>0.14299999999999999</v>
       </c>
-      <c r="AR13" s="9">
+      <c r="AS13" s="9">
         <v>0.16400000000000001</v>
       </c>
-      <c r="AW13" s="9"/>
       <c r="AX13" s="9"/>
-      <c r="AY13" s="9">
+      <c r="AY13" s="9"/>
+      <c r="AZ13" s="9">
         <v>7.3999999999999996E-2</v>
       </c>
-      <c r="AZ13" s="9"/>
       <c r="BA13" s="9"/>
-      <c r="BQ13" t="s">
+      <c r="BB13" s="9"/>
+      <c r="BR13" t="s">
         <v>1499</v>
       </c>
     </row>
-    <row r="14" spans="1:69" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:70" x14ac:dyDescent="0.2">
       <c r="A14">
         <f t="shared" si="1"/>
         <v>12</v>
@@ -7249,52 +7272,53 @@
       <c r="V14" s="4">
         <v>50706.910930999999</v>
       </c>
-      <c r="W14" s="6" t="s">
+      <c r="W14" s="4"/>
+      <c r="X14" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="X14" s="6" t="s">
+      <c r="Y14" s="6" t="s">
         <v>1546</v>
       </c>
-      <c r="Y14" s="8" t="s">
+      <c r="Z14" s="8" t="s">
         <v>673</v>
       </c>
-      <c r="AB14">
+      <c r="AC14">
         <v>82</v>
       </c>
-      <c r="AH14" s="9">
+      <c r="AI14" s="9">
         <v>0.15</v>
       </c>
-      <c r="AI14" s="9">
+      <c r="AJ14" s="9">
         <v>0.33</v>
       </c>
-      <c r="AJ14" s="9">
+      <c r="AK14" s="9">
         <v>-0.18</v>
       </c>
-      <c r="AK14" s="9"/>
-      <c r="AP14" s="9">
+      <c r="AL14" s="9"/>
+      <c r="AQ14" s="9">
         <v>0.13500000000000001</v>
       </c>
-      <c r="AQ14" s="9">
+      <c r="AR14" s="9">
         <v>0.14399999999999999</v>
       </c>
-      <c r="AR14" s="9">
+      <c r="AS14" s="9">
         <v>8.1000000000000003E-2</v>
       </c>
-      <c r="AS14" s="9">
+      <c r="AT14" s="9">
         <v>0.47220000000000001</v>
       </c>
-      <c r="AT14" s="9">
+      <c r="AU14" s="9">
         <v>0.29520000000000002</v>
       </c>
-      <c r="AW14" s="9"/>
-      <c r="AX14" s="9">
+      <c r="AX14" s="9"/>
+      <c r="AY14" s="9">
         <v>-0.43</v>
       </c>
-      <c r="AY14" s="9"/>
       <c r="AZ14" s="9"/>
       <c r="BA14" s="9"/>
-    </row>
-    <row r="15" spans="1:69" x14ac:dyDescent="0.2">
+      <c r="BB14" s="9"/>
+    </row>
+    <row r="15" spans="1:70" x14ac:dyDescent="0.2">
       <c r="A15">
         <f t="shared" si="1"/>
         <v>13</v>
@@ -7335,33 +7359,34 @@
       <c r="V15" s="4">
         <v>66411.788618999999</v>
       </c>
-      <c r="W15" s="6" t="s">
+      <c r="W15" s="4"/>
+      <c r="X15" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="X15" s="6" t="s">
+      <c r="Y15" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="Y15" s="8" t="s">
+      <c r="Z15" s="8" t="s">
         <v>223</v>
       </c>
-      <c r="AB15">
+      <c r="AC15">
         <v>1900</v>
       </c>
-      <c r="AK15" s="9">
+      <c r="AL15" s="9">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="AS15" s="9"/>
-      <c r="AW15" s="9">
+      <c r="AT15" s="9"/>
+      <c r="AX15" s="9">
         <v>8.6400000000000005E-2</v>
       </c>
-      <c r="AX15" s="9">
+      <c r="AY15" s="9">
         <v>4.5999999999999999E-3</v>
       </c>
-      <c r="AY15" s="9"/>
       <c r="AZ15" s="9"/>
       <c r="BA15" s="9"/>
-    </row>
-    <row r="16" spans="1:69" x14ac:dyDescent="0.2">
+      <c r="BB15" s="9"/>
+    </row>
+    <row r="16" spans="1:70" x14ac:dyDescent="0.2">
       <c r="A16">
         <f t="shared" si="1"/>
         <v>14</v>
@@ -7387,27 +7412,28 @@
       <c r="V16" s="4">
         <v>52494.564572000003</v>
       </c>
-      <c r="W16" s="6" t="s">
+      <c r="W16" s="4"/>
+      <c r="X16" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="X16" s="6" t="s">
+      <c r="Y16" s="6" t="s">
         <v>1559</v>
       </c>
-      <c r="AB16">
+      <c r="AC16">
         <v>1787</v>
       </c>
-      <c r="AS16" s="10" t="s">
+      <c r="AT16" s="10" t="s">
         <v>1496</v>
       </c>
-      <c r="AW16" s="9"/>
-      <c r="AX16" s="9" t="s">
+      <c r="AX16" s="9"/>
+      <c r="AY16" s="9" t="s">
         <v>1501</v>
       </c>
-      <c r="AY16" s="9"/>
       <c r="AZ16" s="9"/>
       <c r="BA16" s="9"/>
-    </row>
-    <row r="17" spans="1:66" x14ac:dyDescent="0.2">
+      <c r="BB16" s="9"/>
+    </row>
+    <row r="17" spans="1:67" x14ac:dyDescent="0.2">
       <c r="A17">
         <f t="shared" si="1"/>
         <v>15</v>
@@ -7457,50 +7483,51 @@
       <c r="V17" s="4">
         <v>50941.421372999997</v>
       </c>
-      <c r="W17" s="6" t="s">
+      <c r="W17" s="4"/>
+      <c r="X17" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="X17" s="6" t="s">
+      <c r="Y17" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="Y17" s="8" t="s">
+      <c r="Z17" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="Z17">
+      <c r="AA17">
         <v>1992</v>
       </c>
-      <c r="AB17">
+      <c r="AC17">
         <v>2800</v>
       </c>
-      <c r="AH17" s="9">
+      <c r="AI17" s="9">
         <v>0.19</v>
       </c>
-      <c r="AI17" s="9">
+      <c r="AJ17" s="9">
         <v>0.106</v>
       </c>
-      <c r="AJ17" s="9">
+      <c r="AK17" s="9">
         <v>0.1</v>
       </c>
-      <c r="AK17" s="9">
+      <c r="AL17" s="9">
         <v>0.09</v>
       </c>
-      <c r="AS17" s="9"/>
-      <c r="AT17" s="9">
+      <c r="AT17" s="9"/>
+      <c r="AU17" s="9">
         <v>0.14000000000000001</v>
       </c>
-      <c r="AW17" s="9"/>
-      <c r="AX17" s="9">
+      <c r="AX17" s="9"/>
+      <c r="AY17" s="9">
         <v>-0.18529999999999999</v>
       </c>
-      <c r="AY17" s="9">
+      <c r="AZ17" s="9">
         <v>0.13</v>
       </c>
-      <c r="AZ17" s="9">
+      <c r="BA17" s="9">
         <v>0.34</v>
       </c>
-      <c r="BA17" s="9"/>
-    </row>
-    <row r="18" spans="1:66" x14ac:dyDescent="0.2">
+      <c r="BB17" s="9"/>
+    </row>
+    <row r="18" spans="1:67" x14ac:dyDescent="0.2">
       <c r="A18">
         <f t="shared" si="1"/>
         <v>16</v>
@@ -7535,23 +7562,24 @@
       <c r="V18" s="4">
         <v>27139.356501999999</v>
       </c>
-      <c r="W18" s="6" t="s">
+      <c r="W18" s="4"/>
+      <c r="X18" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="AB18">
+      <c r="AC18">
         <v>119</v>
       </c>
-      <c r="AD18">
+      <c r="AE18">
         <v>2009</v>
       </c>
-      <c r="AS18" s="9"/>
-      <c r="AW18" s="9"/>
+      <c r="AT18" s="9"/>
       <c r="AX18" s="9"/>
       <c r="AY18" s="9"/>
       <c r="AZ18" s="9"/>
       <c r="BA18" s="9"/>
-    </row>
-    <row r="19" spans="1:66" x14ac:dyDescent="0.2">
+      <c r="BB18" s="9"/>
+    </row>
+    <row r="19" spans="1:67" x14ac:dyDescent="0.2">
       <c r="A19">
         <f t="shared" si="1"/>
         <v>17</v>
@@ -7604,38 +7632,39 @@
       <c r="V19" s="4">
         <v>34589.864589999997</v>
       </c>
-      <c r="W19" s="6" t="s">
+      <c r="W19" s="4"/>
+      <c r="X19" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="X19" s="6" t="s">
+      <c r="Y19" s="6" t="s">
         <v>220</v>
       </c>
-      <c r="Y19" s="8" t="s">
+      <c r="Z19" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="AB19">
+      <c r="AC19">
         <v>275</v>
       </c>
-      <c r="AI19" s="9">
+      <c r="AJ19" s="9">
         <v>0.13800000000000001</v>
       </c>
-      <c r="AJ19" s="9">
+      <c r="AK19" s="9">
         <v>-2.4E-2</v>
       </c>
-      <c r="AS19" s="9">
+      <c r="AT19" s="9">
         <v>0.22500000000000001</v>
       </c>
-      <c r="AW19" s="9">
+      <c r="AX19" s="9">
         <v>0.18890000000000001</v>
       </c>
-      <c r="AX19" s="9">
+      <c r="AY19" s="9">
         <v>0.1</v>
       </c>
-      <c r="AY19" s="9"/>
       <c r="AZ19" s="9"/>
       <c r="BA19" s="9"/>
-    </row>
-    <row r="20" spans="1:66" x14ac:dyDescent="0.2">
+      <c r="BB19" s="9"/>
+    </row>
+    <row r="20" spans="1:67" x14ac:dyDescent="0.2">
       <c r="A20">
         <f t="shared" si="1"/>
         <v>18</v>
@@ -7700,30 +7729,31 @@
       <c r="V20" s="4">
         <v>35899.628173999998</v>
       </c>
-      <c r="W20" s="6" t="s">
+      <c r="W20" s="4"/>
+      <c r="X20" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="X20" s="6" t="s">
+      <c r="Y20" s="6" t="s">
         <v>220</v>
       </c>
-      <c r="Y20" s="8" t="s">
+      <c r="Z20" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="AB20">
+      <c r="AC20">
         <v>157</v>
       </c>
-      <c r="AI20" s="9">
+      <c r="AJ20" s="9">
         <v>0.215</v>
       </c>
-      <c r="AQ20" s="9">
+      <c r="AR20" s="9">
         <v>0.111</v>
       </c>
-      <c r="AR20" s="9">
+      <c r="AS20" s="9">
         <v>-2.4E-2</v>
       </c>
-      <c r="AS20" s="9"/>
-    </row>
-    <row r="21" spans="1:66" x14ac:dyDescent="0.2">
+      <c r="AT20" s="9"/>
+    </row>
+    <row r="21" spans="1:67" x14ac:dyDescent="0.2">
       <c r="A21">
         <f t="shared" si="1"/>
         <v>19</v>
@@ -7767,29 +7797,30 @@
       <c r="V21" s="4">
         <v>34081.542845000004</v>
       </c>
-      <c r="W21" s="6" t="s">
+      <c r="W21" s="4"/>
+      <c r="X21" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="X21" s="6" t="s">
+      <c r="Y21" s="6" t="s">
         <v>220</v>
       </c>
-      <c r="Y21" s="8" t="s">
+      <c r="Z21" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="AB21">
+      <c r="AC21">
         <v>162</v>
       </c>
-      <c r="AI21" s="9">
+      <c r="AJ21" s="9">
         <v>0.28499999999999998</v>
       </c>
-      <c r="AJ21" s="9">
+      <c r="AK21" s="9">
         <v>-0.56000000000000005</v>
       </c>
-      <c r="AS21" s="9">
+      <c r="AT21" s="9">
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="22" spans="1:66" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:67" x14ac:dyDescent="0.2">
       <c r="A22">
         <f t="shared" si="1"/>
         <v>20</v>
@@ -7840,62 +7871,63 @@
       <c r="V22" s="4">
         <v>24791.713463</v>
       </c>
-      <c r="W22" s="6" t="s">
+      <c r="W22" s="4"/>
+      <c r="X22" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="Y22" s="8" t="s">
+      <c r="Z22" s="8" t="s">
         <v>238</v>
       </c>
-      <c r="AB22">
+      <c r="AC22">
         <v>1300</v>
       </c>
-      <c r="AD22">
+      <c r="AE22">
         <v>1975</v>
       </c>
-      <c r="AG22" t="s">
+      <c r="AH22" t="s">
         <v>1486</v>
       </c>
-      <c r="AH22" s="9">
+      <c r="AI22" s="9">
         <v>-0.14000000000000001</v>
       </c>
-      <c r="AI22" s="9" t="s">
+      <c r="AJ22" s="9" t="s">
         <v>1500</v>
       </c>
-      <c r="AJ22" s="9">
+      <c r="AK22" s="9">
         <v>0.1</v>
-      </c>
-      <c r="AK22" s="9">
-        <v>-0.05</v>
       </c>
       <c r="AL22" s="9">
         <v>-0.05</v>
       </c>
       <c r="AM22" s="9">
+        <v>-0.05</v>
+      </c>
+      <c r="AN22" s="9">
         <v>0</v>
       </c>
-      <c r="AN22" s="27">
+      <c r="AO22" s="27">
         <v>0.14599999999999999</v>
       </c>
-      <c r="AP22" t="s">
+      <c r="AQ22" t="s">
         <v>1505</v>
       </c>
-      <c r="AQ22" t="s">
+      <c r="AR22" t="s">
         <v>1503</v>
       </c>
-      <c r="AR22" t="s">
+      <c r="AS22" t="s">
         <v>1504</v>
       </c>
-      <c r="AT22" t="s">
+      <c r="AU22" t="s">
         <v>1502</v>
       </c>
-      <c r="AX22" s="27">
+      <c r="AY22" s="27">
         <v>9.4E-2</v>
       </c>
-      <c r="AY22" t="s">
+      <c r="AZ22" t="s">
         <v>1497</v>
       </c>
     </row>
-    <row r="23" spans="1:66" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:67" x14ac:dyDescent="0.2">
       <c r="A23">
         <f t="shared" si="1"/>
         <v>21</v>
@@ -7924,17 +7956,18 @@
       <c r="V23" s="4">
         <v>22465.170517999999</v>
       </c>
-      <c r="W23" s="6" t="s">
+      <c r="W23" s="4"/>
+      <c r="X23" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="X23" s="6" t="s">
+      <c r="Y23" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="AB23">
+      <c r="AC23">
         <v>350</v>
       </c>
     </row>
-    <row r="24" spans="1:66" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:67" x14ac:dyDescent="0.2">
       <c r="A24">
         <f t="shared" si="1"/>
         <v>22</v>
@@ -7969,17 +8002,18 @@
       <c r="V24" s="4">
         <v>28384.872542000001</v>
       </c>
-      <c r="W24" s="6" t="s">
+      <c r="W24" s="4"/>
+      <c r="X24" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="X24" s="6" t="s">
+      <c r="Y24" s="6" t="s">
         <v>1559</v>
       </c>
-      <c r="AB24">
+      <c r="AC24">
         <v>56</v>
       </c>
     </row>
-    <row r="25" spans="1:66" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:67" x14ac:dyDescent="0.2">
       <c r="A25">
         <f t="shared" si="1"/>
         <v>23</v>
@@ -8014,20 +8048,21 @@
       <c r="V25" s="4">
         <v>23178.205569999998</v>
       </c>
-      <c r="W25" s="6" t="s">
+      <c r="W25" s="4"/>
+      <c r="X25" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="X25" s="6" t="s">
+      <c r="Y25" s="6" t="s">
         <v>1560</v>
       </c>
-      <c r="AB25">
+      <c r="AC25">
         <v>230</v>
       </c>
-      <c r="AY25" s="36">
+      <c r="AZ25" s="36">
         <v>0.14799999999999999</v>
       </c>
     </row>
-    <row r="26" spans="1:66" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:67" x14ac:dyDescent="0.2">
       <c r="A26">
         <f t="shared" si="1"/>
         <v>24</v>
@@ -8062,17 +8097,18 @@
       <c r="V26" s="4">
         <v>29446.119595</v>
       </c>
-      <c r="W26" s="6" t="s">
+      <c r="W26" s="4"/>
+      <c r="X26" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="AB26">
+      <c r="AC26">
         <v>241</v>
       </c>
-      <c r="AK26" s="9">
+      <c r="AL26" s="9">
         <v>0.13500000000000001</v>
       </c>
     </row>
-    <row r="27" spans="1:66" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:67" x14ac:dyDescent="0.2">
       <c r="A27">
         <f t="shared" si="1"/>
         <v>25</v>
@@ -8104,26 +8140,27 @@
       <c r="V27" s="4">
         <v>222.78121300000001</v>
       </c>
-      <c r="W27" s="6" t="s">
+      <c r="W27" s="4"/>
+      <c r="X27" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="X27" s="6" t="s">
+      <c r="Y27" s="6" t="s">
         <v>220</v>
       </c>
-      <c r="Z27">
+      <c r="AA27">
         <v>2006</v>
       </c>
-      <c r="AQ27" s="9">
+      <c r="AR27" s="9">
         <v>0.16200000000000001</v>
       </c>
-      <c r="AR27" s="9">
+      <c r="AS27" s="9">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="AS27" s="9">
+      <c r="AT27" s="9">
         <v>0.56000000000000005</v>
       </c>
     </row>
-    <row r="28" spans="1:66" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:67" x14ac:dyDescent="0.2">
       <c r="A28">
         <f t="shared" si="1"/>
         <v>26</v>
@@ -8173,119 +8210,120 @@
       <c r="V28" s="4">
         <v>14051.394007000001</v>
       </c>
-      <c r="W28" s="6" t="s">
+      <c r="W28" s="4"/>
+      <c r="X28" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="X28" s="6" t="s">
+      <c r="Y28" s="6" t="s">
         <v>220</v>
       </c>
-      <c r="Y28" s="8" t="s">
+      <c r="Z28" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="Z28">
+      <c r="AA28">
         <v>1997</v>
       </c>
-      <c r="AA28" t="s">
+      <c r="AB28" t="s">
         <v>227</v>
       </c>
-      <c r="AC28" s="9">
+      <c r="AD28" s="9">
         <f>RATE(2022-1998,0,-1,13.71)</f>
         <v>0.11526111596972678</v>
       </c>
-      <c r="AD28" s="9">
-        <f>1*(1+BH$28)*(1+BG28)*(1+BF28)*(1+BE28)*(1+BD28)*(1+BC28)*(1+BB28)*(1+BA28)*(1+AZ28)*(1+AY28)*(1+AX28)*(1+AW28)*(1+AV28)*(1+AU28)*(1+AT28)*(1+AS28)*(1+AR28)*(1+AQ28)*(1+AP28)*(1+AO28)*(1+AN28)*(1+AM28)*(1+AL28)*(1+AK28)*(1+AJ28)-1</f>
+      <c r="AE28" s="9">
+        <f>1*(1+BI$28)*(1+BH28)*(1+BG28)*(1+BF28)*(1+BE28)*(1+BD28)*(1+BC28)*(1+BB28)*(1+BA28)*(1+AZ28)*(1+AY28)*(1+AX28)*(1+AW28)*(1+AV28)*(1+AU28)*(1+AT28)*(1+AS28)*(1+AR28)*(1+AQ28)*(1+AP28)*(1+AO28)*(1+AN28)*(1+AM28)*(1+AL28)*(1+AK28)-1</f>
         <v>13.713492129281141</v>
       </c>
-      <c r="AE28" s="9"/>
       <c r="AF28" s="9"/>
       <c r="AG28" s="9"/>
       <c r="AH28" s="9"/>
-      <c r="AI28" s="9">
+      <c r="AI28" s="9"/>
+      <c r="AJ28" s="9">
         <v>0.19</v>
       </c>
-      <c r="AJ28" s="10">
+      <c r="AK28" s="10">
         <v>-0.33</v>
       </c>
-      <c r="AK28" s="9">
+      <c r="AL28" s="9">
         <v>-7.0000000000000007E-2</v>
       </c>
-      <c r="AL28" s="9">
+      <c r="AM28" s="9">
         <v>0.23</v>
       </c>
-      <c r="AM28" s="9">
+      <c r="AN28" s="9">
         <v>0.29899999999999999</v>
       </c>
-      <c r="AN28" s="9">
+      <c r="AO28" s="9">
         <v>-0.05</v>
       </c>
-      <c r="AO28" s="9">
+      <c r="AP28" s="9">
         <v>8.2000000000000003E-2</v>
       </c>
-      <c r="AP28" s="9">
+      <c r="AQ28" s="9">
         <v>-2.7E-2</v>
       </c>
-      <c r="AQ28" s="9">
+      <c r="AR28" s="9">
         <v>8.7999999999999995E-2</v>
       </c>
-      <c r="AR28" s="9">
+      <c r="AS28" s="9">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="AS28" s="9">
+      <c r="AT28" s="9">
         <v>0.14199999999999999</v>
       </c>
-      <c r="AT28" s="9">
+      <c r="AU28" s="9">
         <v>0.193</v>
       </c>
-      <c r="AU28" s="9">
+      <c r="AV28" s="9">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="AV28" s="9">
+      <c r="AW28" s="9">
         <v>0.126</v>
       </c>
-      <c r="AW28" s="9">
+      <c r="AX28" s="9">
         <v>0.14000000000000001</v>
       </c>
-      <c r="AX28" s="9">
+      <c r="AY28" s="9">
         <v>-0.32900000000000001</v>
       </c>
-      <c r="AY28" s="9">
+      <c r="AZ28" s="9">
         <v>0.46200000000000002</v>
       </c>
-      <c r="AZ28" s="9">
+      <c r="BA28" s="9">
         <v>0.13700000000000001</v>
       </c>
-      <c r="BA28" s="9">
+      <c r="BB28" s="9">
         <v>0.25900000000000001</v>
       </c>
-      <c r="BB28" s="9">
+      <c r="BC28" s="9">
         <v>0.14599999999999999</v>
       </c>
-      <c r="BC28" s="9">
+      <c r="BD28" s="9">
         <v>8.2000000000000003E-2</v>
       </c>
-      <c r="BD28" s="9">
+      <c r="BE28" s="9">
         <v>0.14599999999999999</v>
       </c>
-      <c r="BE28" s="9">
+      <c r="BF28" s="9">
         <v>0.40400000000000003</v>
       </c>
-      <c r="BF28" s="9">
+      <c r="BG28" s="9">
         <v>0.73399999999999999</v>
       </c>
-      <c r="BG28" s="9">
+      <c r="BH28" s="9">
         <v>0.46800000000000003</v>
       </c>
-      <c r="BH28" s="9">
+      <c r="BI28" s="9">
         <v>7.5999999999999998E-2</v>
       </c>
-      <c r="BI28" s="9"/>
       <c r="BJ28" s="9"/>
       <c r="BK28" s="9"/>
       <c r="BL28" s="9"/>
       <c r="BM28" s="9"/>
       <c r="BN28" s="9"/>
-    </row>
-    <row r="29" spans="1:66" x14ac:dyDescent="0.2">
+      <c r="BO28" s="9"/>
+    </row>
+    <row r="29" spans="1:67" x14ac:dyDescent="0.2">
       <c r="A29">
         <f t="shared" si="1"/>
         <v>27</v>
@@ -8320,16 +8358,17 @@
       <c r="V29" s="4">
         <v>18930.893253999999</v>
       </c>
-      <c r="W29" s="6" t="s">
+      <c r="W29" s="4"/>
+      <c r="X29" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="X29" s="6" t="s">
+      <c r="Y29" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="AX29" s="9"/>
       <c r="AY29" s="9"/>
-    </row>
-    <row r="30" spans="1:66" x14ac:dyDescent="0.2">
+      <c r="AZ29" s="9"/>
+    </row>
+    <row r="30" spans="1:67" x14ac:dyDescent="0.2">
       <c r="A30">
         <f t="shared" si="1"/>
         <v>28</v>
@@ -8367,27 +8406,28 @@
       <c r="V30" s="4">
         <v>13729.120532999999</v>
       </c>
-      <c r="W30" s="6" t="s">
+      <c r="W30" s="4"/>
+      <c r="X30" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="AF30" t="s">
+      <c r="AG30" t="s">
         <v>1562</v>
       </c>
-      <c r="AI30" s="9">
+      <c r="AJ30" s="9">
         <v>0.26300000000000001</v>
       </c>
-      <c r="AJ30" s="9">
+      <c r="AK30" s="9">
         <v>-8.7999999999999995E-2</v>
       </c>
-      <c r="AW30" s="9">
+      <c r="AX30" s="9">
         <v>0.41210000000000002</v>
       </c>
-      <c r="AX30" s="9">
+      <c r="AY30" s="9">
         <v>-0.11899999999999999</v>
       </c>
-      <c r="AY30" s="9"/>
-    </row>
-    <row r="31" spans="1:66" x14ac:dyDescent="0.2">
+      <c r="AZ30" s="9"/>
+    </row>
+    <row r="31" spans="1:67" x14ac:dyDescent="0.2">
       <c r="A31">
         <f t="shared" si="1"/>
         <v>29</v>
@@ -8425,36 +8465,37 @@
       <c r="V31" s="4">
         <v>17593.419802</v>
       </c>
-      <c r="W31" s="6" t="s">
+      <c r="W31" s="4"/>
+      <c r="X31" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="X31" s="6" t="s">
+      <c r="Y31" s="6" t="s">
         <v>1305</v>
       </c>
-      <c r="Y31" s="8" t="s">
+      <c r="Z31" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="Z31">
+      <c r="AA31">
         <v>1977</v>
       </c>
-      <c r="AI31" s="9">
+      <c r="AJ31" s="9">
         <v>4.7E-2</v>
       </c>
-      <c r="AP31" s="9">
+      <c r="AQ31" s="9">
         <v>0.13100000000000001</v>
       </c>
-      <c r="AQ31" s="9">
+      <c r="AR31" s="9">
         <v>2.7E-2</v>
       </c>
-      <c r="AW31" s="9">
+      <c r="AX31" s="9">
         <v>0.307</v>
       </c>
-      <c r="AX31" s="9">
+      <c r="AY31" s="9">
         <v>-0.03</v>
       </c>
-      <c r="AY31" s="9"/>
-    </row>
-    <row r="32" spans="1:66" x14ac:dyDescent="0.2">
+      <c r="AZ31" s="9"/>
+    </row>
+    <row r="32" spans="1:67" x14ac:dyDescent="0.2">
       <c r="A32">
         <f t="shared" si="1"/>
         <v>30</v>
@@ -8487,20 +8528,21 @@
         <v>10.111667000000001</v>
       </c>
       <c r="V32" s="4"/>
-      <c r="W32" s="6" t="s">
+      <c r="W32" s="4"/>
+      <c r="X32" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="X32" s="6" t="s">
+      <c r="Y32" s="6" t="s">
         <v>1559</v>
       </c>
-      <c r="AK32" s="9">
+      <c r="AL32" s="9">
         <v>5.5E-2</v>
       </c>
-      <c r="AW32" s="9"/>
       <c r="AX32" s="9"/>
       <c r="AY32" s="9"/>
-    </row>
-    <row r="33" spans="1:51" x14ac:dyDescent="0.2">
+      <c r="AZ32" s="9"/>
+    </row>
+    <row r="33" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A33">
         <f t="shared" si="1"/>
         <v>31</v>
@@ -8533,14 +8575,15 @@
         <v>30095.626647000001</v>
       </c>
       <c r="V33" s="4"/>
-      <c r="W33" s="6" t="s">
+      <c r="W33" s="4"/>
+      <c r="X33" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="AW33" s="9"/>
       <c r="AX33" s="9"/>
       <c r="AY33" s="9"/>
-    </row>
-    <row r="34" spans="1:51" x14ac:dyDescent="0.2">
+      <c r="AZ33" s="9"/>
+    </row>
+    <row r="34" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A34">
         <f t="shared" si="1"/>
         <v>32</v>
@@ -8579,23 +8622,24 @@
         <v>9036.702464</v>
       </c>
       <c r="V34" s="4"/>
-      <c r="W34" s="6" t="s">
+      <c r="W34" s="4"/>
+      <c r="X34" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="X34" s="6" t="s">
+      <c r="Y34" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="Y34" s="8" t="s">
+      <c r="Z34" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="Z34">
+      <c r="AA34">
         <v>2000</v>
       </c>
-      <c r="AW34" s="9"/>
       <c r="AX34" s="9"/>
       <c r="AY34" s="9"/>
-    </row>
-    <row r="35" spans="1:51" x14ac:dyDescent="0.2">
+      <c r="AZ34" s="9"/>
+    </row>
+    <row r="35" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A35">
         <f t="shared" si="1"/>
         <v>33</v>
@@ -8628,21 +8672,22 @@
         <v>4971.0965189999997</v>
       </c>
       <c r="V35" s="4"/>
-      <c r="W35" s="6" t="s">
+      <c r="W35" s="4"/>
+      <c r="X35" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="X35" s="6" t="s">
+      <c r="Y35" s="6" t="s">
         <v>1564</v>
       </c>
-      <c r="Y35" s="8" t="s">
+      <c r="Z35" s="8" t="s">
         <v>1206</v>
       </c>
-      <c r="Z35">
+      <c r="AA35">
         <v>2008</v>
       </c>
-      <c r="AW35" s="9"/>
-    </row>
-    <row r="36" spans="1:51" x14ac:dyDescent="0.2">
+      <c r="AX35" s="9"/>
+    </row>
+    <row r="36" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A36">
         <f t="shared" si="1"/>
         <v>34</v>
@@ -8666,15 +8711,16 @@
         <v>11911.767229999999</v>
       </c>
       <c r="V36" s="4"/>
-      <c r="W36" s="6" t="s">
+      <c r="W36" s="4"/>
+      <c r="X36" s="6" t="s">
         <v>1267</v>
       </c>
-      <c r="Y36" s="8" t="s">
+      <c r="Z36" s="8" t="s">
         <v>223</v>
       </c>
-      <c r="AW36" s="9"/>
-    </row>
-    <row r="37" spans="1:51" x14ac:dyDescent="0.2">
+      <c r="AX36" s="9"/>
+    </row>
+    <row r="37" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A37">
         <f t="shared" si="1"/>
         <v>35</v>
@@ -8707,20 +8753,21 @@
         <v>6704.9046639999997</v>
       </c>
       <c r="V37" s="4"/>
-      <c r="W37" s="6" t="s">
+      <c r="W37" s="4"/>
+      <c r="X37" s="6" t="s">
         <v>1566</v>
       </c>
-      <c r="X37" s="6" t="s">
+      <c r="Y37" s="6" t="s">
         <v>1565</v>
       </c>
-      <c r="AW37" s="9">
+      <c r="AX37" s="9">
         <v>0.29020000000000001</v>
       </c>
-      <c r="AX37" s="9">
+      <c r="AY37" s="9">
         <v>0.08</v>
       </c>
     </row>
-    <row r="38" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A38">
         <f t="shared" si="1"/>
         <v>36</v>
@@ -8748,17 +8795,18 @@
       <c r="T38" s="4"/>
       <c r="U38" s="4"/>
       <c r="V38" s="4"/>
-      <c r="W38" s="6" t="s">
+      <c r="W38" s="4"/>
+      <c r="X38" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="X38" s="6" t="s">
+      <c r="Y38" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="Y38" s="8" t="s">
+      <c r="Z38" s="8" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="39" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A39">
         <f t="shared" si="1"/>
         <v>37</v>
@@ -8782,17 +8830,18 @@
       <c r="T39" s="4"/>
       <c r="U39" s="4"/>
       <c r="V39" s="4"/>
-      <c r="W39" s="6" t="s">
+      <c r="W39" s="4"/>
+      <c r="X39" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="X39" s="6" t="s">
+      <c r="Y39" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="Y39" s="8" t="s">
+      <c r="Z39" s="8" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="40" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A40">
         <f t="shared" si="1"/>
         <v>38</v>
@@ -8813,8 +8862,9 @@
       <c r="T40" s="4"/>
       <c r="U40" s="4"/>
       <c r="V40" s="4"/>
-    </row>
-    <row r="41" spans="1:51" x14ac:dyDescent="0.2">
+      <c r="W40" s="4"/>
+    </row>
+    <row r="41" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A41">
         <f t="shared" si="1"/>
         <v>39</v>
@@ -8835,8 +8885,9 @@
       <c r="T41" s="4"/>
       <c r="U41" s="4"/>
       <c r="V41" s="4"/>
-    </row>
-    <row r="42" spans="1:51" x14ac:dyDescent="0.2">
+      <c r="W41" s="4"/>
+    </row>
+    <row r="42" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A42">
         <f t="shared" si="1"/>
         <v>40</v>
@@ -8863,23 +8914,24 @@
       <c r="T42" s="4"/>
       <c r="U42" s="4"/>
       <c r="V42" s="4"/>
-      <c r="W42" s="6" t="s">
+      <c r="W42" s="4"/>
+      <c r="X42" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="X42" s="6" t="s">
+      <c r="Y42" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="Y42" s="8" t="s">
+      <c r="Z42" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="AS42" s="36">
+      <c r="AT42" s="36">
         <v>0.2525</v>
       </c>
-      <c r="AT42" s="36">
+      <c r="AU42" s="36">
         <v>0.215</v>
       </c>
     </row>
-    <row r="43" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A43">
         <f t="shared" si="1"/>
         <v>41</v>
@@ -8906,14 +8958,15 @@
       <c r="T43" s="4"/>
       <c r="U43" s="4"/>
       <c r="V43" s="4"/>
-      <c r="W43" s="6" t="s">
+      <c r="W43" s="4"/>
+      <c r="X43" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Y43" s="8" t="s">
+      <c r="Z43" s="8" t="s">
         <v>1206</v>
       </c>
     </row>
-    <row r="44" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A44">
         <f t="shared" si="1"/>
         <v>42</v>
@@ -8931,14 +8984,15 @@
       <c r="T44" s="4"/>
       <c r="U44" s="4"/>
       <c r="V44" s="4"/>
-      <c r="Z44">
+      <c r="W44" s="4"/>
+      <c r="AA44">
         <v>2007</v>
       </c>
-      <c r="AI44" s="9">
+      <c r="AJ44" s="9">
         <v>0.254</v>
       </c>
     </row>
-    <row r="45" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A45">
         <f t="shared" si="1"/>
         <v>43</v>
@@ -8965,17 +9019,18 @@
       <c r="T45" s="4"/>
       <c r="U45" s="4"/>
       <c r="V45" s="4"/>
-      <c r="W45" s="6" t="s">
+      <c r="W45" s="4"/>
+      <c r="X45" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="X45" s="6" t="s">
+      <c r="Y45" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="Y45" s="8" t="s">
+      <c r="Z45" s="8" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="46" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A46">
         <f t="shared" si="1"/>
         <v>44</v>
@@ -8996,11 +9051,12 @@
       <c r="T46" s="4"/>
       <c r="U46" s="4"/>
       <c r="V46" s="4"/>
-      <c r="W46" s="6" t="s">
+      <c r="W46" s="4"/>
+      <c r="X46" s="6" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="47" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A47">
         <f t="shared" si="1"/>
         <v>45</v>
@@ -9015,8 +9071,9 @@
       <c r="T47" s="4"/>
       <c r="U47" s="4"/>
       <c r="V47" s="4"/>
-    </row>
-    <row r="48" spans="1:51" x14ac:dyDescent="0.2">
+      <c r="W47" s="4"/>
+    </row>
+    <row r="48" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A48">
         <f t="shared" si="1"/>
         <v>46</v>
@@ -9031,8 +9088,9 @@
       <c r="T48" s="4"/>
       <c r="U48" s="4"/>
       <c r="V48" s="4"/>
-    </row>
-    <row r="49" spans="1:46" x14ac:dyDescent="0.2">
+      <c r="W48" s="4"/>
+    </row>
+    <row r="49" spans="1:47" x14ac:dyDescent="0.2">
       <c r="A49">
         <f t="shared" si="1"/>
         <v>47</v>
@@ -9056,22 +9114,23 @@
       <c r="T49" s="4"/>
       <c r="U49" s="4"/>
       <c r="V49" s="4"/>
-      <c r="AH49" s="9"/>
-      <c r="AI49" s="9">
+      <c r="W49" s="4"/>
+      <c r="AI49" s="9"/>
+      <c r="AJ49" s="9">
         <v>0.18</v>
       </c>
-      <c r="AQ49" s="9">
+      <c r="AR49" s="9">
         <v>0.11</v>
       </c>
-      <c r="AR49" s="9">
+      <c r="AS49" s="9">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="AS49" s="9"/>
-      <c r="AT49" s="9">
+      <c r="AT49" s="9"/>
+      <c r="AU49" s="9">
         <v>0.29270000000000002</v>
       </c>
     </row>
-    <row r="50" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:47" x14ac:dyDescent="0.2">
       <c r="A50">
         <f t="shared" si="1"/>
         <v>48</v>
@@ -9092,8 +9151,9 @@
       <c r="T50" s="4"/>
       <c r="U50" s="4"/>
       <c r="V50" s="4"/>
-    </row>
-    <row r="51" spans="1:46" x14ac:dyDescent="0.2">
+      <c r="W50" s="4"/>
+    </row>
+    <row r="51" spans="1:47" x14ac:dyDescent="0.2">
       <c r="A51">
         <f t="shared" si="1"/>
         <v>49</v>
@@ -9114,8 +9174,9 @@
       <c r="T51" s="4"/>
       <c r="U51" s="4"/>
       <c r="V51" s="4"/>
-    </row>
-    <row r="52" spans="1:46" x14ac:dyDescent="0.2">
+      <c r="W51" s="4"/>
+    </row>
+    <row r="52" spans="1:47" x14ac:dyDescent="0.2">
       <c r="A52">
         <f t="shared" si="1"/>
         <v>50</v>
@@ -9133,11 +9194,12 @@
       <c r="T52" s="4"/>
       <c r="U52" s="4"/>
       <c r="V52" s="4"/>
-      <c r="W52" s="6" t="s">
+      <c r="W52" s="4"/>
+      <c r="X52" s="6" t="s">
         <v>1326</v>
       </c>
     </row>
-    <row r="53" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:47" x14ac:dyDescent="0.2">
       <c r="A53">
         <f t="shared" si="1"/>
         <v>51</v>
@@ -9161,11 +9223,12 @@
       <c r="T53" s="4"/>
       <c r="U53" s="4"/>
       <c r="V53" s="4"/>
-      <c r="W53" s="6" t="s">
+      <c r="W53" s="4"/>
+      <c r="X53" s="6" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="54" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:47" x14ac:dyDescent="0.2">
       <c r="A54">
         <f t="shared" si="1"/>
         <v>52</v>
@@ -9192,14 +9255,15 @@
       <c r="T54" s="4"/>
       <c r="U54" s="4"/>
       <c r="V54" s="4"/>
-      <c r="W54" s="6" t="s">
+      <c r="W54" s="4"/>
+      <c r="X54" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="X54" s="6" t="s">
+      <c r="Y54" s="6" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="55" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:47" x14ac:dyDescent="0.2">
       <c r="A55">
         <f t="shared" si="1"/>
         <v>53</v>
@@ -9226,14 +9290,15 @@
       <c r="T55" s="4"/>
       <c r="U55" s="4"/>
       <c r="V55" s="4"/>
-      <c r="W55" s="6" t="s">
+      <c r="W55" s="4"/>
+      <c r="X55" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="X55" s="6" t="s">
+      <c r="Y55" s="6" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="56" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:47" x14ac:dyDescent="0.2">
       <c r="A56">
         <f t="shared" si="1"/>
         <v>54</v>
@@ -9263,14 +9328,15 @@
       <c r="T56" s="4"/>
       <c r="U56" s="4"/>
       <c r="V56" s="4"/>
-      <c r="W56" s="6" t="s">
+      <c r="W56" s="4"/>
+      <c r="X56" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="X56" s="6" t="s">
+      <c r="Y56" s="6" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="57" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:47" x14ac:dyDescent="0.2">
       <c r="A57">
         <f t="shared" si="1"/>
         <v>55</v>
@@ -9291,8 +9357,9 @@
       <c r="T57" s="4"/>
       <c r="U57" s="4"/>
       <c r="V57" s="4"/>
-    </row>
-    <row r="58" spans="1:46" x14ac:dyDescent="0.2">
+      <c r="W57" s="4"/>
+    </row>
+    <row r="58" spans="1:47" x14ac:dyDescent="0.2">
       <c r="A58">
         <f t="shared" si="1"/>
         <v>56</v>
@@ -9310,17 +9377,18 @@
       <c r="T58" s="4"/>
       <c r="U58" s="4"/>
       <c r="V58" s="4"/>
-      <c r="AI58" s="36">
+      <c r="W58" s="4"/>
+      <c r="AJ58" s="36">
         <v>0.17399999999999999</v>
       </c>
-      <c r="AS58" s="9">
+      <c r="AT58" s="9">
         <v>1.0174000000000001</v>
       </c>
-      <c r="AT58" s="9">
+      <c r="AU58" s="9">
         <v>0.53800000000000003</v>
       </c>
     </row>
-    <row r="59" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:47" x14ac:dyDescent="0.2">
       <c r="A59">
         <f t="shared" si="1"/>
         <v>57</v>
@@ -9347,11 +9415,12 @@
       <c r="T59" s="4"/>
       <c r="U59" s="4"/>
       <c r="V59" s="4"/>
-      <c r="W59" s="6" t="s">
+      <c r="W59" s="4"/>
+      <c r="X59" s="6" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="60" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:47" x14ac:dyDescent="0.2">
       <c r="A60">
         <f>+A63+1</f>
         <v>61</v>
@@ -9372,8 +9441,9 @@
       <c r="T60" s="4"/>
       <c r="U60" s="4"/>
       <c r="V60" s="4"/>
-    </row>
-    <row r="61" spans="1:46" x14ac:dyDescent="0.2">
+      <c r="W60" s="4"/>
+    </row>
+    <row r="61" spans="1:47" x14ac:dyDescent="0.2">
       <c r="A61">
         <f>+A59+1</f>
         <v>58</v>
@@ -9388,8 +9458,9 @@
       <c r="T61" s="4"/>
       <c r="U61" s="4"/>
       <c r="V61" s="4"/>
-    </row>
-    <row r="62" spans="1:46" x14ac:dyDescent="0.2">
+      <c r="W61" s="4"/>
+    </row>
+    <row r="62" spans="1:47" x14ac:dyDescent="0.2">
       <c r="A62">
         <f t="shared" si="1"/>
         <v>59</v>
@@ -9413,8 +9484,9 @@
       <c r="T62" s="4"/>
       <c r="U62" s="4"/>
       <c r="V62" s="4"/>
-    </row>
-    <row r="63" spans="1:46" x14ac:dyDescent="0.2">
+      <c r="W62" s="4"/>
+    </row>
+    <row r="63" spans="1:47" x14ac:dyDescent="0.2">
       <c r="A63">
         <f t="shared" si="1"/>
         <v>60</v>
@@ -9438,14 +9510,15 @@
       <c r="T63" s="4"/>
       <c r="U63" s="4"/>
       <c r="V63" s="4"/>
-      <c r="W63" s="6" t="s">
+      <c r="W63" s="4"/>
+      <c r="X63" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="X63" s="6" t="s">
+      <c r="Y63" s="6" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="64" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:47" x14ac:dyDescent="0.2">
       <c r="A64">
         <f>+A60+1</f>
         <v>62</v>
@@ -9472,29 +9545,30 @@
       <c r="T64" s="4"/>
       <c r="U64" s="4"/>
       <c r="V64" s="4"/>
-      <c r="W64" s="6" t="s">
+      <c r="W64" s="4"/>
+      <c r="X64" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="X64" s="6" t="s">
+      <c r="Y64" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="AI64" s="9">
+      <c r="AJ64" s="9">
         <v>0.26</v>
       </c>
-      <c r="AJ64" s="9">
+      <c r="AK64" s="9">
         <v>-0.26</v>
       </c>
-      <c r="AK64" s="9">
+      <c r="AL64" s="9">
         <v>-0.21</v>
       </c>
-      <c r="AQ64" s="9">
+      <c r="AR64" s="9">
         <v>0.51800000000000002</v>
       </c>
-      <c r="AR64" s="9">
+      <c r="AS64" s="9">
         <v>0.189</v>
       </c>
     </row>
-    <row r="65" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A65">
         <f t="shared" si="1"/>
         <v>63</v>
@@ -9515,8 +9589,9 @@
       <c r="T65" s="4"/>
       <c r="U65" s="4"/>
       <c r="V65" s="4"/>
-    </row>
-    <row r="66" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="W65" s="4"/>
+    </row>
+    <row r="66" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A66">
         <f t="shared" si="1"/>
         <v>64</v>
@@ -9540,11 +9615,12 @@
       <c r="T66" s="4"/>
       <c r="U66" s="4"/>
       <c r="V66" s="4"/>
-      <c r="W66" s="6" t="s">
+      <c r="W66" s="4"/>
+      <c r="X66" s="6" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="67" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A67">
         <f t="shared" si="1"/>
         <v>65</v>
@@ -9565,11 +9641,12 @@
       <c r="T67" s="4"/>
       <c r="U67" s="4"/>
       <c r="V67" s="4"/>
-      <c r="W67" s="6" t="s">
+      <c r="W67" s="4"/>
+      <c r="X67" s="6" t="s">
         <v>1305</v>
       </c>
     </row>
-    <row r="68" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A68">
         <f t="shared" si="1"/>
         <v>66</v>
@@ -9593,14 +9670,15 @@
       <c r="T68" s="4"/>
       <c r="U68" s="4"/>
       <c r="V68" s="4"/>
-      <c r="W68" s="6" t="s">
+      <c r="W68" s="4"/>
+      <c r="X68" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="AI68" s="36">
+      <c r="AJ68" s="36">
         <v>8.7999999999999995E-2</v>
       </c>
     </row>
-    <row r="69" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A69">
         <f t="shared" si="1"/>
         <v>67</v>
@@ -9615,8 +9693,9 @@
       <c r="T69" s="4"/>
       <c r="U69" s="4"/>
       <c r="V69" s="4"/>
-    </row>
-    <row r="70" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="W69" s="4"/>
+    </row>
+    <row r="70" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A70">
         <f t="shared" si="1"/>
         <v>68</v>
@@ -9629,8 +9708,9 @@
       <c r="T70" s="4"/>
       <c r="U70" s="4"/>
       <c r="V70" s="4"/>
-    </row>
-    <row r="71" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="W70" s="4"/>
+    </row>
+    <row r="71" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A71">
         <f t="shared" si="1"/>
         <v>69</v>
@@ -9646,8 +9726,9 @@
       <c r="T71" s="4"/>
       <c r="U71" s="4"/>
       <c r="V71" s="4"/>
-    </row>
-    <row r="72" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="W71" s="4"/>
+    </row>
+    <row r="72" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A72">
         <f t="shared" si="1"/>
         <v>70</v>
@@ -9668,11 +9749,12 @@
       <c r="T72" s="4"/>
       <c r="U72" s="4"/>
       <c r="V72" s="4"/>
-      <c r="W72" s="6" t="s">
+      <c r="W72" s="4"/>
+      <c r="X72" s="6" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="73" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A73">
         <f t="shared" si="1"/>
         <v>71</v>
@@ -9690,8 +9772,9 @@
       <c r="T73" s="4"/>
       <c r="U73" s="4"/>
       <c r="V73" s="4"/>
-    </row>
-    <row r="74" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="W73" s="4"/>
+    </row>
+    <row r="74" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A74">
         <f t="shared" si="1"/>
         <v>72</v>
@@ -9715,11 +9798,12 @@
       <c r="T74" s="4"/>
       <c r="U74" s="4"/>
       <c r="V74" s="4"/>
-      <c r="W74" s="6" t="s">
+      <c r="W74" s="4"/>
+      <c r="X74" s="6" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="75" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A75">
         <f t="shared" si="1"/>
         <v>73</v>
@@ -9743,8 +9827,9 @@
       <c r="T75" s="4"/>
       <c r="U75" s="4"/>
       <c r="V75" s="4"/>
-    </row>
-    <row r="76" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="W75" s="4"/>
+    </row>
+    <row r="76" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A76">
         <f t="shared" si="1"/>
         <v>74</v>
@@ -9768,11 +9853,12 @@
       <c r="T76" s="4"/>
       <c r="U76" s="4"/>
       <c r="V76" s="4"/>
-      <c r="W76" s="6" t="s">
+      <c r="W76" s="4"/>
+      <c r="X76" s="6" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="77" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A77">
         <f t="shared" si="1"/>
         <v>75</v>
@@ -9787,8 +9873,9 @@
       <c r="T77" s="4"/>
       <c r="U77" s="4"/>
       <c r="V77" s="4"/>
-    </row>
-    <row r="78" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="W77" s="4"/>
+    </row>
+    <row r="78" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A78">
         <f t="shared" si="1"/>
         <v>76</v>
@@ -9803,8 +9890,9 @@
       <c r="T78" s="4"/>
       <c r="U78" s="4"/>
       <c r="V78" s="4"/>
-    </row>
-    <row r="79" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="W78" s="4"/>
+    </row>
+    <row r="79" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A79">
         <f t="shared" si="1"/>
         <v>77</v>
@@ -9822,11 +9910,12 @@
       <c r="T79" s="4"/>
       <c r="U79" s="4"/>
       <c r="V79" s="4"/>
-      <c r="Z79">
+      <c r="W79" s="4"/>
+      <c r="AA79">
         <v>2011</v>
       </c>
     </row>
-    <row r="80" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A80">
         <f t="shared" si="1"/>
         <v>78</v>
@@ -9851,20 +9940,21 @@
       <c r="T80" s="4"/>
       <c r="U80" s="4"/>
       <c r="V80" s="4"/>
-      <c r="W80" s="6" t="s">
+      <c r="W80" s="4"/>
+      <c r="X80" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="X80" s="6" t="s">
+      <c r="Y80" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="AQ80" s="9">
+      <c r="AR80" s="9">
         <v>-0.2</v>
       </c>
-      <c r="AX80" s="9">
+      <c r="AY80" s="9">
         <v>-0.23</v>
       </c>
     </row>
-    <row r="81" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A81">
         <f t="shared" si="1"/>
         <v>79</v>
@@ -9885,11 +9975,12 @@
       <c r="T81" s="4"/>
       <c r="U81" s="4"/>
       <c r="V81" s="4"/>
-      <c r="W81" s="6" t="s">
+      <c r="W81" s="4"/>
+      <c r="X81" s="6" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="82" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A82">
         <f t="shared" si="1"/>
         <v>80</v>
@@ -9904,8 +9995,9 @@
       <c r="T82" s="4"/>
       <c r="U82" s="4"/>
       <c r="V82" s="4"/>
-    </row>
-    <row r="83" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="W82" s="4"/>
+    </row>
+    <row r="83" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A83">
         <f t="shared" si="1"/>
         <v>81</v>
@@ -9920,8 +10012,9 @@
       <c r="T83" s="4"/>
       <c r="U83" s="4"/>
       <c r="V83" s="4"/>
-    </row>
-    <row r="84" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="W83" s="4"/>
+    </row>
+    <row r="84" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A84">
         <f t="shared" si="1"/>
         <v>82</v>
@@ -9942,8 +10035,9 @@
       <c r="T84" s="4"/>
       <c r="U84" s="4"/>
       <c r="V84" s="4"/>
-    </row>
-    <row r="85" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="W84" s="4"/>
+    </row>
+    <row r="85" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A85">
         <f t="shared" ref="A85:A120" si="2">+A84+1</f>
         <v>83</v>
@@ -9964,8 +10058,9 @@
       <c r="T85" s="4"/>
       <c r="U85" s="4"/>
       <c r="V85" s="4"/>
-    </row>
-    <row r="86" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="W85" s="4"/>
+    </row>
+    <row r="86" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A86">
         <f t="shared" si="2"/>
         <v>84</v>
@@ -9989,11 +10084,12 @@
       <c r="T86" s="4"/>
       <c r="U86" s="4"/>
       <c r="V86" s="4"/>
-      <c r="W86" s="6" t="s">
+      <c r="W86" s="4"/>
+      <c r="X86" s="6" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="87" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A87">
         <f t="shared" si="2"/>
         <v>85</v>
@@ -10014,11 +10110,12 @@
       <c r="T87" s="4"/>
       <c r="U87" s="4"/>
       <c r="V87" s="4"/>
-      <c r="Y87" s="8" t="s">
+      <c r="W87" s="4"/>
+      <c r="Z87" s="8" t="s">
         <v>671</v>
       </c>
     </row>
-    <row r="88" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A88">
         <f t="shared" si="2"/>
         <v>86</v>
@@ -10045,14 +10142,15 @@
       <c r="T88" s="4"/>
       <c r="U88" s="4"/>
       <c r="V88" s="4"/>
-      <c r="W88" s="6" t="s">
+      <c r="W88" s="4"/>
+      <c r="X88" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="X88" s="6" t="s">
+      <c r="Y88" s="6" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="89" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A89">
         <f t="shared" si="2"/>
         <v>87</v>
@@ -10076,11 +10174,12 @@
       <c r="T89" s="4"/>
       <c r="U89" s="4"/>
       <c r="V89" s="4"/>
-      <c r="W89" s="6" t="s">
+      <c r="W89" s="4"/>
+      <c r="X89" s="6" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="90" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A90">
         <f t="shared" si="2"/>
         <v>88</v>
@@ -10095,8 +10194,9 @@
       <c r="T90" s="4"/>
       <c r="U90" s="4"/>
       <c r="V90" s="4"/>
-    </row>
-    <row r="91" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="W90" s="4"/>
+    </row>
+    <row r="91" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A91">
         <f t="shared" si="2"/>
         <v>89</v>
@@ -10120,11 +10220,12 @@
       <c r="T91" s="4"/>
       <c r="U91" s="4"/>
       <c r="V91" s="4"/>
-      <c r="W91" s="6" t="s">
+      <c r="W91" s="4"/>
+      <c r="X91" s="6" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="92" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A92">
         <f t="shared" si="2"/>
         <v>90</v>
@@ -10145,8 +10246,9 @@
       <c r="T92" s="4"/>
       <c r="U92" s="4"/>
       <c r="V92" s="4"/>
-    </row>
-    <row r="93" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="W92" s="4"/>
+    </row>
+    <row r="93" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A93">
         <f t="shared" si="2"/>
         <v>91</v>
@@ -10161,8 +10263,9 @@
       <c r="T93" s="4"/>
       <c r="U93" s="4"/>
       <c r="V93" s="4"/>
-    </row>
-    <row r="94" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="W93" s="4"/>
+    </row>
+    <row r="94" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A94">
         <f t="shared" si="2"/>
         <v>92</v>
@@ -10180,17 +10283,18 @@
       <c r="T94" s="4"/>
       <c r="U94" s="4"/>
       <c r="V94" s="4"/>
-      <c r="AH94" s="9">
+      <c r="W94" s="4"/>
+      <c r="AI94" s="9">
         <v>0.52</v>
       </c>
-      <c r="AI94" s="9">
+      <c r="AJ94" s="9">
         <v>0.48</v>
       </c>
-      <c r="AX94" s="36">
+      <c r="AY94" s="36">
         <v>-0.33300000000000002</v>
       </c>
     </row>
-    <row r="95" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A95">
         <f t="shared" si="2"/>
         <v>93</v>
@@ -10214,11 +10318,12 @@
       <c r="T95" s="4"/>
       <c r="U95" s="4"/>
       <c r="V95" s="4"/>
-      <c r="W95" s="6" t="s">
+      <c r="W95" s="4"/>
+      <c r="X95" s="6" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="96" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A96">
         <f t="shared" si="2"/>
         <v>94</v>
@@ -10233,8 +10338,9 @@
       <c r="T96" s="4"/>
       <c r="U96" s="4"/>
       <c r="V96" s="4"/>
-    </row>
-    <row r="97" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="W96" s="4"/>
+    </row>
+    <row r="97" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A97">
         <f t="shared" si="2"/>
         <v>95</v>
@@ -10255,8 +10361,9 @@
       <c r="T97" s="4"/>
       <c r="U97" s="4"/>
       <c r="V97" s="4"/>
-    </row>
-    <row r="98" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="W97" s="4"/>
+    </row>
+    <row r="98" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A98">
         <f t="shared" si="2"/>
         <v>96</v>
@@ -10280,11 +10387,12 @@
       <c r="V98" s="4">
         <v>578.33704</v>
       </c>
-      <c r="W98" s="6" t="s">
+      <c r="W98" s="4"/>
+      <c r="X98" s="6" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="99" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A99">
         <f t="shared" si="2"/>
         <v>97</v>
@@ -10301,8 +10409,9 @@
       <c r="T99" s="4"/>
       <c r="U99" s="4"/>
       <c r="V99" s="4"/>
-    </row>
-    <row r="100" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="W99" s="4"/>
+    </row>
+    <row r="100" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A100">
         <f t="shared" si="2"/>
         <v>98</v>
@@ -10319,11 +10428,12 @@
       <c r="T100" s="4"/>
       <c r="U100" s="4"/>
       <c r="V100" s="4"/>
-      <c r="W100" s="6" t="s">
+      <c r="W100" s="4"/>
+      <c r="X100" s="6" t="s">
         <v>663</v>
       </c>
     </row>
-    <row r="101" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A101">
         <f t="shared" si="2"/>
         <v>99</v>
@@ -10346,17 +10456,18 @@
       <c r="T101" s="4"/>
       <c r="U101" s="4"/>
       <c r="V101" s="4"/>
-      <c r="W101" s="6" t="s">
+      <c r="W101" s="4"/>
+      <c r="X101" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="X101" s="6" t="s">
+      <c r="Y101" s="6" t="s">
         <v>220</v>
       </c>
-      <c r="Y101" s="8" t="s">
+      <c r="Z101" s="8" t="s">
         <v>654</v>
       </c>
     </row>
-    <row r="102" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A102">
         <f t="shared" si="2"/>
         <v>100</v>
@@ -10373,8 +10484,9 @@
       <c r="T102" s="4"/>
       <c r="U102" s="4"/>
       <c r="V102" s="4"/>
-    </row>
-    <row r="103" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="W102" s="4"/>
+    </row>
+    <row r="103" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A103">
         <f t="shared" si="2"/>
         <v>101</v>
@@ -10382,11 +10494,11 @@
       <c r="B103" t="s">
         <v>61</v>
       </c>
-      <c r="W103" s="6" t="s">
+      <c r="X103" s="6" t="s">
         <v>657</v>
       </c>
     </row>
-    <row r="104" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A104">
         <f t="shared" si="2"/>
         <v>102</v>
@@ -10395,7 +10507,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="105" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A105">
         <f t="shared" si="2"/>
         <v>103</v>
@@ -10404,7 +10516,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="106" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A106">
         <f t="shared" si="2"/>
         <v>104</v>
@@ -10413,7 +10525,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="107" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A107">
         <f t="shared" si="2"/>
         <v>105</v>
@@ -10425,7 +10537,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="108" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A108">
         <f t="shared" si="2"/>
         <v>106</v>
@@ -10434,7 +10546,7 @@
         <v>1327</v>
       </c>
     </row>
-    <row r="109" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A109">
         <f>+A107+1</f>
         <v>106</v>
@@ -10443,7 +10555,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="110" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A110">
         <f t="shared" si="2"/>
         <v>107</v>
@@ -10452,7 +10564,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="111" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A111">
         <f t="shared" si="2"/>
         <v>108</v>
@@ -10461,7 +10573,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="112" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A112">
         <f t="shared" si="2"/>
         <v>109</v>
@@ -11196,7 +11308,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="193" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A193">
         <f t="shared" si="4"/>
         <v>189</v>
@@ -11205,7 +11317,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="194" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A194">
         <f t="shared" si="4"/>
         <v>190</v>
@@ -11214,7 +11326,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="195" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A195">
         <f t="shared" si="4"/>
         <v>191</v>
@@ -11223,7 +11335,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="196" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A196">
         <f t="shared" si="4"/>
         <v>192</v>
@@ -11232,7 +11344,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="197" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A197">
         <f t="shared" si="4"/>
         <v>193</v>
@@ -11244,7 +11356,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="198" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A198">
         <f t="shared" si="4"/>
         <v>194</v>
@@ -11253,7 +11365,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="199" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A199">
         <f t="shared" si="4"/>
         <v>195</v>
@@ -11262,7 +11374,7 @@
         <v>1123</v>
       </c>
     </row>
-    <row r="200" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A200">
         <f t="shared" si="4"/>
         <v>196</v>
@@ -11271,7 +11383,7 @@
         <v>1124</v>
       </c>
     </row>
-    <row r="201" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A201">
         <f t="shared" si="4"/>
         <v>197</v>
@@ -11280,7 +11392,7 @@
         <v>1321</v>
       </c>
     </row>
-    <row r="202" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A202">
         <f t="shared" si="4"/>
         <v>198</v>
@@ -11289,7 +11401,7 @@
         <v>1209</v>
       </c>
     </row>
-    <row r="203" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A203">
         <f t="shared" si="4"/>
         <v>199</v>
@@ -11298,7 +11410,7 @@
         <v>1490</v>
       </c>
     </row>
-    <row r="206" spans="1:25" s="22" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:26" s="22" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B206" s="22" t="s">
         <v>1211</v>
       </c>
@@ -11321,11 +11433,12 @@
       <c r="T206" s="23"/>
       <c r="U206" s="23"/>
       <c r="V206" s="23"/>
-      <c r="W206" s="25"/>
+      <c r="W206" s="23"/>
       <c r="X206" s="25"/>
-      <c r="Y206" s="26"/>
-    </row>
-    <row r="207" spans="1:25" s="22" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="Y206" s="25"/>
+      <c r="Z206" s="26"/>
+    </row>
+    <row r="207" spans="1:26" s="22" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B207" s="22" t="s">
         <v>62</v>
       </c>
@@ -11348,13 +11461,14 @@
       <c r="T207" s="23"/>
       <c r="U207" s="23"/>
       <c r="V207" s="23"/>
-      <c r="W207" s="25" t="s">
+      <c r="W207" s="23"/>
+      <c r="X207" s="25" t="s">
         <v>654</v>
       </c>
-      <c r="X207" s="25"/>
-      <c r="Y207" s="26"/>
-    </row>
-    <row r="208" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Y207" s="25"/>
+      <c r="Z207" s="26"/>
+    </row>
+    <row r="208" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B208" s="22" t="s">
         <v>1269</v>
       </c>
@@ -12109,10 +12223,13 @@
     <hyperlink ref="V29" r:id="rId573" display="https://www.sec.gov/Archives/edgar/data/1784547/000117266125003349/0001172661-25-003349-index.htm" xr:uid="{C5D6AC9F-4D6D-4B70-9787-FB5EBA411E32}"/>
     <hyperlink ref="V30" r:id="rId574" display="https://www.sec.gov/Archives/edgar/data/1336528/000117266125003509/0001172661-25-003509-index.htm" xr:uid="{9D083965-04E7-4AC8-8C03-EB9584CFCB5F}"/>
     <hyperlink ref="V31" r:id="rId575" display="https://www.sec.gov/Archives/edgar/data/1791786/000101359425001045/0001013594-25-001045-index.htm" xr:uid="{866D7355-5ECD-4A13-BD27-DA60870A0352}"/>
+    <hyperlink ref="W3" r:id="rId576" display="https://www.sec.gov/Archives/edgar/data/1067983/000119312525282901/0001193125-25-282901-index.htm" xr:uid="{290783D6-41CD-4CF5-99DA-00FFD7CF7A3E}"/>
+    <hyperlink ref="W4" r:id="rId577" display="https://www.sec.gov/Archives/edgar/data/1273087/000127308725000034/0001273087-25-000034-index.htm" xr:uid="{DC39D9C4-C0B9-40A2-B7B7-BD1D94B78BD1}"/>
+    <hyperlink ref="W5" r:id="rId578" display="https://www.sec.gov/Archives/edgar/data/1423053/000110465925112514/0001104659-25-112514-index.htm" xr:uid="{99277AF0-0DA5-4378-8784-28C399D83469}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId576"/>
-  <legacyDrawing r:id="rId577"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId579"/>
+  <legacyDrawing r:id="rId580"/>
 </worksheet>
 </file>
 

--- a/Hedge Funds (1).xlsx
+++ b/Hedge Funds (1).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6CB3134-4AE9-4413-B989-4F8624FE5C60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{552203E9-0CAA-44ED-94A8-CC10B5CC73F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="3855" windowWidth="38175" windowHeight="15240" xr2:uid="{18689D26-F1F3-46B4-82BE-041D095397EB}"/>
+    <workbookView xWindow="225" yWindow="390" windowWidth="38175" windowHeight="15240" xr2:uid="{18689D26-F1F3-46B4-82BE-041D095397EB}"/>
   </bookViews>
   <sheets>
     <sheet name="Hedge" sheetId="1" r:id="rId1"/>
@@ -166,7 +166,7 @@
     210.9B with puts/calls</t>
       </text>
     </comment>
-    <comment ref="Y4" authorId="6" shapeId="0" xr:uid="{C458FA31-CB9B-459E-B4D3-6F93CD9B9108}">
+    <comment ref="Z4" authorId="6" shapeId="0" xr:uid="{C458FA31-CB9B-459E-B4D3-6F93CD9B9108}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -393,7 +393,7 @@
 All Weather 12%</t>
       </text>
     </comment>
-    <comment ref="AE22" authorId="34" shapeId="0" xr:uid="{571E6B33-9F0B-402B-B6AF-3026724B96B6}">
+    <comment ref="AF22" authorId="34" shapeId="0" xr:uid="{571E6B33-9F0B-402B-B6AF-3026724B96B6}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -402,7 +402,7 @@
 Pure alpha 1991</t>
       </text>
     </comment>
-    <comment ref="AN22" authorId="35" shapeId="0" xr:uid="{65A0F6CF-356C-4A90-96D2-FFE35AFE2E62}">
+    <comment ref="AO22" authorId="35" shapeId="0" xr:uid="{65A0F6CF-356C-4A90-96D2-FFE35AFE2E62}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -410,7 +410,7 @@
     All Weather +16%</t>
       </text>
     </comment>
-    <comment ref="AO22" authorId="36" shapeId="0" xr:uid="{267E6B37-EE49-4656-A61F-E5E2C45BA32F}">
+    <comment ref="AP22" authorId="36" shapeId="0" xr:uid="{267E6B37-EE49-4656-A61F-E5E2C45BA32F}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -474,7 +474,7 @@
     Also notes 35.5B</t>
       </text>
     </comment>
-    <comment ref="AK28" authorId="44" shapeId="0" xr:uid="{5F7F3924-A5F8-4D80-90C0-CA8CC6527A95}">
+    <comment ref="AL28" authorId="44" shapeId="0" xr:uid="{5F7F3924-A5F8-4D80-90C0-CA8CC6527A95}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -627,7 +627,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2261" uniqueCount="1569">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2274" uniqueCount="1582">
   <si>
     <t>Name</t>
   </si>
@@ -5334,6 +5334,45 @@
   </si>
   <si>
     <t>Q325</t>
+  </si>
+  <si>
+    <t>Q425</t>
+  </si>
+  <si>
+    <t>Oaktree</t>
+  </si>
+  <si>
+    <t>Howard Marks</t>
+  </si>
+  <si>
+    <t>Paulson &amp; Co</t>
+  </si>
+  <si>
+    <t>Ican Enterprise</t>
+  </si>
+  <si>
+    <t>Starboard Value</t>
+  </si>
+  <si>
+    <t>Coverex</t>
+  </si>
+  <si>
+    <t>John Paulson</t>
+  </si>
+  <si>
+    <t>Carl Ican</t>
+  </si>
+  <si>
+    <t>Trian Partners</t>
+  </si>
+  <si>
+    <t>Nelson Peltz</t>
+  </si>
+  <si>
+    <t>Jefferey Smith</t>
+  </si>
+  <si>
+    <t>Keith Meister</t>
   </si>
 </sst>
 </file>
@@ -5902,7 +5941,7 @@
   <threadedComment ref="S4" dT="2025-01-11T20:11:02.62" personId="{4F866D09-A2D3-41DA-A24C-20DE51662D93}" id="{B533632F-6233-41C2-A96C-9A84235E21C6}">
     <text>210.9B with puts/calls</text>
   </threadedComment>
-  <threadedComment ref="Y4" dT="2025-04-05T10:22:31.39" personId="{C4A9F9C5-0550-4D3E-A9C0-F2F2E5238B0D}" id="{C458FA31-CB9B-459E-B4D3-6F93CD9B9108}">
+  <threadedComment ref="Z4" dT="2025-04-05T10:22:31.39" personId="{C4A9F9C5-0550-4D3E-A9C0-F2F2E5238B0D}" id="{C458FA31-CB9B-459E-B4D3-6F93CD9B9108}">
     <text xml:space="preserve">Pod shop = multi strategy </text>
   </threadedComment>
   <threadedComment ref="P5" dT="2024-03-24T23:23:21.67" personId="{4F866D09-A2D3-41DA-A24C-20DE51662D93}" id="{4762A1A1-5314-4304-962C-F1489B64BA4B}">
@@ -5989,14 +6028,14 @@
 Pure Alpha 18%
 All Weather 12%</text>
   </threadedComment>
-  <threadedComment ref="AE22" dT="2024-11-11T21:29:45.05" personId="{4F866D09-A2D3-41DA-A24C-20DE51662D93}" id="{571E6B33-9F0B-402B-B6AF-3026724B96B6}">
+  <threadedComment ref="AF22" dT="2024-11-11T21:29:45.05" personId="{4F866D09-A2D3-41DA-A24C-20DE51662D93}" id="{571E6B33-9F0B-402B-B6AF-3026724B96B6}">
     <text>All weather opened 1996
 Pure alpha 1991</text>
   </threadedComment>
-  <threadedComment ref="AN22" dT="2024-11-11T21:44:28.32" personId="{4F866D09-A2D3-41DA-A24C-20DE51662D93}" id="{65A0F6CF-356C-4A90-96D2-FFE35AFE2E62}">
+  <threadedComment ref="AO22" dT="2024-11-11T21:44:28.32" personId="{4F866D09-A2D3-41DA-A24C-20DE51662D93}" id="{65A0F6CF-356C-4A90-96D2-FFE35AFE2E62}">
     <text>All Weather +16%</text>
   </threadedComment>
-  <threadedComment ref="AO22" dT="2024-11-11T21:45:06.55" personId="{4F866D09-A2D3-41DA-A24C-20DE51662D93}" id="{267E6B37-EE49-4656-A61F-E5E2C45BA32F}">
+  <threadedComment ref="AP22" dT="2024-11-11T21:45:06.55" personId="{4F866D09-A2D3-41DA-A24C-20DE51662D93}" id="{267E6B37-EE49-4656-A61F-E5E2C45BA32F}">
     <text>All Weather -5.1%</text>
   </threadedComment>
   <threadedComment ref="C23" dT="2025-04-08T16:50:08.35" personId="{C4A9F9C5-0550-4D3E-A9C0-F2F2E5238B0D}" id="{3C8A7604-D0B1-4BD2-8EB5-1FC90AAA41A6}">
@@ -6020,7 +6059,7 @@
   <threadedComment ref="D28" dT="2023-01-28T20:34:58.21" personId="{4F866D09-A2D3-41DA-A24C-20DE51662D93}" id="{9F5197FC-413A-4526-8395-DB7D8217FC78}">
     <text>Also notes 35.5B</text>
   </threadedComment>
-  <threadedComment ref="AK28" dT="2023-01-28T20:41:18.37" personId="{4F866D09-A2D3-41DA-A24C-20DE51662D93}" id="{5F7F3924-A5F8-4D80-90C0-CA8CC6527A95}">
+  <threadedComment ref="AL28" dT="2023-01-28T20:41:18.37" personId="{4F866D09-A2D3-41DA-A24C-20DE51662D93}" id="{5F7F3924-A5F8-4D80-90C0-CA8CC6527A95}">
     <text>https://www.bloomberg.com/news/articles/2022-08-26/lone-pine-assets-shrivel-as-hedge-fund-reels-from-record-losses?leadSource=uverify%20wall</text>
     <extLst>
       <x:ext xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
@@ -6098,7 +6137,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E8001A6-1B33-4EEE-B2A7-E66E0A0975B5}">
-  <dimension ref="A1:BR242"/>
+  <dimension ref="A1:BS248"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.140625" bestFit="1" customWidth="1"/>
@@ -6109,20 +6148,20 @@
     <col min="9" max="14" width="9.28515625" style="3"/>
     <col min="15" max="15" width="8.7109375" style="3"/>
     <col min="16" max="16" width="9.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="17" max="23" width="9.28515625" style="3" customWidth="1"/>
-    <col min="24" max="24" width="12" style="6" customWidth="1"/>
-    <col min="25" max="25" width="10.5703125" style="6" customWidth="1"/>
-    <col min="26" max="26" width="12" style="8" customWidth="1"/>
-    <col min="28" max="29" width="10.7109375" customWidth="1"/>
+    <col min="17" max="24" width="9.28515625" style="3" customWidth="1"/>
+    <col min="25" max="25" width="12" style="6" customWidth="1"/>
+    <col min="26" max="26" width="10.5703125" style="6" customWidth="1"/>
+    <col min="27" max="27" width="12" style="8" customWidth="1"/>
+    <col min="29" max="30" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:70" x14ac:dyDescent="0.2">
-      <c r="AC1">
-        <f>SUM(AC3:AC276)</f>
+    <row r="1" spans="1:71" x14ac:dyDescent="0.2">
+      <c r="AD1">
+        <f>SUM(AD3:AD282)</f>
         <v>30724</v>
       </c>
     </row>
-    <row r="2" spans="1:70" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:71" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -6189,159 +6228,162 @@
       <c r="W2" s="3" t="s">
         <v>1568</v>
       </c>
-      <c r="X2" s="5" t="s">
+      <c r="X2" s="3" t="s">
+        <v>1569</v>
+      </c>
+      <c r="Y2" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="Y2" s="5" t="s">
+      <c r="Z2" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="Z2" s="7" t="s">
+      <c r="AA2" s="7" t="s">
         <v>214</v>
       </c>
-      <c r="AA2" t="s">
+      <c r="AB2" t="s">
         <v>225</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="AC2" t="s">
         <v>226</v>
       </c>
-      <c r="AC2" t="s">
+      <c r="AD2" t="s">
         <v>723</v>
       </c>
-      <c r="AD2" t="s">
+      <c r="AE2" t="s">
         <v>229</v>
       </c>
-      <c r="AE2" t="s">
+      <c r="AF2" t="s">
         <v>228</v>
       </c>
-      <c r="AF2" t="s">
+      <c r="AG2" t="s">
         <v>714</v>
       </c>
-      <c r="AG2" t="s">
+      <c r="AH2" t="s">
         <v>715</v>
       </c>
-      <c r="AH2" t="s">
+      <c r="AI2" t="s">
         <v>713</v>
       </c>
-      <c r="AI2">
+      <c r="AJ2">
         <v>2024</v>
       </c>
-      <c r="AJ2">
+      <c r="AK2">
         <v>2023</v>
       </c>
-      <c r="AK2">
+      <c r="AL2">
         <v>2022</v>
       </c>
-      <c r="AL2">
+      <c r="AM2">
         <v>2021</v>
       </c>
-      <c r="AM2">
+      <c r="AN2">
         <v>2020</v>
       </c>
-      <c r="AN2">
+      <c r="AO2">
         <v>2019</v>
       </c>
-      <c r="AO2">
+      <c r="AP2">
         <v>2018</v>
       </c>
-      <c r="AP2">
+      <c r="AQ2">
         <v>2017</v>
       </c>
-      <c r="AQ2">
+      <c r="AR2">
         <v>2016</v>
       </c>
-      <c r="AR2">
+      <c r="AS2">
         <v>2015</v>
       </c>
-      <c r="AS2">
+      <c r="AT2">
         <v>2014</v>
       </c>
-      <c r="AT2">
+      <c r="AU2">
         <v>2013</v>
       </c>
-      <c r="AU2">
+      <c r="AV2">
         <v>2012</v>
       </c>
-      <c r="AV2">
+      <c r="AW2">
         <v>2011</v>
       </c>
-      <c r="AW2">
-        <f>+AV2-1</f>
+      <c r="AX2">
+        <f>+AW2-1</f>
         <v>2010</v>
       </c>
-      <c r="AX2">
-        <f t="shared" ref="AX2:BL2" si="0">+AW2-1</f>
+      <c r="AY2">
+        <f t="shared" ref="AY2:BM2" si="0">+AX2-1</f>
         <v>2009</v>
       </c>
-      <c r="AY2">
+      <c r="AZ2">
         <f t="shared" si="0"/>
         <v>2008</v>
       </c>
-      <c r="AZ2">
+      <c r="BA2">
         <f t="shared" si="0"/>
         <v>2007</v>
       </c>
-      <c r="BA2">
+      <c r="BB2">
         <f t="shared" si="0"/>
         <v>2006</v>
       </c>
-      <c r="BB2">
+      <c r="BC2">
         <f t="shared" si="0"/>
         <v>2005</v>
       </c>
-      <c r="BC2">
+      <c r="BD2">
         <f t="shared" si="0"/>
         <v>2004</v>
       </c>
-      <c r="BD2">
+      <c r="BE2">
         <f t="shared" si="0"/>
         <v>2003</v>
       </c>
-      <c r="BE2">
+      <c r="BF2">
         <f t="shared" si="0"/>
         <v>2002</v>
       </c>
-      <c r="BF2">
+      <c r="BG2">
         <f t="shared" si="0"/>
         <v>2001</v>
       </c>
-      <c r="BG2">
+      <c r="BH2">
         <f t="shared" si="0"/>
         <v>2000</v>
       </c>
-      <c r="BH2">
+      <c r="BI2">
         <f t="shared" si="0"/>
         <v>1999</v>
       </c>
-      <c r="BI2">
+      <c r="BJ2">
         <f t="shared" si="0"/>
         <v>1998</v>
       </c>
-      <c r="BJ2">
+      <c r="BK2">
         <f t="shared" si="0"/>
         <v>1997</v>
       </c>
-      <c r="BK2">
+      <c r="BL2">
         <f t="shared" si="0"/>
         <v>1996</v>
       </c>
-      <c r="BL2">
+      <c r="BM2">
         <f t="shared" si="0"/>
         <v>1995</v>
       </c>
-      <c r="BM2">
+      <c r="BN2">
         <v>1994</v>
       </c>
-      <c r="BN2">
+      <c r="BO2">
         <v>1993</v>
       </c>
-      <c r="BO2">
+      <c r="BP2">
         <v>1992</v>
       </c>
-      <c r="BP2">
+      <c r="BQ2">
         <v>1991</v>
       </c>
     </row>
-    <row r="3" spans="1:70" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1</v>
       </c>
@@ -6393,20 +6435,23 @@
       <c r="W3" s="4">
         <v>267334.50195499999</v>
       </c>
-      <c r="X3" s="6" t="s">
+      <c r="X3" s="4">
+        <v>274160.08670099999</v>
+      </c>
+      <c r="Y3" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="Y3" s="6" t="s">
+      <c r="Z3" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="Z3" s="8" t="s">
+      <c r="AA3" s="8" t="s">
         <v>217</v>
       </c>
-      <c r="AA3">
+      <c r="AB3">
         <v>1965</v>
       </c>
     </row>
-    <row r="4" spans="1:70" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A4">
         <f>+A3+1</f>
         <v>2</v>
@@ -6465,87 +6510,90 @@
       <c r="W4" s="4">
         <v>234292.490467</v>
       </c>
-      <c r="X4" s="6" t="s">
+      <c r="X4" s="4">
+        <v>237791.01562200001</v>
+      </c>
+      <c r="Y4" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="Y4" s="6" t="s">
+      <c r="Z4" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="Z4" s="8" t="s">
+      <c r="AA4" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="AA4">
+      <c r="AB4">
         <v>1989</v>
       </c>
-      <c r="AC4">
+      <c r="AD4">
         <v>5500</v>
       </c>
-      <c r="AF4" t="s">
+      <c r="AG4" t="s">
         <v>722</v>
       </c>
-      <c r="AI4" s="9">
+      <c r="AJ4" s="9">
         <v>0.15</v>
       </c>
-      <c r="AJ4" s="9">
+      <c r="AK4" s="9">
         <v>0.1</v>
       </c>
-      <c r="AK4" s="9">
+      <c r="AL4" s="9">
         <v>0.12</v>
       </c>
-      <c r="AL4" s="9">
+      <c r="AM4" s="9">
         <v>0.1361</v>
       </c>
-      <c r="AM4" s="9">
+      <c r="AN4" s="9">
         <v>0.25800000000000001</v>
       </c>
-      <c r="AN4" s="9">
+      <c r="AO4" s="9">
         <v>9.8000000000000004E-2</v>
       </c>
-      <c r="AO4" s="9">
+      <c r="AP4" s="9">
         <v>4.9000000000000002E-2</v>
       </c>
-      <c r="AP4" s="9">
+      <c r="AQ4" s="9">
         <v>7.1199999999999999E-2</v>
       </c>
-      <c r="AQ4" s="9">
+      <c r="AR4" s="9">
         <v>3.3799999999999997E-2</v>
       </c>
-      <c r="AR4" s="9">
+      <c r="AS4" s="9">
         <v>0.12540000000000001</v>
       </c>
-      <c r="AS4" s="9">
+      <c r="AT4" s="9">
         <v>0.12089999999999999</v>
       </c>
-      <c r="AT4" s="9">
+      <c r="AU4" s="9">
         <v>0.13270000000000001</v>
       </c>
-      <c r="AU4" s="9">
+      <c r="AV4" s="9">
         <v>6.3200000000000006E-2</v>
       </c>
-      <c r="AV4" s="9">
+      <c r="AW4" s="9">
         <v>8.3900000000000002E-2</v>
       </c>
-      <c r="AW4" s="9">
+      <c r="AX4" s="9">
         <v>0.13400000000000001</v>
       </c>
-      <c r="AX4" s="9">
+      <c r="AY4" s="9">
         <v>0.17199999999999999</v>
       </c>
-      <c r="AY4" s="9">
+      <c r="AZ4" s="9">
         <v>-0.03</v>
       </c>
-      <c r="AZ4" s="9"/>
-      <c r="BA4" s="9">
+      <c r="BA4" s="9"/>
+      <c r="BB4" s="9">
         <v>0.17</v>
       </c>
-      <c r="BB4" s="9">
+      <c r="BC4" s="9">
         <v>0.08</v>
       </c>
-      <c r="BC4" s="9">
+      <c r="BD4" s="9">
         <v>0.35</v>
       </c>
     </row>
-    <row r="5" spans="1:70" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A5">
         <f t="shared" ref="A5:A84" si="1">+A4+1</f>
         <v>3</v>
@@ -6604,101 +6652,104 @@
       <c r="W5" s="4">
         <v>657149.09227400005</v>
       </c>
-      <c r="X5" s="6" t="s">
+      <c r="X5" s="4">
+        <v>665872.16804500006</v>
+      </c>
+      <c r="Y5" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="Y5" s="6" t="s">
+      <c r="Z5" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="Z5" s="8" t="s">
+      <c r="AA5" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="AA5">
+      <c r="AB5">
         <v>1990</v>
       </c>
-      <c r="AB5" t="s">
+      <c r="AC5" t="s">
         <v>235</v>
       </c>
-      <c r="AC5">
+      <c r="AD5">
         <v>2932</v>
       </c>
-      <c r="AI5" s="9">
+      <c r="AJ5" s="9">
         <v>0.15</v>
       </c>
-      <c r="AJ5" s="9">
+      <c r="AK5" s="9">
         <v>0.153</v>
       </c>
-      <c r="AK5" s="9">
+      <c r="AL5" s="9">
         <v>0.38</v>
       </c>
-      <c r="AL5" s="9">
+      <c r="AM5" s="9">
         <v>0.26</v>
       </c>
-      <c r="AM5" s="9">
+      <c r="AN5" s="9">
         <v>0.24399999999999999</v>
       </c>
-      <c r="AN5" s="9">
+      <c r="AO5" s="9">
         <v>0.19400000000000001</v>
       </c>
-      <c r="AO5" s="9">
+      <c r="AP5" s="9">
         <v>9.0999999999999998E-2</v>
       </c>
-      <c r="AP5" s="9">
+      <c r="AQ5" s="9">
         <v>0.13100000000000001</v>
       </c>
-      <c r="AQ5" s="9">
+      <c r="AR5" s="9">
         <v>5.0999999999999997E-2</v>
       </c>
-      <c r="AR5" s="9">
+      <c r="AS5" s="9">
         <v>0.14299999999999999</v>
       </c>
-      <c r="AS5" s="9">
+      <c r="AT5" s="9">
         <v>0.17899999999999999</v>
       </c>
-      <c r="AT5" s="9">
+      <c r="AU5" s="9">
         <v>0.19400000000000001</v>
       </c>
-      <c r="AU5" s="9">
+      <c r="AV5" s="9">
         <v>0.25900000000000001</v>
       </c>
-      <c r="AV5" s="9">
+      <c r="AW5" s="9">
         <v>0.2</v>
       </c>
-      <c r="AW5" s="9">
+      <c r="AX5" s="9">
         <v>0.1</v>
       </c>
-      <c r="AX5" s="9">
+      <c r="AY5" s="9">
         <v>0.62</v>
       </c>
-      <c r="AY5" s="9">
+      <c r="AZ5" s="9">
         <v>-0.55000000000000004</v>
-      </c>
-      <c r="AZ5" s="9">
-        <v>0.3</v>
       </c>
       <c r="BA5" s="9">
         <v>0.3</v>
       </c>
       <c r="BB5" s="9">
+        <v>0.3</v>
+      </c>
+      <c r="BC5" s="9">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="BH5" s="9">
+      <c r="BI5" s="9">
         <v>0.45</v>
       </c>
-      <c r="BM5" s="9">
+      <c r="BN5" s="9">
         <v>-4.2999999999999997E-2</v>
       </c>
-      <c r="BO5" s="9">
+      <c r="BP5" s="9">
         <v>0.4</v>
       </c>
-      <c r="BP5" s="9">
+      <c r="BQ5" s="9">
         <v>0.43</v>
       </c>
-      <c r="BR5" t="s">
+      <c r="BS5" t="s">
         <v>1498</v>
       </c>
     </row>
-    <row r="6" spans="1:70" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A6">
         <f t="shared" si="1"/>
         <v>4</v>
@@ -6745,24 +6796,29 @@
       <c r="V6" s="4">
         <v>505635.20840800001</v>
       </c>
-      <c r="W6" s="4"/>
-      <c r="X6" s="6" t="s">
+      <c r="W6" s="4">
+        <v>657114.98167699995</v>
+      </c>
+      <c r="X6" s="4">
+        <v>662115.96467400005</v>
+      </c>
+      <c r="Y6" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="Y6" s="6" t="s">
+      <c r="Z6" s="6" t="s">
         <v>1477</v>
       </c>
-      <c r="Z6" s="8" t="s">
+      <c r="AA6" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="AA6">
+      <c r="AB6">
         <v>2000</v>
       </c>
-      <c r="AC6">
+      <c r="AD6">
         <v>2600</v>
       </c>
     </row>
-    <row r="7" spans="1:70" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A7">
         <f t="shared" si="1"/>
         <v>5</v>
@@ -6797,39 +6853,44 @@
       <c r="V7" s="4">
         <v>88778.648031000004</v>
       </c>
-      <c r="W7" s="4"/>
-      <c r="X7" s="6" t="s">
+      <c r="W7" s="4">
+        <v>98599.430546000003</v>
+      </c>
+      <c r="X7" s="4">
+        <v>109852.42796099999</v>
+      </c>
+      <c r="Y7" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="Y7" s="6" t="s">
+      <c r="Z7" s="6" t="s">
         <v>1476</v>
       </c>
-      <c r="Z7" s="8" t="s">
+      <c r="AA7" s="8" t="s">
         <v>673</v>
       </c>
-      <c r="AA7">
+      <c r="AB7">
         <v>1997</v>
       </c>
-      <c r="AC7">
+      <c r="AD7">
         <v>650</v>
       </c>
-      <c r="AF7" t="s">
+      <c r="AG7" t="s">
         <v>717</v>
       </c>
-      <c r="AG7" t="s">
+      <c r="AH7" t="s">
         <v>716</v>
       </c>
-      <c r="AH7" t="s">
+      <c r="AI7" t="s">
         <v>1487</v>
       </c>
-      <c r="AJ7" s="36">
+      <c r="AK7" s="36">
         <v>7.5999999999999998E-2</v>
       </c>
-      <c r="AU7" s="36">
+      <c r="AV7" s="36">
         <v>6.83E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:70" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A8">
         <f t="shared" si="1"/>
         <v>6</v>
@@ -6870,30 +6931,35 @@
       <c r="V8" s="4">
         <v>120883.773328</v>
       </c>
-      <c r="W8" s="4"/>
-      <c r="X8" s="6" t="s">
+      <c r="W8" s="4">
+        <v>155999.47028800001</v>
+      </c>
+      <c r="X8" s="4">
+        <v>190628.43056800001</v>
+      </c>
+      <c r="Y8" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="Y8" s="6" t="s">
+      <c r="Z8" s="6" t="s">
         <v>939</v>
       </c>
-      <c r="Z8" s="8" t="s">
+      <c r="AA8" s="8" t="s">
         <v>1478</v>
       </c>
-      <c r="AA8">
+      <c r="AB8">
         <v>1998</v>
       </c>
-      <c r="AC8">
+      <c r="AD8">
         <v>573</v>
       </c>
-      <c r="AR8" s="9">
+      <c r="AS8" s="9">
         <v>0.14699999999999999</v>
       </c>
-      <c r="AS8" s="9">
+      <c r="AT8" s="9">
         <v>5.8000000000000003E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:70" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A9">
         <f t="shared" si="1"/>
         <v>7</v>
@@ -6946,30 +7012,35 @@
       <c r="V9" s="4">
         <v>75171.481593000004</v>
       </c>
-      <c r="W9" s="4"/>
-      <c r="X9" s="6" t="s">
+      <c r="W9" s="4">
+        <v>75753.182516000001</v>
+      </c>
+      <c r="X9" s="4">
+        <v>64461.244358000004</v>
+      </c>
+      <c r="Y9" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="Y9" s="6" t="s">
+      <c r="Z9" s="6" t="s">
         <v>219</v>
       </c>
-      <c r="Z9" s="8" t="s">
+      <c r="AA9" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="AA9">
+      <c r="AB9">
         <v>1978</v>
       </c>
-      <c r="AC9">
+      <c r="AD9">
         <v>310</v>
       </c>
-      <c r="AX9" s="9">
+      <c r="AY9" s="9">
         <v>0.38</v>
       </c>
-      <c r="BC9" s="9">
+      <c r="BD9" s="9">
         <v>0.25</v>
       </c>
     </row>
-    <row r="10" spans="1:70" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A10">
         <f t="shared" si="1"/>
         <v>8</v>
@@ -7022,21 +7093,26 @@
       <c r="V10" s="4">
         <v>719810.28665300005</v>
       </c>
-      <c r="W10" s="4"/>
-      <c r="X10" s="6" t="s">
+      <c r="W10" s="4">
+        <v>874948.30885200005</v>
+      </c>
+      <c r="X10" s="4">
+        <v>868031.75397900003</v>
+      </c>
+      <c r="Y10" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="Y10" s="6" t="s">
+      <c r="Z10" s="6" t="s">
         <v>1130</v>
       </c>
-      <c r="Z10" s="8" t="s">
+      <c r="AA10" s="8" t="s">
         <v>664</v>
       </c>
-      <c r="AC10">
+      <c r="AD10">
         <v>3000</v>
       </c>
     </row>
-    <row r="11" spans="1:70" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A11">
         <f t="shared" si="1"/>
         <v>9</v>
@@ -7068,18 +7144,23 @@
       <c r="V11" s="4">
         <v>98415.069591000007</v>
       </c>
-      <c r="W11" s="4"/>
-      <c r="X11" s="6" t="s">
+      <c r="W11" s="4">
+        <v>96783.126308000006</v>
+      </c>
+      <c r="X11" s="4">
+        <v>98444.689024000007</v>
+      </c>
+      <c r="Y11" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="Y11" s="6" t="s">
+      <c r="Z11" s="6" t="s">
         <v>219</v>
       </c>
-      <c r="AC11">
+      <c r="AD11">
         <v>1100</v>
       </c>
     </row>
-    <row r="12" spans="1:70" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A12">
         <f t="shared" si="1"/>
         <v>10</v>
@@ -7123,40 +7204,45 @@
       <c r="V12" s="4">
         <v>48800.428701999997</v>
       </c>
-      <c r="W12" s="4"/>
-      <c r="X12" s="6" t="s">
+      <c r="W12" s="4">
+        <v>49970.5815</v>
+      </c>
+      <c r="X12" s="4">
+        <v>51433.080634999998</v>
+      </c>
+      <c r="Y12" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="Y12" s="6" t="s">
+      <c r="Z12" s="6" t="s">
         <v>219</v>
       </c>
-      <c r="Z12" s="8" t="s">
+      <c r="AA12" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="AA12">
+      <c r="AB12">
         <v>2001</v>
       </c>
-      <c r="AC12">
+      <c r="AD12">
         <v>2100</v>
       </c>
-      <c r="AJ12" s="9">
+      <c r="AK12" s="9">
         <v>0.12</v>
       </c>
-      <c r="AR12" s="9">
+      <c r="AS12" s="9">
         <v>0.15</v>
       </c>
-      <c r="AS12" s="9">
+      <c r="AT12" s="9">
         <v>0.10100000000000001</v>
       </c>
-      <c r="AX12" s="9">
+      <c r="AY12" s="9">
         <v>0.20230000000000001</v>
       </c>
-      <c r="AY12" s="9"/>
       <c r="AZ12" s="9"/>
       <c r="BA12" s="9"/>
       <c r="BB12" s="9"/>
-    </row>
-    <row r="13" spans="1:70" x14ac:dyDescent="0.2">
+      <c r="BC12" s="9"/>
+    </row>
+    <row r="13" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A13">
         <f t="shared" si="1"/>
         <v>11</v>
@@ -7203,43 +7289,48 @@
       <c r="V13" s="4">
         <v>141059.27600700001</v>
       </c>
-      <c r="W13" s="4"/>
-      <c r="X13" s="6" t="s">
+      <c r="W13" s="4">
+        <v>177162.166815</v>
+      </c>
+      <c r="X13" s="4">
+        <v>182424.02489299999</v>
+      </c>
+      <c r="Y13" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="Y13" s="6" t="s">
+      <c r="Z13" s="6" t="s">
         <v>219</v>
       </c>
-      <c r="Z13" s="8" t="s">
+      <c r="AA13" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="AC13">
+      <c r="AD13">
         <v>2500</v>
       </c>
-      <c r="AJ13" s="9">
+      <c r="AK13" s="9">
         <v>9.6000000000000002E-2</v>
       </c>
-      <c r="AL13" s="9">
+      <c r="AM13" s="9">
         <v>0.185</v>
       </c>
-      <c r="AR13" s="9">
+      <c r="AS13" s="9">
         <v>0.14299999999999999</v>
       </c>
-      <c r="AS13" s="9">
+      <c r="AT13" s="9">
         <v>0.16400000000000001</v>
       </c>
-      <c r="AX13" s="9"/>
       <c r="AY13" s="9"/>
-      <c r="AZ13" s="9">
+      <c r="AZ13" s="9"/>
+      <c r="BA13" s="9">
         <v>7.3999999999999996E-2</v>
       </c>
-      <c r="BA13" s="9"/>
       <c r="BB13" s="9"/>
-      <c r="BR13" t="s">
+      <c r="BC13" s="9"/>
+      <c r="BS13" t="s">
         <v>1499</v>
       </c>
     </row>
-    <row r="14" spans="1:70" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A14">
         <f t="shared" si="1"/>
         <v>12</v>
@@ -7272,53 +7363,58 @@
       <c r="V14" s="4">
         <v>50706.910930999999</v>
       </c>
-      <c r="W14" s="4"/>
-      <c r="X14" s="6" t="s">
+      <c r="W14" s="4">
+        <v>52699.548277000002</v>
+      </c>
+      <c r="X14" s="4">
+        <v>53648.816253999998</v>
+      </c>
+      <c r="Y14" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="Y14" s="6" t="s">
+      <c r="Z14" s="6" t="s">
         <v>1546</v>
       </c>
-      <c r="Z14" s="8" t="s">
+      <c r="AA14" s="8" t="s">
         <v>673</v>
       </c>
-      <c r="AC14">
+      <c r="AD14">
         <v>82</v>
       </c>
-      <c r="AI14" s="9">
+      <c r="AJ14" s="9">
         <v>0.15</v>
       </c>
-      <c r="AJ14" s="9">
+      <c r="AK14" s="9">
         <v>0.33</v>
       </c>
-      <c r="AK14" s="9">
+      <c r="AL14" s="9">
         <v>-0.18</v>
       </c>
-      <c r="AL14" s="9"/>
-      <c r="AQ14" s="9">
+      <c r="AM14" s="9"/>
+      <c r="AR14" s="9">
         <v>0.13500000000000001</v>
       </c>
-      <c r="AR14" s="9">
+      <c r="AS14" s="9">
         <v>0.14399999999999999</v>
       </c>
-      <c r="AS14" s="9">
+      <c r="AT14" s="9">
         <v>8.1000000000000003E-2</v>
       </c>
-      <c r="AT14" s="9">
+      <c r="AU14" s="9">
         <v>0.47220000000000001</v>
       </c>
-      <c r="AU14" s="9">
+      <c r="AV14" s="9">
         <v>0.29520000000000002</v>
       </c>
-      <c r="AX14" s="9"/>
-      <c r="AY14" s="9">
+      <c r="AY14" s="9"/>
+      <c r="AZ14" s="9">
         <v>-0.43</v>
       </c>
-      <c r="AZ14" s="9"/>
       <c r="BA14" s="9"/>
       <c r="BB14" s="9"/>
-    </row>
-    <row r="15" spans="1:70" x14ac:dyDescent="0.2">
+      <c r="BC14" s="9"/>
+    </row>
+    <row r="15" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A15">
         <f t="shared" si="1"/>
         <v>13</v>
@@ -7359,34 +7455,39 @@
       <c r="V15" s="4">
         <v>66411.788618999999</v>
       </c>
-      <c r="W15" s="4"/>
-      <c r="X15" s="6" t="s">
+      <c r="W15" s="4">
+        <v>78911.255296000003</v>
+      </c>
+      <c r="X15" s="4">
+        <v>78776.702306000007</v>
+      </c>
+      <c r="Y15" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="Y15" s="6" t="s">
+      <c r="Z15" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="Z15" s="8" t="s">
+      <c r="AA15" s="8" t="s">
         <v>223</v>
       </c>
-      <c r="AC15">
+      <c r="AD15">
         <v>1900</v>
       </c>
-      <c r="AL15" s="9">
+      <c r="AM15" s="9">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="AT15" s="9"/>
-      <c r="AX15" s="9">
+      <c r="AU15" s="9"/>
+      <c r="AY15" s="9">
         <v>8.6400000000000005E-2</v>
       </c>
-      <c r="AY15" s="9">
+      <c r="AZ15" s="9">
         <v>4.5999999999999999E-3</v>
       </c>
-      <c r="AZ15" s="9"/>
       <c r="BA15" s="9"/>
       <c r="BB15" s="9"/>
-    </row>
-    <row r="16" spans="1:70" x14ac:dyDescent="0.2">
+      <c r="BC15" s="9"/>
+    </row>
+    <row r="16" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A16">
         <f t="shared" si="1"/>
         <v>14</v>
@@ -7412,28 +7513,33 @@
       <c r="V16" s="4">
         <v>52494.564572000003</v>
       </c>
-      <c r="W16" s="4"/>
-      <c r="X16" s="6" t="s">
+      <c r="W16" s="4">
+        <v>57507.894307000002</v>
+      </c>
+      <c r="X16" s="4">
+        <v>58828.069125000002</v>
+      </c>
+      <c r="Y16" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="Y16" s="6" t="s">
+      <c r="Z16" s="6" t="s">
         <v>1559</v>
       </c>
-      <c r="AC16">
+      <c r="AD16">
         <v>1787</v>
       </c>
-      <c r="AT16" s="10" t="s">
+      <c r="AU16" s="10" t="s">
         <v>1496</v>
       </c>
-      <c r="AX16" s="9"/>
-      <c r="AY16" s="9" t="s">
+      <c r="AY16" s="9"/>
+      <c r="AZ16" s="9" t="s">
         <v>1501</v>
       </c>
-      <c r="AZ16" s="9"/>
       <c r="BA16" s="9"/>
       <c r="BB16" s="9"/>
-    </row>
-    <row r="17" spans="1:67" x14ac:dyDescent="0.2">
+      <c r="BC16" s="9"/>
+    </row>
+    <row r="17" spans="1:68" x14ac:dyDescent="0.2">
       <c r="A17">
         <f t="shared" si="1"/>
         <v>15</v>
@@ -7483,51 +7589,56 @@
       <c r="V17" s="4">
         <v>50941.421372999997</v>
       </c>
-      <c r="W17" s="4"/>
-      <c r="X17" s="6" t="s">
+      <c r="W17" s="4">
+        <v>59757.433233999996</v>
+      </c>
+      <c r="X17" s="4">
+        <v>89421.368730999995</v>
+      </c>
+      <c r="Y17" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="Y17" s="6" t="s">
+      <c r="Z17" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="Z17" s="8" t="s">
+      <c r="AA17" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="AA17">
+      <c r="AB17">
         <v>1992</v>
       </c>
-      <c r="AC17">
+      <c r="AD17">
         <v>2800</v>
       </c>
-      <c r="AI17" s="9">
+      <c r="AJ17" s="9">
         <v>0.19</v>
       </c>
-      <c r="AJ17" s="9">
+      <c r="AK17" s="9">
         <v>0.106</v>
       </c>
-      <c r="AK17" s="9">
+      <c r="AL17" s="9">
         <v>0.1</v>
       </c>
-      <c r="AL17" s="9">
+      <c r="AM17" s="9">
         <v>0.09</v>
       </c>
-      <c r="AT17" s="9"/>
-      <c r="AU17" s="9">
+      <c r="AU17" s="9"/>
+      <c r="AV17" s="9">
         <v>0.14000000000000001</v>
       </c>
-      <c r="AX17" s="9"/>
-      <c r="AY17" s="9">
+      <c r="AY17" s="9"/>
+      <c r="AZ17" s="9">
         <v>-0.18529999999999999</v>
       </c>
-      <c r="AZ17" s="9">
+      <c r="BA17" s="9">
         <v>0.13</v>
       </c>
-      <c r="BA17" s="9">
+      <c r="BB17" s="9">
         <v>0.34</v>
       </c>
-      <c r="BB17" s="9"/>
-    </row>
-    <row r="18" spans="1:67" x14ac:dyDescent="0.2">
+      <c r="BC17" s="9"/>
+    </row>
+    <row r="18" spans="1:68" x14ac:dyDescent="0.2">
       <c r="A18">
         <f t="shared" si="1"/>
         <v>16</v>
@@ -7562,24 +7673,29 @@
       <c r="V18" s="4">
         <v>27139.356501999999</v>
       </c>
-      <c r="W18" s="4"/>
-      <c r="X18" s="6" t="s">
+      <c r="W18" s="4">
+        <v>29791.421547999998</v>
+      </c>
+      <c r="X18" s="4">
+        <v>28451.166436</v>
+      </c>
+      <c r="Y18" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="AC18">
+      <c r="AD18">
         <v>119</v>
       </c>
-      <c r="AE18">
+      <c r="AF18">
         <v>2009</v>
       </c>
-      <c r="AT18" s="9"/>
-      <c r="AX18" s="9"/>
+      <c r="AU18" s="9"/>
       <c r="AY18" s="9"/>
       <c r="AZ18" s="9"/>
       <c r="BA18" s="9"/>
       <c r="BB18" s="9"/>
-    </row>
-    <row r="19" spans="1:67" x14ac:dyDescent="0.2">
+      <c r="BC18" s="9"/>
+    </row>
+    <row r="19" spans="1:68" x14ac:dyDescent="0.2">
       <c r="A19">
         <f t="shared" si="1"/>
         <v>17</v>
@@ -7632,39 +7748,44 @@
       <c r="V19" s="4">
         <v>34589.864589999997</v>
       </c>
-      <c r="W19" s="4"/>
-      <c r="X19" s="6" t="s">
+      <c r="W19" s="4">
+        <v>38504.949476000002</v>
+      </c>
+      <c r="X19" s="4">
+        <v>37677.848897999997</v>
+      </c>
+      <c r="Y19" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="Y19" s="6" t="s">
+      <c r="Z19" s="6" t="s">
         <v>220</v>
       </c>
-      <c r="Z19" s="8" t="s">
+      <c r="AA19" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="AC19">
+      <c r="AD19">
         <v>275</v>
       </c>
-      <c r="AJ19" s="9">
+      <c r="AK19" s="9">
         <v>0.13800000000000001</v>
       </c>
-      <c r="AK19" s="9">
+      <c r="AL19" s="9">
         <v>-2.4E-2</v>
       </c>
-      <c r="AT19" s="9">
+      <c r="AU19" s="9">
         <v>0.22500000000000001</v>
       </c>
-      <c r="AX19" s="9">
+      <c r="AY19" s="9">
         <v>0.18890000000000001</v>
       </c>
-      <c r="AY19" s="9">
+      <c r="AZ19" s="9">
         <v>0.1</v>
       </c>
-      <c r="AZ19" s="9"/>
       <c r="BA19" s="9"/>
       <c r="BB19" s="9"/>
-    </row>
-    <row r="20" spans="1:67" x14ac:dyDescent="0.2">
+      <c r="BC19" s="9"/>
+    </row>
+    <row r="20" spans="1:68" x14ac:dyDescent="0.2">
       <c r="A20">
         <f t="shared" si="1"/>
         <v>18</v>
@@ -7729,31 +7850,36 @@
       <c r="V20" s="4">
         <v>35899.628173999998</v>
       </c>
-      <c r="W20" s="4"/>
-      <c r="X20" s="6" t="s">
+      <c r="W20" s="4">
+        <v>40788.469402000002</v>
+      </c>
+      <c r="X20" s="4">
+        <v>39962.643006999999</v>
+      </c>
+      <c r="Y20" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="Y20" s="6" t="s">
+      <c r="Z20" s="6" t="s">
         <v>220</v>
       </c>
-      <c r="Z20" s="8" t="s">
+      <c r="AA20" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="AC20">
+      <c r="AD20">
         <v>157</v>
       </c>
-      <c r="AJ20" s="9">
+      <c r="AK20" s="9">
         <v>0.215</v>
       </c>
-      <c r="AR20" s="9">
+      <c r="AS20" s="9">
         <v>0.111</v>
       </c>
-      <c r="AS20" s="9">
+      <c r="AT20" s="9">
         <v>-2.4E-2</v>
       </c>
-      <c r="AT20" s="9"/>
-    </row>
-    <row r="21" spans="1:67" x14ac:dyDescent="0.2">
+      <c r="AU20" s="9"/>
+    </row>
+    <row r="21" spans="1:68" x14ac:dyDescent="0.2">
       <c r="A21">
         <f t="shared" si="1"/>
         <v>19</v>
@@ -7797,30 +7923,35 @@
       <c r="V21" s="4">
         <v>34081.542845000004</v>
       </c>
-      <c r="W21" s="4"/>
-      <c r="X21" s="6" t="s">
+      <c r="W21" s="4">
+        <v>32359.754158</v>
+      </c>
+      <c r="X21" s="4">
+        <v>29714.313269999999</v>
+      </c>
+      <c r="Y21" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="Y21" s="6" t="s">
+      <c r="Z21" s="6" t="s">
         <v>220</v>
       </c>
-      <c r="Z21" s="8" t="s">
+      <c r="AA21" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="AC21">
+      <c r="AD21">
         <v>162</v>
       </c>
-      <c r="AJ21" s="9">
+      <c r="AK21" s="9">
         <v>0.28499999999999998</v>
       </c>
-      <c r="AK21" s="9">
+      <c r="AL21" s="9">
         <v>-0.56000000000000005</v>
       </c>
-      <c r="AT21" s="9">
+      <c r="AU21" s="9">
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="22" spans="1:67" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:68" x14ac:dyDescent="0.2">
       <c r="A22">
         <f t="shared" si="1"/>
         <v>20</v>
@@ -7871,63 +8002,68 @@
       <c r="V22" s="4">
         <v>24791.713463</v>
       </c>
-      <c r="W22" s="4"/>
-      <c r="X22" s="6" t="s">
+      <c r="W22" s="4">
+        <v>25527.677108</v>
+      </c>
+      <c r="X22" s="4">
+        <v>27421.613829999998</v>
+      </c>
+      <c r="Y22" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="Z22" s="8" t="s">
+      <c r="AA22" s="8" t="s">
         <v>238</v>
       </c>
-      <c r="AC22">
+      <c r="AD22">
         <v>1300</v>
       </c>
-      <c r="AE22">
+      <c r="AF22">
         <v>1975</v>
       </c>
-      <c r="AH22" t="s">
+      <c r="AI22" t="s">
         <v>1486</v>
       </c>
-      <c r="AI22" s="9">
+      <c r="AJ22" s="9">
         <v>-0.14000000000000001</v>
       </c>
-      <c r="AJ22" s="9" t="s">
+      <c r="AK22" s="9" t="s">
         <v>1500</v>
       </c>
-      <c r="AK22" s="9">
+      <c r="AL22" s="9">
         <v>0.1</v>
-      </c>
-      <c r="AL22" s="9">
-        <v>-0.05</v>
       </c>
       <c r="AM22" s="9">
         <v>-0.05</v>
       </c>
       <c r="AN22" s="9">
+        <v>-0.05</v>
+      </c>
+      <c r="AO22" s="9">
         <v>0</v>
       </c>
-      <c r="AO22" s="27">
+      <c r="AP22" s="27">
         <v>0.14599999999999999</v>
       </c>
-      <c r="AQ22" t="s">
+      <c r="AR22" t="s">
         <v>1505</v>
       </c>
-      <c r="AR22" t="s">
+      <c r="AS22" t="s">
         <v>1503</v>
       </c>
-      <c r="AS22" t="s">
+      <c r="AT22" t="s">
         <v>1504</v>
       </c>
-      <c r="AU22" t="s">
+      <c r="AV22" t="s">
         <v>1502</v>
       </c>
-      <c r="AY22" s="27">
+      <c r="AZ22" s="27">
         <v>9.4E-2</v>
       </c>
-      <c r="AZ22" t="s">
+      <c r="BA22" t="s">
         <v>1497</v>
       </c>
     </row>
-    <row r="23" spans="1:67" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:68" x14ac:dyDescent="0.2">
       <c r="A23">
         <f t="shared" si="1"/>
         <v>21</v>
@@ -7956,18 +8092,23 @@
       <c r="V23" s="4">
         <v>22465.170517999999</v>
       </c>
-      <c r="W23" s="4"/>
-      <c r="X23" s="6" t="s">
+      <c r="W23" s="4">
+        <v>24228.580918</v>
+      </c>
+      <c r="X23" s="4">
+        <v>25469.090312</v>
+      </c>
+      <c r="Y23" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="Y23" s="6" t="s">
+      <c r="Z23" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="AC23">
+      <c r="AD23">
         <v>350</v>
       </c>
     </row>
-    <row r="24" spans="1:67" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:68" x14ac:dyDescent="0.2">
       <c r="A24">
         <f t="shared" si="1"/>
         <v>22</v>
@@ -8002,18 +8143,23 @@
       <c r="V24" s="4">
         <v>28384.872542000001</v>
       </c>
-      <c r="W24" s="4"/>
-      <c r="X24" s="6" t="s">
+      <c r="W24" s="4">
+        <v>33053.672677000002</v>
+      </c>
+      <c r="X24" s="4">
+        <v>35403.796805999998</v>
+      </c>
+      <c r="Y24" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="Y24" s="6" t="s">
+      <c r="Z24" s="6" t="s">
         <v>1559</v>
       </c>
-      <c r="AC24">
+      <c r="AD24">
         <v>56</v>
       </c>
     </row>
-    <row r="25" spans="1:67" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:68" x14ac:dyDescent="0.2">
       <c r="A25">
         <f t="shared" si="1"/>
         <v>23</v>
@@ -8048,21 +8194,26 @@
       <c r="V25" s="4">
         <v>23178.205569999998</v>
       </c>
-      <c r="W25" s="4"/>
-      <c r="X25" s="6" t="s">
+      <c r="W25" s="4">
+        <v>24428.147560000001</v>
+      </c>
+      <c r="X25" s="4">
+        <v>20722.385988999999</v>
+      </c>
+      <c r="Y25" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="Y25" s="6" t="s">
+      <c r="Z25" s="6" t="s">
         <v>1560</v>
       </c>
-      <c r="AC25">
+      <c r="AD25">
         <v>230</v>
       </c>
-      <c r="AZ25" s="36">
+      <c r="BA25" s="36">
         <v>0.14799999999999999</v>
       </c>
     </row>
-    <row r="26" spans="1:67" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:68" x14ac:dyDescent="0.2">
       <c r="A26">
         <f t="shared" si="1"/>
         <v>24</v>
@@ -8097,18 +8248,23 @@
       <c r="V26" s="4">
         <v>29446.119595</v>
       </c>
-      <c r="W26" s="4"/>
-      <c r="X26" s="6" t="s">
+      <c r="W26" s="4">
+        <v>30086.997002</v>
+      </c>
+      <c r="X26" s="4">
+        <v>30340.662734000001</v>
+      </c>
+      <c r="Y26" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="AC26">
+      <c r="AD26">
         <v>241</v>
       </c>
-      <c r="AL26" s="9">
+      <c r="AM26" s="9">
         <v>0.13500000000000001</v>
       </c>
     </row>
-    <row r="27" spans="1:67" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:68" x14ac:dyDescent="0.2">
       <c r="A27">
         <f t="shared" si="1"/>
         <v>25</v>
@@ -8140,27 +8296,32 @@
       <c r="V27" s="4">
         <v>222.78121300000001</v>
       </c>
-      <c r="W27" s="4"/>
-      <c r="X27" s="6" t="s">
+      <c r="W27" s="4">
+        <v>106.74292199999999</v>
+      </c>
+      <c r="X27" s="4">
+        <v>57.616042</v>
+      </c>
+      <c r="Y27" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="Y27" s="6" t="s">
+      <c r="Z27" s="6" t="s">
         <v>220</v>
       </c>
-      <c r="AA27">
+      <c r="AB27">
         <v>2006</v>
       </c>
-      <c r="AR27" s="9">
+      <c r="AS27" s="9">
         <v>0.16200000000000001</v>
       </c>
-      <c r="AS27" s="9">
+      <c r="AT27" s="9">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="AT27" s="9">
+      <c r="AU27" s="9">
         <v>0.56000000000000005</v>
       </c>
     </row>
-    <row r="28" spans="1:67" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:68" x14ac:dyDescent="0.2">
       <c r="A28">
         <f t="shared" si="1"/>
         <v>26</v>
@@ -8210,120 +8371,125 @@
       <c r="V28" s="4">
         <v>14051.394007000001</v>
       </c>
-      <c r="W28" s="4"/>
-      <c r="X28" s="6" t="s">
+      <c r="W28" s="4">
+        <v>13742.951177000001</v>
+      </c>
+      <c r="X28" s="4">
+        <v>13611.137640000001</v>
+      </c>
+      <c r="Y28" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="Y28" s="6" t="s">
+      <c r="Z28" s="6" t="s">
         <v>220</v>
       </c>
-      <c r="Z28" s="8" t="s">
+      <c r="AA28" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="AA28">
+      <c r="AB28">
         <v>1997</v>
       </c>
-      <c r="AB28" t="s">
+      <c r="AC28" t="s">
         <v>227</v>
       </c>
-      <c r="AD28" s="9">
+      <c r="AE28" s="9">
         <f>RATE(2022-1998,0,-1,13.71)</f>
         <v>0.11526111596972678</v>
       </c>
-      <c r="AE28" s="9">
-        <f>1*(1+BI$28)*(1+BH28)*(1+BG28)*(1+BF28)*(1+BE28)*(1+BD28)*(1+BC28)*(1+BB28)*(1+BA28)*(1+AZ28)*(1+AY28)*(1+AX28)*(1+AW28)*(1+AV28)*(1+AU28)*(1+AT28)*(1+AS28)*(1+AR28)*(1+AQ28)*(1+AP28)*(1+AO28)*(1+AN28)*(1+AM28)*(1+AL28)*(1+AK28)-1</f>
+      <c r="AF28" s="9">
+        <f>1*(1+BJ$28)*(1+BI28)*(1+BH28)*(1+BG28)*(1+BF28)*(1+BE28)*(1+BD28)*(1+BC28)*(1+BB28)*(1+BA28)*(1+AZ28)*(1+AY28)*(1+AX28)*(1+AW28)*(1+AV28)*(1+AU28)*(1+AT28)*(1+AS28)*(1+AR28)*(1+AQ28)*(1+AP28)*(1+AO28)*(1+AN28)*(1+AM28)*(1+AL28)-1</f>
         <v>13.713492129281141</v>
       </c>
-      <c r="AF28" s="9"/>
       <c r="AG28" s="9"/>
       <c r="AH28" s="9"/>
       <c r="AI28" s="9"/>
-      <c r="AJ28" s="9">
+      <c r="AJ28" s="9"/>
+      <c r="AK28" s="9">
         <v>0.19</v>
       </c>
-      <c r="AK28" s="10">
+      <c r="AL28" s="10">
         <v>-0.33</v>
       </c>
-      <c r="AL28" s="9">
+      <c r="AM28" s="9">
         <v>-7.0000000000000007E-2</v>
       </c>
-      <c r="AM28" s="9">
+      <c r="AN28" s="9">
         <v>0.23</v>
       </c>
-      <c r="AN28" s="9">
+      <c r="AO28" s="9">
         <v>0.29899999999999999</v>
       </c>
-      <c r="AO28" s="9">
+      <c r="AP28" s="9">
         <v>-0.05</v>
       </c>
-      <c r="AP28" s="9">
+      <c r="AQ28" s="9">
         <v>8.2000000000000003E-2</v>
       </c>
-      <c r="AQ28" s="9">
+      <c r="AR28" s="9">
         <v>-2.7E-2</v>
       </c>
-      <c r="AR28" s="9">
+      <c r="AS28" s="9">
         <v>8.7999999999999995E-2</v>
       </c>
-      <c r="AS28" s="9">
+      <c r="AT28" s="9">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="AT28" s="9">
+      <c r="AU28" s="9">
         <v>0.14199999999999999</v>
       </c>
-      <c r="AU28" s="9">
+      <c r="AV28" s="9">
         <v>0.193</v>
       </c>
-      <c r="AV28" s="9">
+      <c r="AW28" s="9">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="AW28" s="9">
+      <c r="AX28" s="9">
         <v>0.126</v>
       </c>
-      <c r="AX28" s="9">
+      <c r="AY28" s="9">
         <v>0.14000000000000001</v>
       </c>
-      <c r="AY28" s="9">
+      <c r="AZ28" s="9">
         <v>-0.32900000000000001</v>
       </c>
-      <c r="AZ28" s="9">
+      <c r="BA28" s="9">
         <v>0.46200000000000002</v>
       </c>
-      <c r="BA28" s="9">
+      <c r="BB28" s="9">
         <v>0.13700000000000001</v>
       </c>
-      <c r="BB28" s="9">
+      <c r="BC28" s="9">
         <v>0.25900000000000001</v>
       </c>
-      <c r="BC28" s="9">
+      <c r="BD28" s="9">
         <v>0.14599999999999999</v>
       </c>
-      <c r="BD28" s="9">
+      <c r="BE28" s="9">
         <v>8.2000000000000003E-2</v>
       </c>
-      <c r="BE28" s="9">
+      <c r="BF28" s="9">
         <v>0.14599999999999999</v>
       </c>
-      <c r="BF28" s="9">
+      <c r="BG28" s="9">
         <v>0.40400000000000003</v>
       </c>
-      <c r="BG28" s="9">
+      <c r="BH28" s="9">
         <v>0.73399999999999999</v>
       </c>
-      <c r="BH28" s="9">
+      <c r="BI28" s="9">
         <v>0.46800000000000003</v>
       </c>
-      <c r="BI28" s="9">
+      <c r="BJ28" s="9">
         <v>7.5999999999999998E-2</v>
       </c>
-      <c r="BJ28" s="9"/>
       <c r="BK28" s="9"/>
       <c r="BL28" s="9"/>
       <c r="BM28" s="9"/>
       <c r="BN28" s="9"/>
       <c r="BO28" s="9"/>
-    </row>
-    <row r="29" spans="1:67" x14ac:dyDescent="0.2">
+      <c r="BP28" s="9"/>
+    </row>
+    <row r="29" spans="1:68" x14ac:dyDescent="0.2">
       <c r="A29">
         <f t="shared" si="1"/>
         <v>27</v>
@@ -8358,17 +8524,22 @@
       <c r="V29" s="4">
         <v>18930.893253999999</v>
       </c>
-      <c r="W29" s="4"/>
-      <c r="X29" s="6" t="s">
+      <c r="W29" s="4">
+        <v>21244.592129000001</v>
+      </c>
+      <c r="X29" s="4">
+        <v>25809.366483000002</v>
+      </c>
+      <c r="Y29" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="Y29" s="6" t="s">
+      <c r="Z29" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="AY29" s="9"/>
       <c r="AZ29" s="9"/>
-    </row>
-    <row r="30" spans="1:67" x14ac:dyDescent="0.2">
+      <c r="BA29" s="9"/>
+    </row>
+    <row r="30" spans="1:68" x14ac:dyDescent="0.2">
       <c r="A30">
         <f t="shared" si="1"/>
         <v>28</v>
@@ -8406,28 +8577,33 @@
       <c r="V30" s="4">
         <v>13729.120532999999</v>
       </c>
-      <c r="W30" s="4"/>
-      <c r="X30" s="6" t="s">
+      <c r="W30" s="4">
+        <v>14643.293766999999</v>
+      </c>
+      <c r="X30" s="4">
+        <v>15526.737802</v>
+      </c>
+      <c r="Y30" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="AG30" t="s">
+      <c r="AH30" t="s">
         <v>1562</v>
       </c>
-      <c r="AJ30" s="9">
+      <c r="AK30" s="9">
         <v>0.26300000000000001</v>
       </c>
-      <c r="AK30" s="9">
+      <c r="AL30" s="9">
         <v>-8.7999999999999995E-2</v>
       </c>
-      <c r="AX30" s="9">
+      <c r="AY30" s="9">
         <v>0.41210000000000002</v>
       </c>
-      <c r="AY30" s="9">
+      <c r="AZ30" s="9">
         <v>-0.11899999999999999</v>
       </c>
-      <c r="AZ30" s="9"/>
-    </row>
-    <row r="31" spans="1:67" x14ac:dyDescent="0.2">
+      <c r="BA30" s="9"/>
+    </row>
+    <row r="31" spans="1:68" x14ac:dyDescent="0.2">
       <c r="A31">
         <f t="shared" si="1"/>
         <v>29</v>
@@ -8465,37 +8641,42 @@
       <c r="V31" s="4">
         <v>17593.419802</v>
       </c>
-      <c r="W31" s="4"/>
-      <c r="X31" s="6" t="s">
+      <c r="W31" s="4">
+        <v>22721.159136999999</v>
+      </c>
+      <c r="X31" s="4">
+        <v>22594.232626000001</v>
+      </c>
+      <c r="Y31" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="Y31" s="6" t="s">
+      <c r="Z31" s="6" t="s">
         <v>1305</v>
       </c>
-      <c r="Z31" s="8" t="s">
+      <c r="AA31" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="AA31">
+      <c r="AB31">
         <v>1977</v>
       </c>
-      <c r="AJ31" s="9">
+      <c r="AK31" s="9">
         <v>4.7E-2</v>
       </c>
-      <c r="AQ31" s="9">
+      <c r="AR31" s="9">
         <v>0.13100000000000001</v>
       </c>
-      <c r="AR31" s="9">
+      <c r="AS31" s="9">
         <v>2.7E-2</v>
       </c>
-      <c r="AX31" s="9">
+      <c r="AY31" s="9">
         <v>0.307</v>
       </c>
-      <c r="AY31" s="9">
+      <c r="AZ31" s="9">
         <v>-0.03</v>
       </c>
-      <c r="AZ31" s="9"/>
-    </row>
-    <row r="32" spans="1:67" x14ac:dyDescent="0.2">
+      <c r="BA31" s="9"/>
+    </row>
+    <row r="32" spans="1:68" x14ac:dyDescent="0.2">
       <c r="A32">
         <f t="shared" si="1"/>
         <v>30</v>
@@ -8529,20 +8710,21 @@
       </c>
       <c r="V32" s="4"/>
       <c r="W32" s="4"/>
-      <c r="X32" s="6" t="s">
+      <c r="X32" s="4"/>
+      <c r="Y32" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="Y32" s="6" t="s">
+      <c r="Z32" s="6" t="s">
         <v>1559</v>
       </c>
-      <c r="AL32" s="9">
+      <c r="AM32" s="9">
         <v>5.5E-2</v>
       </c>
-      <c r="AX32" s="9"/>
       <c r="AY32" s="9"/>
       <c r="AZ32" s="9"/>
-    </row>
-    <row r="33" spans="1:52" x14ac:dyDescent="0.2">
+      <c r="BA32" s="9"/>
+    </row>
+    <row r="33" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A33">
         <f t="shared" si="1"/>
         <v>31</v>
@@ -8576,14 +8758,15 @@
       </c>
       <c r="V33" s="4"/>
       <c r="W33" s="4"/>
-      <c r="X33" s="6" t="s">
+      <c r="X33" s="4"/>
+      <c r="Y33" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="AX33" s="9"/>
       <c r="AY33" s="9"/>
       <c r="AZ33" s="9"/>
-    </row>
-    <row r="34" spans="1:52" x14ac:dyDescent="0.2">
+      <c r="BA33" s="9"/>
+    </row>
+    <row r="34" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A34">
         <f t="shared" si="1"/>
         <v>32</v>
@@ -8623,23 +8806,24 @@
       </c>
       <c r="V34" s="4"/>
       <c r="W34" s="4"/>
-      <c r="X34" s="6" t="s">
+      <c r="X34" s="4"/>
+      <c r="Y34" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Y34" s="6" t="s">
+      <c r="Z34" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="Z34" s="8" t="s">
+      <c r="AA34" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="AA34">
+      <c r="AB34">
         <v>2000</v>
       </c>
-      <c r="AX34" s="9"/>
       <c r="AY34" s="9"/>
       <c r="AZ34" s="9"/>
-    </row>
-    <row r="35" spans="1:52" x14ac:dyDescent="0.2">
+      <c r="BA34" s="9"/>
+    </row>
+    <row r="35" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A35">
         <f t="shared" si="1"/>
         <v>33</v>
@@ -8673,21 +8857,22 @@
       </c>
       <c r="V35" s="4"/>
       <c r="W35" s="4"/>
-      <c r="X35" s="6" t="s">
+      <c r="X35" s="4"/>
+      <c r="Y35" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="Y35" s="6" t="s">
+      <c r="Z35" s="6" t="s">
         <v>1564</v>
       </c>
-      <c r="Z35" s="8" t="s">
+      <c r="AA35" s="8" t="s">
         <v>1206</v>
       </c>
-      <c r="AA35">
+      <c r="AB35">
         <v>2008</v>
       </c>
-      <c r="AX35" s="9"/>
-    </row>
-    <row r="36" spans="1:52" x14ac:dyDescent="0.2">
+      <c r="AY35" s="9"/>
+    </row>
+    <row r="36" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A36">
         <f t="shared" si="1"/>
         <v>34</v>
@@ -8712,15 +8897,16 @@
       </c>
       <c r="V36" s="4"/>
       <c r="W36" s="4"/>
-      <c r="X36" s="6" t="s">
+      <c r="X36" s="4"/>
+      <c r="Y36" s="6" t="s">
         <v>1267</v>
       </c>
-      <c r="Z36" s="8" t="s">
+      <c r="AA36" s="8" t="s">
         <v>223</v>
       </c>
-      <c r="AX36" s="9"/>
-    </row>
-    <row r="37" spans="1:52" x14ac:dyDescent="0.2">
+      <c r="AY36" s="9"/>
+    </row>
+    <row r="37" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A37">
         <f t="shared" si="1"/>
         <v>35</v>
@@ -8754,20 +8940,21 @@
       </c>
       <c r="V37" s="4"/>
       <c r="W37" s="4"/>
-      <c r="X37" s="6" t="s">
+      <c r="X37" s="4"/>
+      <c r="Y37" s="6" t="s">
         <v>1566</v>
       </c>
-      <c r="Y37" s="6" t="s">
+      <c r="Z37" s="6" t="s">
         <v>1565</v>
       </c>
-      <c r="AX37" s="9">
+      <c r="AY37" s="9">
         <v>0.29020000000000001</v>
       </c>
-      <c r="AY37" s="9">
+      <c r="AZ37" s="9">
         <v>0.08</v>
       </c>
     </row>
-    <row r="38" spans="1:52" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A38">
         <f t="shared" si="1"/>
         <v>36</v>
@@ -8796,17 +8983,18 @@
       <c r="U38" s="4"/>
       <c r="V38" s="4"/>
       <c r="W38" s="4"/>
-      <c r="X38" s="6" t="s">
+      <c r="X38" s="4"/>
+      <c r="Y38" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Y38" s="6" t="s">
+      <c r="Z38" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="Z38" s="8" t="s">
+      <c r="AA38" s="8" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="39" spans="1:52" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A39">
         <f t="shared" si="1"/>
         <v>37</v>
@@ -8831,17 +9019,18 @@
       <c r="U39" s="4"/>
       <c r="V39" s="4"/>
       <c r="W39" s="4"/>
-      <c r="X39" s="6" t="s">
+      <c r="X39" s="4"/>
+      <c r="Y39" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Y39" s="6" t="s">
+      <c r="Z39" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="Z39" s="8" t="s">
+      <c r="AA39" s="8" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="40" spans="1:52" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A40">
         <f t="shared" si="1"/>
         <v>38</v>
@@ -8863,8 +9052,9 @@
       <c r="U40" s="4"/>
       <c r="V40" s="4"/>
       <c r="W40" s="4"/>
-    </row>
-    <row r="41" spans="1:52" x14ac:dyDescent="0.2">
+      <c r="X40" s="4"/>
+    </row>
+    <row r="41" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A41">
         <f t="shared" si="1"/>
         <v>39</v>
@@ -8886,8 +9076,9 @@
       <c r="U41" s="4"/>
       <c r="V41" s="4"/>
       <c r="W41" s="4"/>
-    </row>
-    <row r="42" spans="1:52" x14ac:dyDescent="0.2">
+      <c r="X41" s="4"/>
+    </row>
+    <row r="42" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A42">
         <f t="shared" si="1"/>
         <v>40</v>
@@ -8915,23 +9106,24 @@
       <c r="U42" s="4"/>
       <c r="V42" s="4"/>
       <c r="W42" s="4"/>
-      <c r="X42" s="6" t="s">
+      <c r="X42" s="4"/>
+      <c r="Y42" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="Y42" s="6" t="s">
+      <c r="Z42" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="Z42" s="8" t="s">
+      <c r="AA42" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="AT42" s="36">
+      <c r="AU42" s="36">
         <v>0.2525</v>
       </c>
-      <c r="AU42" s="36">
+      <c r="AV42" s="36">
         <v>0.215</v>
       </c>
     </row>
-    <row r="43" spans="1:52" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A43">
         <f t="shared" si="1"/>
         <v>41</v>
@@ -8959,14 +9151,15 @@
       <c r="U43" s="4"/>
       <c r="V43" s="4"/>
       <c r="W43" s="4"/>
-      <c r="X43" s="6" t="s">
+      <c r="X43" s="4"/>
+      <c r="Y43" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Z43" s="8" t="s">
+      <c r="AA43" s="8" t="s">
         <v>1206</v>
       </c>
     </row>
-    <row r="44" spans="1:52" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A44">
         <f t="shared" si="1"/>
         <v>42</v>
@@ -8985,14 +9178,15 @@
       <c r="U44" s="4"/>
       <c r="V44" s="4"/>
       <c r="W44" s="4"/>
-      <c r="AA44">
+      <c r="X44" s="4"/>
+      <c r="AB44">
         <v>2007</v>
       </c>
-      <c r="AJ44" s="9">
+      <c r="AK44" s="9">
         <v>0.254</v>
       </c>
     </row>
-    <row r="45" spans="1:52" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A45">
         <f t="shared" si="1"/>
         <v>43</v>
@@ -9020,17 +9214,18 @@
       <c r="U45" s="4"/>
       <c r="V45" s="4"/>
       <c r="W45" s="4"/>
-      <c r="X45" s="6" t="s">
+      <c r="X45" s="4"/>
+      <c r="Y45" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Y45" s="6" t="s">
+      <c r="Z45" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="Z45" s="8" t="s">
+      <c r="AA45" s="8" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="46" spans="1:52" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A46">
         <f t="shared" si="1"/>
         <v>44</v>
@@ -9052,11 +9247,12 @@
       <c r="U46" s="4"/>
       <c r="V46" s="4"/>
       <c r="W46" s="4"/>
-      <c r="X46" s="6" t="s">
+      <c r="X46" s="4"/>
+      <c r="Y46" s="6" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="47" spans="1:52" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A47">
         <f t="shared" si="1"/>
         <v>45</v>
@@ -9072,8 +9268,9 @@
       <c r="U47" s="4"/>
       <c r="V47" s="4"/>
       <c r="W47" s="4"/>
-    </row>
-    <row r="48" spans="1:52" x14ac:dyDescent="0.2">
+      <c r="X47" s="4"/>
+    </row>
+    <row r="48" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A48">
         <f t="shared" si="1"/>
         <v>46</v>
@@ -9089,8 +9286,9 @@
       <c r="U48" s="4"/>
       <c r="V48" s="4"/>
       <c r="W48" s="4"/>
-    </row>
-    <row r="49" spans="1:47" x14ac:dyDescent="0.2">
+      <c r="X48" s="4"/>
+    </row>
+    <row r="49" spans="1:48" x14ac:dyDescent="0.2">
       <c r="A49">
         <f t="shared" si="1"/>
         <v>47</v>
@@ -9115,22 +9313,23 @@
       <c r="U49" s="4"/>
       <c r="V49" s="4"/>
       <c r="W49" s="4"/>
-      <c r="AI49" s="9"/>
-      <c r="AJ49" s="9">
+      <c r="X49" s="4"/>
+      <c r="AJ49" s="9"/>
+      <c r="AK49" s="9">
         <v>0.18</v>
       </c>
-      <c r="AR49" s="9">
+      <c r="AS49" s="9">
         <v>0.11</v>
       </c>
-      <c r="AS49" s="9">
+      <c r="AT49" s="9">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="AT49" s="9"/>
-      <c r="AU49" s="9">
+      <c r="AU49" s="9"/>
+      <c r="AV49" s="9">
         <v>0.29270000000000002</v>
       </c>
     </row>
-    <row r="50" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:48" x14ac:dyDescent="0.2">
       <c r="A50">
         <f t="shared" si="1"/>
         <v>48</v>
@@ -9152,8 +9351,9 @@
       <c r="U50" s="4"/>
       <c r="V50" s="4"/>
       <c r="W50" s="4"/>
-    </row>
-    <row r="51" spans="1:47" x14ac:dyDescent="0.2">
+      <c r="X50" s="4"/>
+    </row>
+    <row r="51" spans="1:48" x14ac:dyDescent="0.2">
       <c r="A51">
         <f t="shared" si="1"/>
         <v>49</v>
@@ -9175,8 +9375,9 @@
       <c r="U51" s="4"/>
       <c r="V51" s="4"/>
       <c r="W51" s="4"/>
-    </row>
-    <row r="52" spans="1:47" x14ac:dyDescent="0.2">
+      <c r="X51" s="4"/>
+    </row>
+    <row r="52" spans="1:48" x14ac:dyDescent="0.2">
       <c r="A52">
         <f t="shared" si="1"/>
         <v>50</v>
@@ -9195,11 +9396,12 @@
       <c r="U52" s="4"/>
       <c r="V52" s="4"/>
       <c r="W52" s="4"/>
-      <c r="X52" s="6" t="s">
+      <c r="X52" s="4"/>
+      <c r="Y52" s="6" t="s">
         <v>1326</v>
       </c>
     </row>
-    <row r="53" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:48" x14ac:dyDescent="0.2">
       <c r="A53">
         <f t="shared" si="1"/>
         <v>51</v>
@@ -9224,11 +9426,12 @@
       <c r="U53" s="4"/>
       <c r="V53" s="4"/>
       <c r="W53" s="4"/>
-      <c r="X53" s="6" t="s">
+      <c r="X53" s="4"/>
+      <c r="Y53" s="6" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="54" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:48" x14ac:dyDescent="0.2">
       <c r="A54">
         <f t="shared" si="1"/>
         <v>52</v>
@@ -9256,14 +9459,15 @@
       <c r="U54" s="4"/>
       <c r="V54" s="4"/>
       <c r="W54" s="4"/>
-      <c r="X54" s="6" t="s">
+      <c r="X54" s="4"/>
+      <c r="Y54" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="Y54" s="6" t="s">
+      <c r="Z54" s="6" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="55" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:48" x14ac:dyDescent="0.2">
       <c r="A55">
         <f t="shared" si="1"/>
         <v>53</v>
@@ -9291,14 +9495,15 @@
       <c r="U55" s="4"/>
       <c r="V55" s="4"/>
       <c r="W55" s="4"/>
-      <c r="X55" s="6" t="s">
+      <c r="X55" s="4"/>
+      <c r="Y55" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="Y55" s="6" t="s">
+      <c r="Z55" s="6" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="56" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:48" x14ac:dyDescent="0.2">
       <c r="A56">
         <f t="shared" si="1"/>
         <v>54</v>
@@ -9329,14 +9534,15 @@
       <c r="U56" s="4"/>
       <c r="V56" s="4"/>
       <c r="W56" s="4"/>
-      <c r="X56" s="6" t="s">
+      <c r="X56" s="4"/>
+      <c r="Y56" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="Y56" s="6" t="s">
+      <c r="Z56" s="6" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="57" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:48" x14ac:dyDescent="0.2">
       <c r="A57">
         <f t="shared" si="1"/>
         <v>55</v>
@@ -9358,8 +9564,9 @@
       <c r="U57" s="4"/>
       <c r="V57" s="4"/>
       <c r="W57" s="4"/>
-    </row>
-    <row r="58" spans="1:47" x14ac:dyDescent="0.2">
+      <c r="X57" s="4"/>
+    </row>
+    <row r="58" spans="1:48" x14ac:dyDescent="0.2">
       <c r="A58">
         <f t="shared" si="1"/>
         <v>56</v>
@@ -9378,17 +9585,18 @@
       <c r="U58" s="4"/>
       <c r="V58" s="4"/>
       <c r="W58" s="4"/>
-      <c r="AJ58" s="36">
+      <c r="X58" s="4"/>
+      <c r="AK58" s="36">
         <v>0.17399999999999999</v>
       </c>
-      <c r="AT58" s="9">
+      <c r="AU58" s="9">
         <v>1.0174000000000001</v>
       </c>
-      <c r="AU58" s="9">
+      <c r="AV58" s="9">
         <v>0.53800000000000003</v>
       </c>
     </row>
-    <row r="59" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:48" x14ac:dyDescent="0.2">
       <c r="A59">
         <f t="shared" si="1"/>
         <v>57</v>
@@ -9416,11 +9624,12 @@
       <c r="U59" s="4"/>
       <c r="V59" s="4"/>
       <c r="W59" s="4"/>
-      <c r="X59" s="6" t="s">
+      <c r="X59" s="4"/>
+      <c r="Y59" s="6" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="60" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:48" x14ac:dyDescent="0.2">
       <c r="A60">
         <f>+A63+1</f>
         <v>61</v>
@@ -9442,8 +9651,9 @@
       <c r="U60" s="4"/>
       <c r="V60" s="4"/>
       <c r="W60" s="4"/>
-    </row>
-    <row r="61" spans="1:47" x14ac:dyDescent="0.2">
+      <c r="X60" s="4"/>
+    </row>
+    <row r="61" spans="1:48" x14ac:dyDescent="0.2">
       <c r="A61">
         <f>+A59+1</f>
         <v>58</v>
@@ -9459,8 +9669,9 @@
       <c r="U61" s="4"/>
       <c r="V61" s="4"/>
       <c r="W61" s="4"/>
-    </row>
-    <row r="62" spans="1:47" x14ac:dyDescent="0.2">
+      <c r="X61" s="4"/>
+    </row>
+    <row r="62" spans="1:48" x14ac:dyDescent="0.2">
       <c r="A62">
         <f t="shared" si="1"/>
         <v>59</v>
@@ -9485,8 +9696,9 @@
       <c r="U62" s="4"/>
       <c r="V62" s="4"/>
       <c r="W62" s="4"/>
-    </row>
-    <row r="63" spans="1:47" x14ac:dyDescent="0.2">
+      <c r="X62" s="4"/>
+    </row>
+    <row r="63" spans="1:48" x14ac:dyDescent="0.2">
       <c r="A63">
         <f t="shared" si="1"/>
         <v>60</v>
@@ -9511,14 +9723,17 @@
       <c r="U63" s="4"/>
       <c r="V63" s="4"/>
       <c r="W63" s="4"/>
-      <c r="X63" s="6" t="s">
+      <c r="X63" s="4">
+        <v>5278.59</v>
+      </c>
+      <c r="Y63" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="Y63" s="6" t="s">
+      <c r="Z63" s="6" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="64" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:48" x14ac:dyDescent="0.2">
       <c r="A64">
         <f>+A60+1</f>
         <v>62</v>
@@ -9546,29 +9761,30 @@
       <c r="U64" s="4"/>
       <c r="V64" s="4"/>
       <c r="W64" s="4"/>
-      <c r="X64" s="6" t="s">
+      <c r="X64" s="4"/>
+      <c r="Y64" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Y64" s="6" t="s">
+      <c r="Z64" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="AJ64" s="9">
+      <c r="AK64" s="9">
         <v>0.26</v>
       </c>
-      <c r="AK64" s="9">
+      <c r="AL64" s="9">
         <v>-0.26</v>
       </c>
-      <c r="AL64" s="9">
+      <c r="AM64" s="9">
         <v>-0.21</v>
       </c>
-      <c r="AR64" s="9">
+      <c r="AS64" s="9">
         <v>0.51800000000000002</v>
       </c>
-      <c r="AS64" s="9">
+      <c r="AT64" s="9">
         <v>0.189</v>
       </c>
     </row>
-    <row r="65" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A65">
         <f t="shared" si="1"/>
         <v>63</v>
@@ -9590,8 +9806,9 @@
       <c r="U65" s="4"/>
       <c r="V65" s="4"/>
       <c r="W65" s="4"/>
-    </row>
-    <row r="66" spans="1:51" x14ac:dyDescent="0.2">
+      <c r="X65" s="4"/>
+    </row>
+    <row r="66" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A66">
         <f t="shared" si="1"/>
         <v>64</v>
@@ -9616,11 +9833,12 @@
       <c r="U66" s="4"/>
       <c r="V66" s="4"/>
       <c r="W66" s="4"/>
-      <c r="X66" s="6" t="s">
+      <c r="X66" s="4"/>
+      <c r="Y66" s="6" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="67" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A67">
         <f t="shared" si="1"/>
         <v>65</v>
@@ -9642,11 +9860,12 @@
       <c r="U67" s="4"/>
       <c r="V67" s="4"/>
       <c r="W67" s="4"/>
-      <c r="X67" s="6" t="s">
+      <c r="X67" s="4"/>
+      <c r="Y67" s="6" t="s">
         <v>1305</v>
       </c>
     </row>
-    <row r="68" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A68">
         <f t="shared" si="1"/>
         <v>66</v>
@@ -9671,14 +9890,15 @@
       <c r="U68" s="4"/>
       <c r="V68" s="4"/>
       <c r="W68" s="4"/>
-      <c r="X68" s="6" t="s">
+      <c r="X68" s="4"/>
+      <c r="Y68" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="AJ68" s="36">
+      <c r="AK68" s="36">
         <v>8.7999999999999995E-2</v>
       </c>
     </row>
-    <row r="69" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A69">
         <f t="shared" si="1"/>
         <v>67</v>
@@ -9694,8 +9914,9 @@
       <c r="U69" s="4"/>
       <c r="V69" s="4"/>
       <c r="W69" s="4"/>
-    </row>
-    <row r="70" spans="1:51" x14ac:dyDescent="0.2">
+      <c r="X69" s="4"/>
+    </row>
+    <row r="70" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A70">
         <f t="shared" si="1"/>
         <v>68</v>
@@ -9709,8 +9930,9 @@
       <c r="U70" s="4"/>
       <c r="V70" s="4"/>
       <c r="W70" s="4"/>
-    </row>
-    <row r="71" spans="1:51" x14ac:dyDescent="0.2">
+      <c r="X70" s="4"/>
+    </row>
+    <row r="71" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A71">
         <f t="shared" si="1"/>
         <v>69</v>
@@ -9727,8 +9949,9 @@
       <c r="U71" s="4"/>
       <c r="V71" s="4"/>
       <c r="W71" s="4"/>
-    </row>
-    <row r="72" spans="1:51" x14ac:dyDescent="0.2">
+      <c r="X71" s="4"/>
+    </row>
+    <row r="72" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A72">
         <f t="shared" si="1"/>
         <v>70</v>
@@ -9750,11 +9973,12 @@
       <c r="U72" s="4"/>
       <c r="V72" s="4"/>
       <c r="W72" s="4"/>
-      <c r="X72" s="6" t="s">
+      <c r="X72" s="4"/>
+      <c r="Y72" s="6" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="73" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A73">
         <f t="shared" si="1"/>
         <v>71</v>
@@ -9773,8 +9997,9 @@
       <c r="U73" s="4"/>
       <c r="V73" s="4"/>
       <c r="W73" s="4"/>
-    </row>
-    <row r="74" spans="1:51" x14ac:dyDescent="0.2">
+      <c r="X73" s="4"/>
+    </row>
+    <row r="74" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A74">
         <f t="shared" si="1"/>
         <v>72</v>
@@ -9799,11 +10024,12 @@
       <c r="U74" s="4"/>
       <c r="V74" s="4"/>
       <c r="W74" s="4"/>
-      <c r="X74" s="6" t="s">
+      <c r="X74" s="4"/>
+      <c r="Y74" s="6" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="75" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A75">
         <f t="shared" si="1"/>
         <v>73</v>
@@ -9828,8 +10054,9 @@
       <c r="U75" s="4"/>
       <c r="V75" s="4"/>
       <c r="W75" s="4"/>
-    </row>
-    <row r="76" spans="1:51" x14ac:dyDescent="0.2">
+      <c r="X75" s="4"/>
+    </row>
+    <row r="76" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A76">
         <f t="shared" si="1"/>
         <v>74</v>
@@ -9854,11 +10081,12 @@
       <c r="U76" s="4"/>
       <c r="V76" s="4"/>
       <c r="W76" s="4"/>
-      <c r="X76" s="6" t="s">
+      <c r="X76" s="4"/>
+      <c r="Y76" s="6" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="77" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A77">
         <f t="shared" si="1"/>
         <v>75</v>
@@ -9874,8 +10102,9 @@
       <c r="U77" s="4"/>
       <c r="V77" s="4"/>
       <c r="W77" s="4"/>
-    </row>
-    <row r="78" spans="1:51" x14ac:dyDescent="0.2">
+      <c r="X77" s="4"/>
+    </row>
+    <row r="78" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A78">
         <f t="shared" si="1"/>
         <v>76</v>
@@ -9891,8 +10120,9 @@
       <c r="U78" s="4"/>
       <c r="V78" s="4"/>
       <c r="W78" s="4"/>
-    </row>
-    <row r="79" spans="1:51" x14ac:dyDescent="0.2">
+      <c r="X78" s="4"/>
+    </row>
+    <row r="79" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A79">
         <f t="shared" si="1"/>
         <v>77</v>
@@ -9911,11 +10141,12 @@
       <c r="U79" s="4"/>
       <c r="V79" s="4"/>
       <c r="W79" s="4"/>
-      <c r="AA79">
+      <c r="X79" s="4"/>
+      <c r="AB79">
         <v>2011</v>
       </c>
     </row>
-    <row r="80" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A80">
         <f t="shared" si="1"/>
         <v>78</v>
@@ -9941,20 +10172,21 @@
       <c r="U80" s="4"/>
       <c r="V80" s="4"/>
       <c r="W80" s="4"/>
-      <c r="X80" s="6" t="s">
+      <c r="X80" s="4"/>
+      <c r="Y80" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="Y80" s="6" t="s">
+      <c r="Z80" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="AR80" s="9">
+      <c r="AS80" s="9">
         <v>-0.2</v>
       </c>
-      <c r="AY80" s="9">
+      <c r="AZ80" s="9">
         <v>-0.23</v>
       </c>
     </row>
-    <row r="81" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A81">
         <f t="shared" si="1"/>
         <v>79</v>
@@ -9976,11 +10208,12 @@
       <c r="U81" s="4"/>
       <c r="V81" s="4"/>
       <c r="W81" s="4"/>
-      <c r="X81" s="6" t="s">
+      <c r="X81" s="4"/>
+      <c r="Y81" s="6" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="82" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A82">
         <f t="shared" si="1"/>
         <v>80</v>
@@ -9996,8 +10229,9 @@
       <c r="U82" s="4"/>
       <c r="V82" s="4"/>
       <c r="W82" s="4"/>
-    </row>
-    <row r="83" spans="1:51" x14ac:dyDescent="0.2">
+      <c r="X82" s="4"/>
+    </row>
+    <row r="83" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A83">
         <f t="shared" si="1"/>
         <v>81</v>
@@ -10013,8 +10247,9 @@
       <c r="U83" s="4"/>
       <c r="V83" s="4"/>
       <c r="W83" s="4"/>
-    </row>
-    <row r="84" spans="1:51" x14ac:dyDescent="0.2">
+      <c r="X83" s="4"/>
+    </row>
+    <row r="84" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A84">
         <f t="shared" si="1"/>
         <v>82</v>
@@ -10036,8 +10271,9 @@
       <c r="U84" s="4"/>
       <c r="V84" s="4"/>
       <c r="W84" s="4"/>
-    </row>
-    <row r="85" spans="1:51" x14ac:dyDescent="0.2">
+      <c r="X84" s="4"/>
+    </row>
+    <row r="85" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A85">
         <f t="shared" ref="A85:A120" si="2">+A84+1</f>
         <v>83</v>
@@ -10059,8 +10295,9 @@
       <c r="U85" s="4"/>
       <c r="V85" s="4"/>
       <c r="W85" s="4"/>
-    </row>
-    <row r="86" spans="1:51" x14ac:dyDescent="0.2">
+      <c r="X85" s="4"/>
+    </row>
+    <row r="86" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A86">
         <f t="shared" si="2"/>
         <v>84</v>
@@ -10085,11 +10322,12 @@
       <c r="U86" s="4"/>
       <c r="V86" s="4"/>
       <c r="W86" s="4"/>
-      <c r="X86" s="6" t="s">
+      <c r="X86" s="4"/>
+      <c r="Y86" s="6" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="87" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A87">
         <f t="shared" si="2"/>
         <v>85</v>
@@ -10111,11 +10349,12 @@
       <c r="U87" s="4"/>
       <c r="V87" s="4"/>
       <c r="W87" s="4"/>
-      <c r="Z87" s="8" t="s">
+      <c r="X87" s="4"/>
+      <c r="AA87" s="8" t="s">
         <v>671</v>
       </c>
     </row>
-    <row r="88" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A88">
         <f t="shared" si="2"/>
         <v>86</v>
@@ -10143,14 +10382,15 @@
       <c r="U88" s="4"/>
       <c r="V88" s="4"/>
       <c r="W88" s="4"/>
-      <c r="X88" s="6" t="s">
+      <c r="X88" s="4"/>
+      <c r="Y88" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Y88" s="6" t="s">
+      <c r="Z88" s="6" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="89" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A89">
         <f t="shared" si="2"/>
         <v>87</v>
@@ -10175,11 +10415,12 @@
       <c r="U89" s="4"/>
       <c r="V89" s="4"/>
       <c r="W89" s="4"/>
-      <c r="X89" s="6" t="s">
+      <c r="X89" s="4"/>
+      <c r="Y89" s="6" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="90" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A90">
         <f t="shared" si="2"/>
         <v>88</v>
@@ -10195,8 +10436,9 @@
       <c r="U90" s="4"/>
       <c r="V90" s="4"/>
       <c r="W90" s="4"/>
-    </row>
-    <row r="91" spans="1:51" x14ac:dyDescent="0.2">
+      <c r="X90" s="4"/>
+    </row>
+    <row r="91" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A91">
         <f t="shared" si="2"/>
         <v>89</v>
@@ -10221,11 +10463,12 @@
       <c r="U91" s="4"/>
       <c r="V91" s="4"/>
       <c r="W91" s="4"/>
-      <c r="X91" s="6" t="s">
+      <c r="X91" s="4"/>
+      <c r="Y91" s="6" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="92" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A92">
         <f t="shared" si="2"/>
         <v>90</v>
@@ -10247,8 +10490,9 @@
       <c r="U92" s="4"/>
       <c r="V92" s="4"/>
       <c r="W92" s="4"/>
-    </row>
-    <row r="93" spans="1:51" x14ac:dyDescent="0.2">
+      <c r="X92" s="4"/>
+    </row>
+    <row r="93" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A93">
         <f t="shared" si="2"/>
         <v>91</v>
@@ -10264,8 +10508,9 @@
       <c r="U93" s="4"/>
       <c r="V93" s="4"/>
       <c r="W93" s="4"/>
-    </row>
-    <row r="94" spans="1:51" x14ac:dyDescent="0.2">
+      <c r="X93" s="4"/>
+    </row>
+    <row r="94" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A94">
         <f t="shared" si="2"/>
         <v>92</v>
@@ -10284,17 +10529,18 @@
       <c r="U94" s="4"/>
       <c r="V94" s="4"/>
       <c r="W94" s="4"/>
-      <c r="AI94" s="9">
+      <c r="X94" s="4"/>
+      <c r="AJ94" s="9">
         <v>0.52</v>
       </c>
-      <c r="AJ94" s="9">
+      <c r="AK94" s="9">
         <v>0.48</v>
       </c>
-      <c r="AY94" s="36">
+      <c r="AZ94" s="36">
         <v>-0.33300000000000002</v>
       </c>
     </row>
-    <row r="95" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A95">
         <f t="shared" si="2"/>
         <v>93</v>
@@ -10319,11 +10565,12 @@
       <c r="U95" s="4"/>
       <c r="V95" s="4"/>
       <c r="W95" s="4"/>
-      <c r="X95" s="6" t="s">
+      <c r="X95" s="4"/>
+      <c r="Y95" s="6" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="96" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A96">
         <f t="shared" si="2"/>
         <v>94</v>
@@ -10339,8 +10586,9 @@
       <c r="U96" s="4"/>
       <c r="V96" s="4"/>
       <c r="W96" s="4"/>
-    </row>
-    <row r="97" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="X96" s="4"/>
+    </row>
+    <row r="97" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A97">
         <f t="shared" si="2"/>
         <v>95</v>
@@ -10362,8 +10610,9 @@
       <c r="U97" s="4"/>
       <c r="V97" s="4"/>
       <c r="W97" s="4"/>
-    </row>
-    <row r="98" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="X97" s="4"/>
+    </row>
+    <row r="98" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A98">
         <f t="shared" si="2"/>
         <v>96</v>
@@ -10387,12 +10636,15 @@
       <c r="V98" s="4">
         <v>578.33704</v>
       </c>
-      <c r="W98" s="4"/>
-      <c r="X98" s="6" t="s">
+      <c r="W98" s="4">
+        <v>1381.1980759999999</v>
+      </c>
+      <c r="X98" s="4"/>
+      <c r="Y98" s="6" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="99" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A99">
         <f t="shared" si="2"/>
         <v>97</v>
@@ -10410,8 +10662,9 @@
       <c r="U99" s="4"/>
       <c r="V99" s="4"/>
       <c r="W99" s="4"/>
-    </row>
-    <row r="100" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="X99" s="4"/>
+    </row>
+    <row r="100" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A100">
         <f t="shared" si="2"/>
         <v>98</v>
@@ -10429,11 +10682,12 @@
       <c r="U100" s="4"/>
       <c r="V100" s="4"/>
       <c r="W100" s="4"/>
-      <c r="X100" s="6" t="s">
+      <c r="X100" s="4"/>
+      <c r="Y100" s="6" t="s">
         <v>663</v>
       </c>
     </row>
-    <row r="101" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A101">
         <f t="shared" si="2"/>
         <v>99</v>
@@ -10457,17 +10711,18 @@
       <c r="U101" s="4"/>
       <c r="V101" s="4"/>
       <c r="W101" s="4"/>
-      <c r="X101" s="6" t="s">
+      <c r="X101" s="4"/>
+      <c r="Y101" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="Y101" s="6" t="s">
+      <c r="Z101" s="6" t="s">
         <v>220</v>
       </c>
-      <c r="Z101" s="8" t="s">
+      <c r="AA101" s="8" t="s">
         <v>654</v>
       </c>
     </row>
-    <row r="102" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A102">
         <f t="shared" si="2"/>
         <v>100</v>
@@ -10485,8 +10740,9 @@
       <c r="U102" s="4"/>
       <c r="V102" s="4"/>
       <c r="W102" s="4"/>
-    </row>
-    <row r="103" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="X102" s="4"/>
+    </row>
+    <row r="103" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A103">
         <f t="shared" si="2"/>
         <v>101</v>
@@ -10494,11 +10750,11 @@
       <c r="B103" t="s">
         <v>61</v>
       </c>
-      <c r="X103" s="6" t="s">
+      <c r="Y103" s="6" t="s">
         <v>657</v>
       </c>
     </row>
-    <row r="104" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A104">
         <f t="shared" si="2"/>
         <v>102</v>
@@ -10507,7 +10763,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="105" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A105">
         <f t="shared" si="2"/>
         <v>103</v>
@@ -10516,7 +10772,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="106" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A106">
         <f t="shared" si="2"/>
         <v>104</v>
@@ -10525,7 +10781,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="107" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A107">
         <f t="shared" si="2"/>
         <v>105</v>
@@ -10537,7 +10793,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="108" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A108">
         <f t="shared" si="2"/>
         <v>106</v>
@@ -10546,7 +10802,7 @@
         <v>1327</v>
       </c>
     </row>
-    <row r="109" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A109">
         <f>+A107+1</f>
         <v>106</v>
@@ -10555,7 +10811,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="110" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A110">
         <f t="shared" si="2"/>
         <v>107</v>
@@ -10564,7 +10820,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="111" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A111">
         <f t="shared" si="2"/>
         <v>108</v>
@@ -10573,7 +10829,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="112" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A112">
         <f t="shared" si="2"/>
         <v>109</v>
@@ -11265,7 +11521,7 @@
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A188">
-        <f t="shared" ref="A188:A203" si="4">+A187+1</f>
+        <f t="shared" ref="A188:A209" si="4">+A187+1</f>
         <v>184</v>
       </c>
       <c r="B188" t="s">
@@ -11308,7 +11564,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="193" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A193">
         <f t="shared" si="4"/>
         <v>189</v>
@@ -11317,7 +11573,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="194" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A194">
         <f t="shared" si="4"/>
         <v>190</v>
@@ -11326,7 +11582,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="195" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A195">
         <f t="shared" si="4"/>
         <v>191</v>
@@ -11335,7 +11591,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="196" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A196">
         <f t="shared" si="4"/>
         <v>192</v>
@@ -11344,7 +11600,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="197" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A197">
         <f t="shared" si="4"/>
         <v>193</v>
@@ -11356,7 +11612,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="198" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A198">
         <f t="shared" si="4"/>
         <v>194</v>
@@ -11365,7 +11621,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="199" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A199">
         <f t="shared" si="4"/>
         <v>195</v>
@@ -11374,7 +11630,7 @@
         <v>1123</v>
       </c>
     </row>
-    <row r="200" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200">
         <f t="shared" si="4"/>
         <v>196</v>
@@ -11383,7 +11639,7 @@
         <v>1124</v>
       </c>
     </row>
-    <row r="201" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A201">
         <f t="shared" si="4"/>
         <v>197</v>
@@ -11392,7 +11648,7 @@
         <v>1321</v>
       </c>
     </row>
-    <row r="202" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A202">
         <f t="shared" si="4"/>
         <v>198</v>
@@ -11401,7 +11657,7 @@
         <v>1209</v>
       </c>
     </row>
-    <row r="203" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A203">
         <f t="shared" si="4"/>
         <v>199</v>
@@ -11410,239 +11666,316 @@
         <v>1490</v>
       </c>
     </row>
-    <row r="206" spans="1:26" s="22" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B206" s="22" t="s">
+    <row r="204" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A204">
+        <f t="shared" si="4"/>
+        <v>200</v>
+      </c>
+      <c r="B204" s="2" t="s">
+        <v>1570</v>
+      </c>
+      <c r="C204" t="s">
+        <v>1571</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A205">
+        <f t="shared" si="4"/>
+        <v>201</v>
+      </c>
+      <c r="B205" s="2" t="s">
+        <v>1572</v>
+      </c>
+      <c r="C205" t="s">
+        <v>1576</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A206">
+        <f t="shared" si="4"/>
+        <v>202</v>
+      </c>
+      <c r="B206" s="2" t="s">
+        <v>1573</v>
+      </c>
+      <c r="C206" t="s">
+        <v>1577</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A207">
+        <f t="shared" si="4"/>
+        <v>203</v>
+      </c>
+      <c r="B207" s="2" t="s">
+        <v>1578</v>
+      </c>
+      <c r="C207" t="s">
+        <v>1579</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A208">
+        <f t="shared" si="4"/>
+        <v>204</v>
+      </c>
+      <c r="B208" s="2" t="s">
+        <v>1574</v>
+      </c>
+      <c r="C208" t="s">
+        <v>1580</v>
+      </c>
+    </row>
+    <row r="209" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A209">
+        <f t="shared" si="4"/>
+        <v>205</v>
+      </c>
+      <c r="B209" s="2" t="s">
+        <v>1575</v>
+      </c>
+      <c r="C209" t="s">
+        <v>1581</v>
+      </c>
+    </row>
+    <row r="210" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="B210" s="2"/>
+    </row>
+    <row r="212" spans="1:27" s="22" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B212" s="22" t="s">
         <v>1211</v>
       </c>
-      <c r="D206" s="23"/>
-      <c r="E206" s="24"/>
-      <c r="F206" s="24"/>
-      <c r="G206" s="24"/>
-      <c r="H206" s="24"/>
-      <c r="I206" s="23"/>
-      <c r="J206" s="23"/>
-      <c r="K206" s="23"/>
-      <c r="L206" s="23"/>
-      <c r="M206" s="23"/>
-      <c r="N206" s="23"/>
-      <c r="O206" s="23"/>
-      <c r="P206" s="23"/>
-      <c r="Q206" s="23"/>
-      <c r="R206" s="23"/>
-      <c r="S206" s="23"/>
-      <c r="T206" s="23"/>
-      <c r="U206" s="23"/>
-      <c r="V206" s="23"/>
-      <c r="W206" s="23"/>
-      <c r="X206" s="25"/>
-      <c r="Y206" s="25"/>
-      <c r="Z206" s="26"/>
-    </row>
-    <row r="207" spans="1:26" s="22" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B207" s="22" t="s">
+      <c r="D212" s="23"/>
+      <c r="E212" s="24"/>
+      <c r="F212" s="24"/>
+      <c r="G212" s="24"/>
+      <c r="H212" s="24"/>
+      <c r="I212" s="23"/>
+      <c r="J212" s="23"/>
+      <c r="K212" s="23"/>
+      <c r="L212" s="23"/>
+      <c r="M212" s="23"/>
+      <c r="N212" s="23"/>
+      <c r="O212" s="23"/>
+      <c r="P212" s="23"/>
+      <c r="Q212" s="23"/>
+      <c r="R212" s="23"/>
+      <c r="S212" s="23"/>
+      <c r="T212" s="23"/>
+      <c r="U212" s="23"/>
+      <c r="V212" s="23"/>
+      <c r="W212" s="23"/>
+      <c r="X212" s="23"/>
+      <c r="Y212" s="25"/>
+      <c r="Z212" s="25"/>
+      <c r="AA212" s="26"/>
+    </row>
+    <row r="213" spans="1:27" s="22" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B213" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="D207" s="23"/>
-      <c r="E207" s="24"/>
-      <c r="F207" s="24"/>
-      <c r="G207" s="24"/>
-      <c r="H207" s="24"/>
-      <c r="I207" s="23"/>
-      <c r="J207" s="23"/>
-      <c r="K207" s="23"/>
-      <c r="L207" s="23"/>
-      <c r="M207" s="23"/>
-      <c r="N207" s="23"/>
-      <c r="O207" s="23"/>
-      <c r="P207" s="23"/>
-      <c r="Q207" s="23"/>
-      <c r="R207" s="23"/>
-      <c r="S207" s="23"/>
-      <c r="T207" s="23"/>
-      <c r="U207" s="23"/>
-      <c r="V207" s="23"/>
-      <c r="W207" s="23"/>
-      <c r="X207" s="25" t="s">
+      <c r="D213" s="23"/>
+      <c r="E213" s="24"/>
+      <c r="F213" s="24"/>
+      <c r="G213" s="24"/>
+      <c r="H213" s="24"/>
+      <c r="I213" s="23"/>
+      <c r="J213" s="23"/>
+      <c r="K213" s="23"/>
+      <c r="L213" s="23"/>
+      <c r="M213" s="23"/>
+      <c r="N213" s="23"/>
+      <c r="O213" s="23"/>
+      <c r="P213" s="23"/>
+      <c r="Q213" s="23"/>
+      <c r="R213" s="23"/>
+      <c r="S213" s="23"/>
+      <c r="T213" s="23"/>
+      <c r="U213" s="23"/>
+      <c r="V213" s="23"/>
+      <c r="W213" s="23"/>
+      <c r="X213" s="23"/>
+      <c r="Y213" s="25" t="s">
         <v>654</v>
       </c>
-      <c r="Y207" s="25"/>
-      <c r="Z207" s="26"/>
-    </row>
-    <row r="208" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="B208" s="22" t="s">
+      <c r="Z213" s="25"/>
+      <c r="AA213" s="26"/>
+    </row>
+    <row r="214" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="B214" s="22" t="s">
         <v>1269</v>
       </c>
     </row>
-    <row r="209" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B209" s="22" t="s">
+    <row r="215" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="B215" s="22" t="s">
         <v>1270</v>
       </c>
     </row>
-    <row r="210" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B210" s="22" t="s">
+    <row r="216" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="B216" s="22" t="s">
         <v>1271</v>
       </c>
     </row>
-    <row r="211" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B211" s="22" t="s">
+    <row r="217" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="B217" s="22" t="s">
         <v>1272</v>
       </c>
     </row>
-    <row r="212" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B212" s="22" t="s">
+    <row r="218" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="B218" s="22" t="s">
         <v>1273</v>
       </c>
-      <c r="C212" t="s">
+      <c r="C218" t="s">
         <v>1320</v>
       </c>
     </row>
-    <row r="213" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B213" s="22" t="s">
+    <row r="219" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="B219" s="22" t="s">
         <v>1274</v>
       </c>
     </row>
-    <row r="214" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B214" s="22" t="s">
+    <row r="220" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="B220" s="22" t="s">
         <v>1275</v>
       </c>
     </row>
-    <row r="215" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B215" s="22" t="s">
+    <row r="221" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="B221" s="22" t="s">
         <v>1276</v>
       </c>
     </row>
-    <row r="216" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B216" s="22" t="s">
+    <row r="222" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="B222" s="22" t="s">
         <v>1277</v>
       </c>
     </row>
-    <row r="217" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B217" s="22" t="s">
+    <row r="223" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="B223" s="22" t="s">
         <v>1278</v>
       </c>
     </row>
-    <row r="218" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B218" s="22" t="s">
+    <row r="224" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="B224" s="22" t="s">
         <v>724</v>
-      </c>
-    </row>
-    <row r="219" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B219" s="22" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="220" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B220" s="22" t="s">
-        <v>1279</v>
-      </c>
-    </row>
-    <row r="221" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B221" s="22" t="s">
-        <v>1280</v>
-      </c>
-    </row>
-    <row r="222" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B222" s="22" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="223" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B223" s="22" t="s">
-        <v>1281</v>
-      </c>
-    </row>
-    <row r="224" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B224" s="22" t="s">
-        <v>1282</v>
       </c>
     </row>
     <row r="225" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B225" s="22" t="s">
-        <v>1283</v>
+        <v>75</v>
       </c>
     </row>
     <row r="226" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B226" s="22" t="s">
-        <v>1284</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="227" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B227" s="22" t="s">
-        <v>1285</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="228" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B228" s="22" t="s">
-        <v>1286</v>
+        <v>195</v>
       </c>
     </row>
     <row r="229" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B229" s="22" t="s">
-        <v>43</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="230" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B230" s="22" t="s">
-        <v>1287</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="231" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B231" s="22" t="s">
-        <v>1288</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="232" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B232" s="22" t="s">
-        <v>1289</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="233" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B233" s="22" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="234" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B234" s="22" t="s">
-        <v>187</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="235" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B235" s="22" t="s">
-        <v>1291</v>
+        <v>43</v>
       </c>
     </row>
     <row r="236" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B236" s="22" t="s">
-        <v>189</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="237" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B237" s="22" t="s">
-        <v>1292</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="238" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B238" s="22" t="s">
-        <v>1293</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="239" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B239" s="22" t="s">
-        <v>107</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="240" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B240" s="22" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
     </row>
     <row r="241" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B241" s="22" t="s">
-        <v>1306</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="242" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B242" s="22" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="243" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B243" s="22" t="s">
+        <v>1292</v>
+      </c>
+    </row>
+    <row r="244" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B244" s="22" t="s">
+        <v>1293</v>
+      </c>
+    </row>
+    <row r="245" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B245" s="22" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="246" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B246" s="22" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="247" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B247" s="22" t="s">
+        <v>1306</v>
+      </c>
+    </row>
+    <row r="248" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B248" s="22" t="s">
         <v>1307</v>
       </c>
     </row>
@@ -12226,10 +12559,70 @@
     <hyperlink ref="W3" r:id="rId576" display="https://www.sec.gov/Archives/edgar/data/1067983/000119312525282901/0001193125-25-282901-index.htm" xr:uid="{290783D6-41CD-4CF5-99DA-00FFD7CF7A3E}"/>
     <hyperlink ref="W4" r:id="rId577" display="https://www.sec.gov/Archives/edgar/data/1273087/000127308725000034/0001273087-25-000034-index.htm" xr:uid="{DC39D9C4-C0B9-40A2-B7B7-BD1D94B78BD1}"/>
     <hyperlink ref="W5" r:id="rId578" display="https://www.sec.gov/Archives/edgar/data/1423053/000110465925112514/0001104659-25-112514-index.htm" xr:uid="{99277AF0-0DA5-4378-8784-28C399D83469}"/>
+    <hyperlink ref="X3" r:id="rId579" display="https://www.sec.gov/Archives/edgar/data/1067983/000119312526054580/0001193125-26-054580-index.htm" xr:uid="{172DA7CF-349C-44B3-A0DC-D9E0542360B4}"/>
+    <hyperlink ref="X63" r:id="rId580" display="https://www.sec.gov/Archives/edgar/data/1061768/000106176826000005/0001061768-26-000005-index.htm" xr:uid="{FDB2AA42-38E1-43A3-AA0C-0C465903C5A5}"/>
+    <hyperlink ref="X14" r:id="rId581" display="https://www.sec.gov/Archives/edgar/data/1647251/000164725126000002/0001647251-26-000002-index.htm" xr:uid="{8E7CA14F-E8BD-4E91-A35E-1932815E9E4A}"/>
+    <hyperlink ref="W14" r:id="rId582" display="https://www.sec.gov/Archives/edgar/data/1647251/000164725125000014/0001647251-25-000014-index.htm" xr:uid="{84936686-4EC2-4C64-A10F-FA9A8AF0B6C8}"/>
+    <hyperlink ref="X16" r:id="rId583" display="https://www.sec.gov/Archives/edgar/data/1637460/000163746026000001/0001637460-26-000001-index.htm" xr:uid="{635A0B2D-9BF9-4E0F-B797-32D85AFC063D}"/>
+    <hyperlink ref="X25" r:id="rId584" display="https://www.sec.gov/Archives/edgar/data/909661/000090883426000087/0000908834-26-000087-index.htm" xr:uid="{B05FFD1E-12D6-4BF5-A8CA-3FE210DE67F9}"/>
+    <hyperlink ref="W25" r:id="rId585" display="https://www.sec.gov/Archives/edgar/data/909661/000090883425000353/0000908834-25-000353-index.htm" xr:uid="{ADA58C4A-54BC-47EC-9008-B5BB887FBCA6}"/>
+    <hyperlink ref="W98" r:id="rId586" display="https://www.sec.gov/Archives/edgar/data/1649339/000164933925000007/0001649339-25-000007-index.htm" xr:uid="{36C20724-27A3-4B24-AA1F-9F2BF3E81025}"/>
+    <hyperlink ref="X26" r:id="rId587" display="https://www.sec.gov/Archives/edgar/data/1393825/000139382526000021/0001393825-26-000021-index.htm" xr:uid="{E1C0A921-2BA1-4875-8327-EE13C5672A65}"/>
+    <hyperlink ref="X4" r:id="rId588" display="https://www.sec.gov/Archives/edgar/data/1273087/000127308726000002/0001273087-26-000002-index.htm" xr:uid="{01DC177D-C33E-443C-8E40-2C1B4D38D1DE}"/>
+    <hyperlink ref="X5" r:id="rId589" display="https://www.sec.gov/Archives/edgar/data/1423053/000110465926016408/0001104659-26-016408-index.htm" xr:uid="{FC3C3FE0-DA4E-4B9C-8528-AD77D4790D2A}"/>
+    <hyperlink ref="X6" r:id="rId590" display="https://www.sec.gov/Archives/edgar/data/1595888/000159588826000023/0001595888-26-000023-index.htm" xr:uid="{D59EEAB0-8C8B-4187-8415-57301F749C48}"/>
+    <hyperlink ref="W6" r:id="rId591" display="https://www.sec.gov/Archives/edgar/data/1595888/000159588825000155/0001595888-25-000155-index.htm" xr:uid="{A1A598C6-F985-42CA-9D59-BCF86AADF35F}"/>
+    <hyperlink ref="W7" r:id="rId592" display="https://www.sec.gov/Archives/edgar/data/1318757/000131875725000046/0001318757-25-000046-index.htm" xr:uid="{E936F497-2B07-4500-8FC2-9B187F3700EC}"/>
+    <hyperlink ref="X8" r:id="rId593" display="https://www.sec.gov/Archives/edgar/data/1167557/000108514626000240/0001085146-26-000240-index.htm" xr:uid="{2C8EBD41-3922-46F5-B0D3-1ECB11FDBC14}"/>
+    <hyperlink ref="X9" r:id="rId594" display="https://www.sec.gov/Archives/edgar/data/1037389/000103738926000023/0001037389-26-000023-index.htm" xr:uid="{1A1907A4-37BC-4CDB-B2DA-5DB162922E81}"/>
+    <hyperlink ref="W9" r:id="rId595" display="https://www.sec.gov/Archives/edgar/data/1037389/000103738925000064/0001037389-25-000064-index.htm" xr:uid="{6F11A574-90C6-436A-AD4A-F6C62FC2469B}"/>
+    <hyperlink ref="X10" r:id="rId596" display="https://www.sec.gov/Archives/edgar/data/1446194/000144619426000001/0001446194-26-000001-index.htm" xr:uid="{1766D65F-3441-4974-AB07-5C82658A488A}"/>
+    <hyperlink ref="X11" r:id="rId597" display="https://www.sec.gov/Archives/edgar/data/1729829/000172982926000002/0001729829-26-000002-index.htm" xr:uid="{3AF607B2-D056-4426-9F39-DE09A5466268}"/>
+    <hyperlink ref="W11" r:id="rId598" display="https://www.sec.gov/Archives/edgar/data/1729829/000172982925000053/0001729829-25-000053-index.htm" xr:uid="{E7A16820-7555-4CE0-8D9B-98B298BEEF30}"/>
+    <hyperlink ref="X12" r:id="rId599" display="https://www.sec.gov/Archives/edgar/data/1478735/000089914026000225/0000899140-26-000225-index.htm" xr:uid="{F32F9896-072B-4F2C-A3C7-CAE10FA85D10}"/>
+    <hyperlink ref="W12" r:id="rId600" display="https://www.sec.gov/Archives/edgar/data/1478735/000089914025001279/0000899140-25-001279-index.htm" xr:uid="{95D0D110-2FF1-41A7-B783-66066C74815B}"/>
+    <hyperlink ref="X13" r:id="rId601" display="https://www.sec.gov/Archives/edgar/data/1009207/000110465926016332/0001104659-26-016332-index.htm" xr:uid="{E4EC3E0F-8A97-4AA6-8EEB-EE2BCF24C9E7}"/>
+    <hyperlink ref="W13" r:id="rId602" display="https://www.sec.gov/Archives/edgar/data/1009207/000110465925112505/0001104659-25-112505-index.htm" xr:uid="{492468DB-D0D8-43CD-9556-D23ED910912D}"/>
+    <hyperlink ref="X15" r:id="rId603" display="https://www.sec.gov/Archives/edgar/data/1218710/000119312526054303/0001193125-26-054303-index.htm" xr:uid="{07E058C0-910C-4FE8-BEDC-01624FAF49C0}"/>
+    <hyperlink ref="W15" r:id="rId604" display="https://www.sec.gov/Archives/edgar/data/1218710/000119312525282267/0001193125-25-282267-index.htm" xr:uid="{344FDE68-07C2-47FC-9DC7-91F0E50B19B8}"/>
+    <hyperlink ref="W16" r:id="rId605" display="https://www.sec.gov/Archives/edgar/data/1637460/000163746025000003/0001637460-25-000003-index.htm" xr:uid="{98F5B6E7-98A8-4D00-9AFC-3C3480B7A691}"/>
+    <hyperlink ref="X17" r:id="rId606" display="https://www.sec.gov/Archives/edgar/data/1603466/000090266426001100/0000902664-26-001100-index.htm" xr:uid="{BE6C4BE7-69EB-468E-A2B4-DBEDB60F907F}"/>
+    <hyperlink ref="W17" r:id="rId607" display="https://www.sec.gov/Archives/edgar/data/1603466/000090266425005042/0000902664-25-005042-index.htm" xr:uid="{7A3C8223-F253-48CA-82AB-3D4BDD5EB696}"/>
+    <hyperlink ref="X18" r:id="rId608" display="https://www.sec.gov/Archives/edgar/data/1556921/000142050626000565/0001420506-26-000565-index.htm" xr:uid="{9B605A6C-860F-4584-8D0A-CD61256AA164}"/>
+    <hyperlink ref="W18" r:id="rId609" display="https://www.sec.gov/Archives/edgar/data/1556921/000121465925016646/0001214659-25-016646-index.htm" xr:uid="{028B7A52-892D-42CC-A1C9-6A30D2AAB57A}"/>
+    <hyperlink ref="X19" r:id="rId610" display="https://www.sec.gov/Archives/edgar/data/1103804/000110380426000002/0001103804-26-000002-index.htm" xr:uid="{4F5EC96B-82CD-41E7-8B90-06D26C2960FB}"/>
+    <hyperlink ref="W19" r:id="rId611" display="https://www.sec.gov/Archives/edgar/data/1103804/000110380425000010/0001103804-25-000010-index.htm" xr:uid="{89DCD08D-00E4-4877-97D9-BE53FD7A53B3}"/>
+    <hyperlink ref="X20" r:id="rId612" display="https://www.sec.gov/Archives/edgar/data/1135730/000091957426001239/0000919574-26-001239-index.htm" xr:uid="{F6405659-547E-49ED-B0C8-AD1EABB1DB9B}"/>
+    <hyperlink ref="W20" r:id="rId613" display="https://www.sec.gov/Archives/edgar/data/1135730/000091957425006976/0000919574-25-006976-index.htm" xr:uid="{FAC60CC9-177C-4857-A2AF-96467FAE8572}"/>
+    <hyperlink ref="X21" r:id="rId614" display="https://www.sec.gov/Archives/edgar/data/1167483/000091957426001143/0000919574-26-001143-index.htm" xr:uid="{B01B7A4B-573E-4232-B853-E44F199F16D1}"/>
+    <hyperlink ref="W21" r:id="rId615" display="https://www.sec.gov/Archives/edgar/data/1167483/000091957425006931/0000919574-25-006931-index.htm" xr:uid="{39963B98-3DF2-4C73-B905-CFAC834F9DE5}"/>
+    <hyperlink ref="X22" r:id="rId616" display="https://www.sec.gov/Archives/edgar/data/1350694/000135069426000001/0001350694-26-000001-index.htm" xr:uid="{62801BD1-EC13-45F6-8AF3-BBB46B09FE30}"/>
+    <hyperlink ref="W22" r:id="rId617" display="https://www.sec.gov/Archives/edgar/data/1350694/000117266125004777/0001172661-25-004777-index.htm" xr:uid="{7A2C58C4-6D57-4F32-B76E-1E26C2E58D12}"/>
+    <hyperlink ref="X23" r:id="rId618" display="https://www.sec.gov/Archives/edgar/data/1454027/000145402726000001/0001454027-26-000001-index.htm" xr:uid="{ECD20A8F-A0F7-4564-A2DD-0198D9A9F892}"/>
+    <hyperlink ref="W23" r:id="rId619" display="https://www.sec.gov/Archives/edgar/data/1454027/000145402725000007/0001454027-25-000007-index.htm" xr:uid="{F8C16428-33D4-4E06-90AA-D5E591089B04}"/>
+    <hyperlink ref="X24" r:id="rId620" display="https://www.sec.gov/Archives/edgar/data/1453072/000117266126000737/0001172661-26-000737-index.htm" xr:uid="{D2278DDB-C952-454F-AFFD-832C70721AD0}"/>
+    <hyperlink ref="W24" r:id="rId621" display="https://www.sec.gov/Archives/edgar/data/1453072/000117266125005150/0001172661-25-005150-index.htm" xr:uid="{113B22E6-A064-4183-BCAF-5ECE1E6E5B88}"/>
+    <hyperlink ref="W26" r:id="rId622" display="https://www.sec.gov/Archives/edgar/data/1393825/000139382525000090/0001393825-25-000090-index.htm" xr:uid="{A6C9A71B-ADAA-4C6D-AFB0-08B37DF670CF}"/>
+    <hyperlink ref="X27" r:id="rId623" display="https://www.sec.gov/Archives/edgar/data/1410830/000117266126000728/0001172661-26-000728-index.htm" xr:uid="{C64E4305-218F-4927-BE66-2B5CC6298D2C}"/>
+    <hyperlink ref="W27" r:id="rId624" display="https://www.sec.gov/Archives/edgar/data/1410830/000117266125004764/0001172661-25-004764-index.htm" xr:uid="{EE48FFFA-4C2C-4321-A2FA-C669F7F9E1A3}"/>
+    <hyperlink ref="X28" r:id="rId625" display="https://www.sec.gov/Archives/edgar/data/1061165/000090266426001084/0000902664-26-001084-index.htm" xr:uid="{E73990D1-6E66-4BE1-9F89-5750D62A4653}"/>
+    <hyperlink ref="W28" r:id="rId626" display="https://www.sec.gov/Archives/edgar/data/1061165/000090266425004988/0000902664-25-004988-index.htm" xr:uid="{BC127516-264C-482E-94DF-07703C0D0663}"/>
+    <hyperlink ref="X29" r:id="rId627" display="https://www.sec.gov/Archives/edgar/data/1784547/000117266126000861/0001172661-26-000861-index.htm" xr:uid="{0E684CD0-C711-4F00-B77A-7D7C33EDA6AB}"/>
+    <hyperlink ref="W29" r:id="rId628" display="https://www.sec.gov/Archives/edgar/data/1784547/000117266125004991/0001172661-25-004991-index.htm" xr:uid="{B3369319-A80E-4AEB-B6D7-758BAD75A207}"/>
+    <hyperlink ref="X30" r:id="rId629" display="https://www.sec.gov/Archives/edgar/data/1336528/000117266126001091/0001172661-26-001091-index.htm" xr:uid="{3839FE1E-C15D-411F-83D9-D4563EF2DDB5}"/>
+    <hyperlink ref="W30" r:id="rId630" display="https://www.sec.gov/Archives/edgar/data/1336528/000117266125005039/0001172661-25-005039-index.htm" xr:uid="{8B68D6EB-6D09-4585-8C12-72C5DC9DE796}"/>
+    <hyperlink ref="X31" r:id="rId631" display="https://www.sec.gov/Archives/edgar/data/1791786/000101359426000272/0001013594-26-000272-index.htm" xr:uid="{DA809EEC-FEC6-494E-8E3F-2B8F0BB91B5C}"/>
+    <hyperlink ref="W31" r:id="rId632" display="https://www.sec.gov/Archives/edgar/data/1791786/000101359425001440/0001013594-25-001440-index.htm" xr:uid="{76282B8B-9E45-42F8-A2BD-AD6A546D5807}"/>
+    <hyperlink ref="B204" r:id="rId633" xr:uid="{6E650FC5-9DD9-4CEA-A597-2A39797A6D2B}"/>
+    <hyperlink ref="B205" r:id="rId634" xr:uid="{74EE2AF6-56AE-4862-BD51-F5D374701FA1}"/>
+    <hyperlink ref="B206" r:id="rId635" xr:uid="{2350FD2E-2640-4C09-8AE2-CE07F5FF47F9}"/>
+    <hyperlink ref="B207" r:id="rId636" xr:uid="{F5480301-9AD7-424D-A7C3-63820D49E8C5}"/>
+    <hyperlink ref="B208" r:id="rId637" xr:uid="{E838595A-4E14-49EA-BF17-C7E8603F0B21}"/>
+    <hyperlink ref="B209" r:id="rId638" xr:uid="{0B08BEEF-641E-4803-BFB7-7F2843A49571}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId579"/>
-  <legacyDrawing r:id="rId580"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId639"/>
+  <legacyDrawing r:id="rId640"/>
 </worksheet>
 </file>
 

--- a/Hedge Funds (1).xlsx
+++ b/Hedge Funds (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{552203E9-0CAA-44ED-94A8-CC10B5CC73F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBF24C41-075E-4EEC-8217-71E82BF93C0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="225" yWindow="390" windowWidth="38175" windowHeight="15240" xr2:uid="{18689D26-F1F3-46B4-82BE-041D095397EB}"/>
   </bookViews>
@@ -11605,7 +11605,7 @@
         <f t="shared" si="4"/>
         <v>193</v>
       </c>
-      <c r="B197" t="s">
+      <c r="B197" s="2" t="s">
         <v>231</v>
       </c>
       <c r="C197" t="s">
@@ -12619,10 +12619,11 @@
     <hyperlink ref="B207" r:id="rId636" xr:uid="{F5480301-9AD7-424D-A7C3-63820D49E8C5}"/>
     <hyperlink ref="B208" r:id="rId637" xr:uid="{E838595A-4E14-49EA-BF17-C7E8603F0B21}"/>
     <hyperlink ref="B209" r:id="rId638" xr:uid="{0B08BEEF-641E-4803-BFB7-7F2843A49571}"/>
+    <hyperlink ref="B197" r:id="rId639" xr:uid="{57211A5D-F080-4C13-A991-6C2745F91A4D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId639"/>
-  <legacyDrawing r:id="rId640"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId640"/>
+  <legacyDrawing r:id="rId641"/>
 </worksheet>
 </file>
 

--- a/Hedge Funds (1).xlsx
+++ b/Hedge Funds (1).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBF24C41-075E-4EEC-8217-71E82BF93C0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{552D5523-7C5F-4345-8A14-DFC373C28231}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="390" windowWidth="38175" windowHeight="15240" xr2:uid="{18689D26-F1F3-46B4-82BE-041D095397EB}"/>
+    <workbookView xWindow="225" yWindow="2730" windowWidth="38175" windowHeight="15240" xr2:uid="{18689D26-F1F3-46B4-82BE-041D095397EB}"/>
   </bookViews>
   <sheets>
     <sheet name="Hedge" sheetId="1" r:id="rId1"/>
@@ -627,7 +627,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2274" uniqueCount="1582">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2275" uniqueCount="1582">
   <si>
     <t>Name</t>
   </si>
@@ -10172,7 +10172,9 @@
       <c r="U80" s="4"/>
       <c r="V80" s="4"/>
       <c r="W80" s="4"/>
-      <c r="X80" s="4"/>
+      <c r="X80" s="4">
+        <v>2047.9987269999999</v>
+      </c>
       <c r="Y80" s="6" t="s">
         <v>101</v>
       </c>
@@ -11564,7 +11566,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A193">
         <f t="shared" si="4"/>
         <v>189</v>
@@ -11573,7 +11575,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A194">
         <f t="shared" si="4"/>
         <v>190</v>
@@ -11582,7 +11584,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A195">
         <f t="shared" si="4"/>
         <v>191</v>
@@ -11591,7 +11593,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A196">
         <f t="shared" si="4"/>
         <v>192</v>
@@ -11600,7 +11602,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A197">
         <f t="shared" si="4"/>
         <v>193</v>
@@ -11611,8 +11613,14 @@
       <c r="C197" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="X197" s="4">
+        <v>3612.1441329999998</v>
+      </c>
+      <c r="Y197" s="6" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="198" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A198">
         <f t="shared" si="4"/>
         <v>194</v>
@@ -11621,7 +11629,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A199">
         <f t="shared" si="4"/>
         <v>195</v>
@@ -11630,7 +11638,7 @@
         <v>1123</v>
       </c>
     </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A200">
         <f t="shared" si="4"/>
         <v>196</v>
@@ -11639,7 +11647,7 @@
         <v>1124</v>
       </c>
     </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A201">
         <f t="shared" si="4"/>
         <v>197</v>
@@ -11648,7 +11656,7 @@
         <v>1321</v>
       </c>
     </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A202">
         <f t="shared" si="4"/>
         <v>198</v>
@@ -11657,7 +11665,7 @@
         <v>1209</v>
       </c>
     </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A203">
         <f t="shared" si="4"/>
         <v>199</v>
@@ -11666,7 +11674,7 @@
         <v>1490</v>
       </c>
     </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A204">
         <f t="shared" si="4"/>
         <v>200</v>
@@ -11678,7 +11686,7 @@
         <v>1571</v>
       </c>
     </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A205">
         <f t="shared" si="4"/>
         <v>201</v>
@@ -11690,7 +11698,7 @@
         <v>1576</v>
       </c>
     </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A206">
         <f t="shared" si="4"/>
         <v>202</v>
@@ -11702,7 +11710,7 @@
         <v>1577</v>
       </c>
     </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A207">
         <f t="shared" si="4"/>
         <v>203</v>
@@ -11714,7 +11722,7 @@
         <v>1579</v>
       </c>
     </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A208">
         <f t="shared" si="4"/>
         <v>204</v>
@@ -12620,10 +12628,12 @@
     <hyperlink ref="B208" r:id="rId637" xr:uid="{E838595A-4E14-49EA-BF17-C7E8603F0B21}"/>
     <hyperlink ref="B209" r:id="rId638" xr:uid="{0B08BEEF-641E-4803-BFB7-7F2843A49571}"/>
     <hyperlink ref="B197" r:id="rId639" xr:uid="{57211A5D-F080-4C13-A991-6C2745F91A4D}"/>
+    <hyperlink ref="X80" r:id="rId640" display="https://www.sec.gov/Archives/edgar/data/1079114/000117266124001512/0001172661-24-001512-index.htm" xr:uid="{29A13787-56B5-45C0-8D77-D395490EA1B0}"/>
+    <hyperlink ref="X197" r:id="rId641" display="https://www.sec.gov/Archives/edgar/data/1960830/000091957426001016/0000919574-26-001016-index.htm" xr:uid="{6361078E-F13D-4E19-A00E-CCBE2355774B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId640"/>
-  <legacyDrawing r:id="rId641"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId642"/>
+  <legacyDrawing r:id="rId643"/>
 </worksheet>
 </file>
 

--- a/Hedge Funds (1).xlsx
+++ b/Hedge Funds (1).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{552D5523-7C5F-4345-8A14-DFC373C28231}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D50C59D-0560-4817-8950-1EC92996ED48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="2730" windowWidth="38175" windowHeight="15240" xr2:uid="{18689D26-F1F3-46B4-82BE-041D095397EB}"/>
+    <workbookView xWindow="225" yWindow="4290" windowWidth="38175" windowHeight="15240" xr2:uid="{18689D26-F1F3-46B4-82BE-041D095397EB}"/>
   </bookViews>
   <sheets>
     <sheet name="Hedge" sheetId="1" r:id="rId1"/>
@@ -627,7 +627,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2275" uniqueCount="1582">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2280" uniqueCount="1587">
   <si>
     <t>Name</t>
   </si>
@@ -5373,6 +5373,21 @@
   </si>
   <si>
     <t>Keith Meister</t>
+  </si>
+  <si>
+    <t>Situational Awarness</t>
+  </si>
+  <si>
+    <t>Leopold Aschenbrenner</t>
+  </si>
+  <si>
+    <t>SF</t>
+  </si>
+  <si>
+    <t>Focus on AI</t>
+  </si>
+  <si>
+    <t>https://situational-awareness.ai/</t>
   </si>
 </sst>
 </file>
@@ -11523,7 +11538,7 @@
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A188">
-        <f t="shared" ref="A188:A209" si="4">+A187+1</f>
+        <f t="shared" ref="A188:A210" si="4">+A187+1</f>
         <v>184</v>
       </c>
       <c r="B188" t="s">
@@ -11734,7 +11749,7 @@
         <v>1580</v>
       </c>
     </row>
-    <row r="209" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A209">
         <f t="shared" si="4"/>
         <v>205</v>
@@ -11746,10 +11761,31 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="210" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="B210" s="2"/>
-    </row>
-    <row r="212" spans="1:27" s="22" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="A210">
+        <f t="shared" si="4"/>
+        <v>206</v>
+      </c>
+      <c r="B210" s="2" t="s">
+        <v>1582</v>
+      </c>
+      <c r="C210" t="s">
+        <v>1583</v>
+      </c>
+      <c r="X210" s="4">
+        <v>5516.7583439999999</v>
+      </c>
+      <c r="Z210" s="6" t="s">
+        <v>1585</v>
+      </c>
+      <c r="AA210" s="8" t="s">
+        <v>1584</v>
+      </c>
+      <c r="AH210" t="s">
+        <v>1586</v>
+      </c>
+    </row>
+    <row r="212" spans="1:34" s="22" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B212" s="22" t="s">
         <v>1211</v>
       </c>
@@ -11778,7 +11814,7 @@
       <c r="Z212" s="25"/>
       <c r="AA212" s="26"/>
     </row>
-    <row r="213" spans="1:27" s="22" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:34" s="22" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B213" s="22" t="s">
         <v>62</v>
       </c>
@@ -11809,27 +11845,27 @@
       <c r="Z213" s="25"/>
       <c r="AA213" s="26"/>
     </row>
-    <row r="214" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B214" s="22" t="s">
         <v>1269</v>
       </c>
     </row>
-    <row r="215" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B215" s="22" t="s">
         <v>1270</v>
       </c>
     </row>
-    <row r="216" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B216" s="22" t="s">
         <v>1271</v>
       </c>
     </row>
-    <row r="217" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B217" s="22" t="s">
         <v>1272</v>
       </c>
     </row>
-    <row r="218" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B218" s="22" t="s">
         <v>1273</v>
       </c>
@@ -11837,32 +11873,32 @@
         <v>1320</v>
       </c>
     </row>
-    <row r="219" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B219" s="22" t="s">
         <v>1274</v>
       </c>
     </row>
-    <row r="220" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B220" s="22" t="s">
         <v>1275</v>
       </c>
     </row>
-    <row r="221" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B221" s="22" t="s">
         <v>1276</v>
       </c>
     </row>
-    <row r="222" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B222" s="22" t="s">
         <v>1277</v>
       </c>
     </row>
-    <row r="223" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B223" s="22" t="s">
         <v>1278</v>
       </c>
     </row>
-    <row r="224" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B224" s="22" t="s">
         <v>724</v>
       </c>
@@ -12630,10 +12666,12 @@
     <hyperlink ref="B197" r:id="rId639" xr:uid="{57211A5D-F080-4C13-A991-6C2745F91A4D}"/>
     <hyperlink ref="X80" r:id="rId640" display="https://www.sec.gov/Archives/edgar/data/1079114/000117266124001512/0001172661-24-001512-index.htm" xr:uid="{29A13787-56B5-45C0-8D77-D395490EA1B0}"/>
     <hyperlink ref="X197" r:id="rId641" display="https://www.sec.gov/Archives/edgar/data/1960830/000091957426001016/0000919574-26-001016-index.htm" xr:uid="{6361078E-F13D-4E19-A00E-CCBE2355774B}"/>
+    <hyperlink ref="B210" r:id="rId642" xr:uid="{E772CE81-C0A7-40B7-A0F7-0B990343273E}"/>
+    <hyperlink ref="X210" r:id="rId643" display="https://www.sec.gov/Archives/edgar/data/2045724/000204572426000002/0002045724-26-000002-index.htm" xr:uid="{52D0C669-28FD-4B4C-A951-7B9DB3938C6E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId642"/>
-  <legacyDrawing r:id="rId643"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId644"/>
+  <legacyDrawing r:id="rId645"/>
 </worksheet>
 </file>
 

--- a/Hedge Funds (1).xlsx
+++ b/Hedge Funds (1).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D50C59D-0560-4817-8950-1EC92996ED48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23A95E28-C37C-4404-93CD-A8F36AFD3391}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="4290" windowWidth="38175" windowHeight="15240" xr2:uid="{18689D26-F1F3-46B4-82BE-041D095397EB}"/>
+    <workbookView xWindow="225" yWindow="2340" windowWidth="38175" windowHeight="15240" xr2:uid="{18689D26-F1F3-46B4-82BE-041D095397EB}"/>
   </bookViews>
   <sheets>
     <sheet name="Hedge" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
     <definedName name="JPY">[1]FX!$C$7</definedName>
     <definedName name="KRW">[1]FX!$C$9</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -166,7 +166,7 @@
     210.9B with puts/calls</t>
       </text>
     </comment>
-    <comment ref="Z4" authorId="6" shapeId="0" xr:uid="{C458FA31-CB9B-459E-B4D3-6F93CD9B9108}">
+    <comment ref="AD4" authorId="6" shapeId="0" xr:uid="{C458FA31-CB9B-459E-B4D3-6F93CD9B9108}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -393,7 +393,7 @@
 All Weather 12%</t>
       </text>
     </comment>
-    <comment ref="AF22" authorId="34" shapeId="0" xr:uid="{571E6B33-9F0B-402B-B6AF-3026724B96B6}">
+    <comment ref="AJ22" authorId="34" shapeId="0" xr:uid="{571E6B33-9F0B-402B-B6AF-3026724B96B6}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -402,7 +402,7 @@
 Pure alpha 1991</t>
       </text>
     </comment>
-    <comment ref="AO22" authorId="35" shapeId="0" xr:uid="{65A0F6CF-356C-4A90-96D2-FFE35AFE2E62}">
+    <comment ref="AS22" authorId="35" shapeId="0" xr:uid="{65A0F6CF-356C-4A90-96D2-FFE35AFE2E62}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -410,7 +410,7 @@
     All Weather +16%</t>
       </text>
     </comment>
-    <comment ref="AP22" authorId="36" shapeId="0" xr:uid="{267E6B37-EE49-4656-A61F-E5E2C45BA32F}">
+    <comment ref="AT22" authorId="36" shapeId="0" xr:uid="{267E6B37-EE49-4656-A61F-E5E2C45BA32F}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -474,7 +474,7 @@
     Also notes 35.5B</t>
       </text>
     </comment>
-    <comment ref="AL28" authorId="44" shapeId="0" xr:uid="{5F7F3924-A5F8-4D80-90C0-CA8CC6527A95}">
+    <comment ref="AP28" authorId="44" shapeId="0" xr:uid="{5F7F3924-A5F8-4D80-90C0-CA8CC6527A95}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -627,7 +627,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2280" uniqueCount="1587">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2284" uniqueCount="1591">
   <si>
     <t>Name</t>
   </si>
@@ -5388,6 +5388,18 @@
   </si>
   <si>
     <t>https://situational-awareness.ai/</t>
+  </si>
+  <si>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>Q226</t>
+  </si>
+  <si>
+    <t>Q326</t>
+  </si>
+  <si>
+    <t>Q426</t>
   </si>
 </sst>
 </file>
@@ -5956,7 +5968,7 @@
   <threadedComment ref="S4" dT="2025-01-11T20:11:02.62" personId="{4F866D09-A2D3-41DA-A24C-20DE51662D93}" id="{B533632F-6233-41C2-A96C-9A84235E21C6}">
     <text>210.9B with puts/calls</text>
   </threadedComment>
-  <threadedComment ref="Z4" dT="2025-04-05T10:22:31.39" personId="{C4A9F9C5-0550-4D3E-A9C0-F2F2E5238B0D}" id="{C458FA31-CB9B-459E-B4D3-6F93CD9B9108}">
+  <threadedComment ref="AD4" dT="2025-04-05T10:22:31.39" personId="{C4A9F9C5-0550-4D3E-A9C0-F2F2E5238B0D}" id="{C458FA31-CB9B-459E-B4D3-6F93CD9B9108}">
     <text xml:space="preserve">Pod shop = multi strategy </text>
   </threadedComment>
   <threadedComment ref="P5" dT="2024-03-24T23:23:21.67" personId="{4F866D09-A2D3-41DA-A24C-20DE51662D93}" id="{4762A1A1-5314-4304-962C-F1489B64BA4B}">
@@ -6043,14 +6055,14 @@
 Pure Alpha 18%
 All Weather 12%</text>
   </threadedComment>
-  <threadedComment ref="AF22" dT="2024-11-11T21:29:45.05" personId="{4F866D09-A2D3-41DA-A24C-20DE51662D93}" id="{571E6B33-9F0B-402B-B6AF-3026724B96B6}">
+  <threadedComment ref="AJ22" dT="2024-11-11T21:29:45.05" personId="{4F866D09-A2D3-41DA-A24C-20DE51662D93}" id="{571E6B33-9F0B-402B-B6AF-3026724B96B6}">
     <text>All weather opened 1996
 Pure alpha 1991</text>
   </threadedComment>
-  <threadedComment ref="AO22" dT="2024-11-11T21:44:28.32" personId="{4F866D09-A2D3-41DA-A24C-20DE51662D93}" id="{65A0F6CF-356C-4A90-96D2-FFE35AFE2E62}">
+  <threadedComment ref="AS22" dT="2024-11-11T21:44:28.32" personId="{4F866D09-A2D3-41DA-A24C-20DE51662D93}" id="{65A0F6CF-356C-4A90-96D2-FFE35AFE2E62}">
     <text>All Weather +16%</text>
   </threadedComment>
-  <threadedComment ref="AP22" dT="2024-11-11T21:45:06.55" personId="{4F866D09-A2D3-41DA-A24C-20DE51662D93}" id="{267E6B37-EE49-4656-A61F-E5E2C45BA32F}">
+  <threadedComment ref="AT22" dT="2024-11-11T21:45:06.55" personId="{4F866D09-A2D3-41DA-A24C-20DE51662D93}" id="{267E6B37-EE49-4656-A61F-E5E2C45BA32F}">
     <text>All Weather -5.1%</text>
   </threadedComment>
   <threadedComment ref="C23" dT="2025-04-08T16:50:08.35" personId="{C4A9F9C5-0550-4D3E-A9C0-F2F2E5238B0D}" id="{3C8A7604-D0B1-4BD2-8EB5-1FC90AAA41A6}">
@@ -6074,7 +6086,7 @@
   <threadedComment ref="D28" dT="2023-01-28T20:34:58.21" personId="{4F866D09-A2D3-41DA-A24C-20DE51662D93}" id="{9F5197FC-413A-4526-8395-DB7D8217FC78}">
     <text>Also notes 35.5B</text>
   </threadedComment>
-  <threadedComment ref="AL28" dT="2023-01-28T20:41:18.37" personId="{4F866D09-A2D3-41DA-A24C-20DE51662D93}" id="{5F7F3924-A5F8-4D80-90C0-CA8CC6527A95}">
+  <threadedComment ref="AP28" dT="2023-01-28T20:41:18.37" personId="{4F866D09-A2D3-41DA-A24C-20DE51662D93}" id="{5F7F3924-A5F8-4D80-90C0-CA8CC6527A95}">
     <text>https://www.bloomberg.com/news/articles/2022-08-26/lone-pine-assets-shrivel-as-hedge-fund-reels-from-record-losses?leadSource=uverify%20wall</text>
     <extLst>
       <x:ext xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
@@ -6152,7 +6164,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E8001A6-1B33-4EEE-B2A7-E66E0A0975B5}">
-  <dimension ref="A1:BS248"/>
+  <dimension ref="A1:BW248"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.140625" bestFit="1" customWidth="1"/>
@@ -6163,20 +6175,20 @@
     <col min="9" max="14" width="9.28515625" style="3"/>
     <col min="15" max="15" width="8.7109375" style="3"/>
     <col min="16" max="16" width="9.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="17" max="24" width="9.28515625" style="3" customWidth="1"/>
-    <col min="25" max="25" width="12" style="6" customWidth="1"/>
-    <col min="26" max="26" width="10.5703125" style="6" customWidth="1"/>
-    <col min="27" max="27" width="12" style="8" customWidth="1"/>
-    <col min="29" max="30" width="10.7109375" customWidth="1"/>
+    <col min="17" max="28" width="9.28515625" style="3" customWidth="1"/>
+    <col min="29" max="29" width="12" style="6" customWidth="1"/>
+    <col min="30" max="30" width="10.5703125" style="6" customWidth="1"/>
+    <col min="31" max="31" width="12" style="8" customWidth="1"/>
+    <col min="33" max="34" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:71" x14ac:dyDescent="0.2">
-      <c r="AD1">
-        <f>SUM(AD3:AD282)</f>
+    <row r="1" spans="1:75" x14ac:dyDescent="0.2">
+      <c r="AH1">
+        <f>SUM(AH3:AH282)</f>
         <v>30724</v>
       </c>
     </row>
-    <row r="2" spans="1:71" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:75" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -6246,159 +6258,171 @@
       <c r="X2" s="3" t="s">
         <v>1569</v>
       </c>
-      <c r="Y2" s="5" t="s">
+      <c r="Y2" s="3" t="s">
+        <v>1587</v>
+      </c>
+      <c r="Z2" s="3" t="s">
+        <v>1588</v>
+      </c>
+      <c r="AA2" s="3" t="s">
+        <v>1589</v>
+      </c>
+      <c r="AB2" s="3" t="s">
+        <v>1590</v>
+      </c>
+      <c r="AC2" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="Z2" s="5" t="s">
+      <c r="AD2" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="AA2" s="7" t="s">
+      <c r="AE2" s="7" t="s">
         <v>214</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="AF2" t="s">
         <v>225</v>
       </c>
-      <c r="AC2" t="s">
+      <c r="AG2" t="s">
         <v>226</v>
       </c>
-      <c r="AD2" t="s">
+      <c r="AH2" t="s">
         <v>723</v>
       </c>
-      <c r="AE2" t="s">
+      <c r="AI2" t="s">
         <v>229</v>
       </c>
-      <c r="AF2" t="s">
+      <c r="AJ2" t="s">
         <v>228</v>
       </c>
-      <c r="AG2" t="s">
+      <c r="AK2" t="s">
         <v>714</v>
       </c>
-      <c r="AH2" t="s">
+      <c r="AL2" t="s">
         <v>715</v>
       </c>
-      <c r="AI2" t="s">
+      <c r="AM2" t="s">
         <v>713</v>
       </c>
-      <c r="AJ2">
+      <c r="AN2">
         <v>2024</v>
       </c>
-      <c r="AK2">
+      <c r="AO2">
         <v>2023</v>
       </c>
-      <c r="AL2">
+      <c r="AP2">
         <v>2022</v>
       </c>
-      <c r="AM2">
+      <c r="AQ2">
         <v>2021</v>
       </c>
-      <c r="AN2">
+      <c r="AR2">
         <v>2020</v>
       </c>
-      <c r="AO2">
+      <c r="AS2">
         <v>2019</v>
       </c>
-      <c r="AP2">
+      <c r="AT2">
         <v>2018</v>
       </c>
-      <c r="AQ2">
+      <c r="AU2">
         <v>2017</v>
       </c>
-      <c r="AR2">
+      <c r="AV2">
         <v>2016</v>
       </c>
-      <c r="AS2">
+      <c r="AW2">
         <v>2015</v>
       </c>
-      <c r="AT2">
+      <c r="AX2">
         <v>2014</v>
       </c>
-      <c r="AU2">
+      <c r="AY2">
         <v>2013</v>
       </c>
-      <c r="AV2">
+      <c r="AZ2">
         <v>2012</v>
       </c>
-      <c r="AW2">
+      <c r="BA2">
         <v>2011</v>
       </c>
-      <c r="AX2">
-        <f>+AW2-1</f>
+      <c r="BB2">
+        <f>+BA2-1</f>
         <v>2010</v>
       </c>
-      <c r="AY2">
-        <f t="shared" ref="AY2:BM2" si="0">+AX2-1</f>
+      <c r="BC2">
+        <f t="shared" ref="BC2:BQ2" si="0">+BB2-1</f>
         <v>2009</v>
       </c>
-      <c r="AZ2">
+      <c r="BD2">
         <f t="shared" si="0"/>
         <v>2008</v>
       </c>
-      <c r="BA2">
+      <c r="BE2">
         <f t="shared" si="0"/>
         <v>2007</v>
       </c>
-      <c r="BB2">
+      <c r="BF2">
         <f t="shared" si="0"/>
         <v>2006</v>
       </c>
-      <c r="BC2">
+      <c r="BG2">
         <f t="shared" si="0"/>
         <v>2005</v>
       </c>
-      <c r="BD2">
+      <c r="BH2">
         <f t="shared" si="0"/>
         <v>2004</v>
       </c>
-      <c r="BE2">
+      <c r="BI2">
         <f t="shared" si="0"/>
         <v>2003</v>
       </c>
-      <c r="BF2">
+      <c r="BJ2">
         <f t="shared" si="0"/>
         <v>2002</v>
       </c>
-      <c r="BG2">
+      <c r="BK2">
         <f t="shared" si="0"/>
         <v>2001</v>
       </c>
-      <c r="BH2">
+      <c r="BL2">
         <f t="shared" si="0"/>
         <v>2000</v>
       </c>
-      <c r="BI2">
+      <c r="BM2">
         <f t="shared" si="0"/>
         <v>1999</v>
       </c>
-      <c r="BJ2">
+      <c r="BN2">
         <f t="shared" si="0"/>
         <v>1998</v>
       </c>
-      <c r="BK2">
+      <c r="BO2">
         <f t="shared" si="0"/>
         <v>1997</v>
       </c>
-      <c r="BL2">
+      <c r="BP2">
         <f t="shared" si="0"/>
         <v>1996</v>
       </c>
-      <c r="BM2">
+      <c r="BQ2">
         <f t="shared" si="0"/>
         <v>1995</v>
       </c>
-      <c r="BN2">
+      <c r="BR2">
         <v>1994</v>
       </c>
-      <c r="BO2">
+      <c r="BS2">
         <v>1993</v>
       </c>
-      <c r="BP2">
+      <c r="BT2">
         <v>1992</v>
       </c>
-      <c r="BQ2">
+      <c r="BU2">
         <v>1991</v>
       </c>
     </row>
-    <row r="3" spans="1:71" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:75" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1</v>
       </c>
@@ -6453,20 +6477,24 @@
       <c r="X3" s="4">
         <v>274160.08670099999</v>
       </c>
-      <c r="Y3" s="6" t="s">
+      <c r="Y3" s="4"/>
+      <c r="Z3" s="4"/>
+      <c r="AA3" s="4"/>
+      <c r="AB3" s="4"/>
+      <c r="AC3" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="Z3" s="6" t="s">
+      <c r="AD3" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="AA3" s="8" t="s">
+      <c r="AE3" s="8" t="s">
         <v>217</v>
       </c>
-      <c r="AB3">
+      <c r="AF3">
         <v>1965</v>
       </c>
     </row>
-    <row r="4" spans="1:71" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:75" x14ac:dyDescent="0.2">
       <c r="A4">
         <f>+A3+1</f>
         <v>2</v>
@@ -6528,87 +6556,91 @@
       <c r="X4" s="4">
         <v>237791.01562200001</v>
       </c>
-      <c r="Y4" s="6" t="s">
+      <c r="Y4" s="4"/>
+      <c r="Z4" s="4"/>
+      <c r="AA4" s="4"/>
+      <c r="AB4" s="4"/>
+      <c r="AC4" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="Z4" s="6" t="s">
+      <c r="AD4" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="AA4" s="8" t="s">
+      <c r="AE4" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="AB4">
+      <c r="AF4">
         <v>1989</v>
       </c>
-      <c r="AD4">
+      <c r="AH4">
         <v>5500</v>
       </c>
-      <c r="AG4" t="s">
+      <c r="AK4" t="s">
         <v>722</v>
       </c>
-      <c r="AJ4" s="9">
+      <c r="AN4" s="9">
         <v>0.15</v>
       </c>
-      <c r="AK4" s="9">
+      <c r="AO4" s="9">
         <v>0.1</v>
       </c>
-      <c r="AL4" s="9">
+      <c r="AP4" s="9">
         <v>0.12</v>
       </c>
-      <c r="AM4" s="9">
+      <c r="AQ4" s="9">
         <v>0.1361</v>
       </c>
-      <c r="AN4" s="9">
+      <c r="AR4" s="9">
         <v>0.25800000000000001</v>
       </c>
-      <c r="AO4" s="9">
+      <c r="AS4" s="9">
         <v>9.8000000000000004E-2</v>
       </c>
-      <c r="AP4" s="9">
+      <c r="AT4" s="9">
         <v>4.9000000000000002E-2</v>
       </c>
-      <c r="AQ4" s="9">
+      <c r="AU4" s="9">
         <v>7.1199999999999999E-2</v>
       </c>
-      <c r="AR4" s="9">
+      <c r="AV4" s="9">
         <v>3.3799999999999997E-2</v>
       </c>
-      <c r="AS4" s="9">
+      <c r="AW4" s="9">
         <v>0.12540000000000001</v>
       </c>
-      <c r="AT4" s="9">
+      <c r="AX4" s="9">
         <v>0.12089999999999999</v>
       </c>
-      <c r="AU4" s="9">
+      <c r="AY4" s="9">
         <v>0.13270000000000001</v>
       </c>
-      <c r="AV4" s="9">
+      <c r="AZ4" s="9">
         <v>6.3200000000000006E-2</v>
       </c>
-      <c r="AW4" s="9">
+      <c r="BA4" s="9">
         <v>8.3900000000000002E-2</v>
       </c>
-      <c r="AX4" s="9">
+      <c r="BB4" s="9">
         <v>0.13400000000000001</v>
       </c>
-      <c r="AY4" s="9">
+      <c r="BC4" s="9">
         <v>0.17199999999999999</v>
       </c>
-      <c r="AZ4" s="9">
+      <c r="BD4" s="9">
         <v>-0.03</v>
       </c>
-      <c r="BA4" s="9"/>
-      <c r="BB4" s="9">
+      <c r="BE4" s="9"/>
+      <c r="BF4" s="9">
         <v>0.17</v>
       </c>
-      <c r="BC4" s="9">
+      <c r="BG4" s="9">
         <v>0.08</v>
       </c>
-      <c r="BD4" s="9">
+      <c r="BH4" s="9">
         <v>0.35</v>
       </c>
     </row>
-    <row r="5" spans="1:71" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:75" x14ac:dyDescent="0.2">
       <c r="A5">
         <f t="shared" ref="A5:A84" si="1">+A4+1</f>
         <v>3</v>
@@ -6670,101 +6702,105 @@
       <c r="X5" s="4">
         <v>665872.16804500006</v>
       </c>
-      <c r="Y5" s="6" t="s">
+      <c r="Y5" s="4"/>
+      <c r="Z5" s="4"/>
+      <c r="AA5" s="4"/>
+      <c r="AB5" s="4"/>
+      <c r="AC5" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="Z5" s="6" t="s">
+      <c r="AD5" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="AA5" s="8" t="s">
+      <c r="AE5" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="AB5">
+      <c r="AF5">
         <v>1990</v>
       </c>
-      <c r="AC5" t="s">
+      <c r="AG5" t="s">
         <v>235</v>
       </c>
-      <c r="AD5">
+      <c r="AH5">
         <v>2932</v>
       </c>
-      <c r="AJ5" s="9">
+      <c r="AN5" s="9">
         <v>0.15</v>
       </c>
-      <c r="AK5" s="9">
+      <c r="AO5" s="9">
         <v>0.153</v>
       </c>
-      <c r="AL5" s="9">
+      <c r="AP5" s="9">
         <v>0.38</v>
       </c>
-      <c r="AM5" s="9">
+      <c r="AQ5" s="9">
         <v>0.26</v>
       </c>
-      <c r="AN5" s="9">
+      <c r="AR5" s="9">
         <v>0.24399999999999999</v>
       </c>
-      <c r="AO5" s="9">
+      <c r="AS5" s="9">
         <v>0.19400000000000001</v>
       </c>
-      <c r="AP5" s="9">
+      <c r="AT5" s="9">
         <v>9.0999999999999998E-2</v>
       </c>
-      <c r="AQ5" s="9">
+      <c r="AU5" s="9">
         <v>0.13100000000000001</v>
       </c>
-      <c r="AR5" s="9">
+      <c r="AV5" s="9">
         <v>5.0999999999999997E-2</v>
       </c>
-      <c r="AS5" s="9">
+      <c r="AW5" s="9">
         <v>0.14299999999999999</v>
       </c>
-      <c r="AT5" s="9">
+      <c r="AX5" s="9">
         <v>0.17899999999999999</v>
       </c>
-      <c r="AU5" s="9">
+      <c r="AY5" s="9">
         <v>0.19400000000000001</v>
       </c>
-      <c r="AV5" s="9">
+      <c r="AZ5" s="9">
         <v>0.25900000000000001</v>
       </c>
-      <c r="AW5" s="9">
+      <c r="BA5" s="9">
         <v>0.2</v>
       </c>
-      <c r="AX5" s="9">
+      <c r="BB5" s="9">
         <v>0.1</v>
       </c>
-      <c r="AY5" s="9">
+      <c r="BC5" s="9">
         <v>0.62</v>
       </c>
-      <c r="AZ5" s="9">
+      <c r="BD5" s="9">
         <v>-0.55000000000000004</v>
       </c>
-      <c r="BA5" s="9">
+      <c r="BE5" s="9">
         <v>0.3</v>
       </c>
-      <c r="BB5" s="9">
+      <c r="BF5" s="9">
         <v>0.3</v>
       </c>
-      <c r="BC5" s="9">
+      <c r="BG5" s="9">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="BI5" s="9">
+      <c r="BM5" s="9">
         <v>0.45</v>
       </c>
-      <c r="BN5" s="9">
+      <c r="BR5" s="9">
         <v>-4.2999999999999997E-2</v>
       </c>
-      <c r="BP5" s="9">
+      <c r="BT5" s="9">
         <v>0.4</v>
       </c>
-      <c r="BQ5" s="9">
+      <c r="BU5" s="9">
         <v>0.43</v>
       </c>
-      <c r="BS5" t="s">
+      <c r="BW5" t="s">
         <v>1498</v>
       </c>
     </row>
-    <row r="6" spans="1:71" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:75" x14ac:dyDescent="0.2">
       <c r="A6">
         <f t="shared" si="1"/>
         <v>4</v>
@@ -6817,23 +6853,27 @@
       <c r="X6" s="4">
         <v>662115.96467400005</v>
       </c>
-      <c r="Y6" s="6" t="s">
+      <c r="Y6" s="4"/>
+      <c r="Z6" s="4"/>
+      <c r="AA6" s="4"/>
+      <c r="AB6" s="4"/>
+      <c r="AC6" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="Z6" s="6" t="s">
+      <c r="AD6" s="6" t="s">
         <v>1477</v>
       </c>
-      <c r="AA6" s="8" t="s">
+      <c r="AE6" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="AB6">
+      <c r="AF6">
         <v>2000</v>
       </c>
-      <c r="AD6">
+      <c r="AH6">
         <v>2600</v>
       </c>
     </row>
-    <row r="7" spans="1:71" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:75" x14ac:dyDescent="0.2">
       <c r="A7">
         <f t="shared" si="1"/>
         <v>5</v>
@@ -6874,38 +6914,42 @@
       <c r="X7" s="4">
         <v>109852.42796099999</v>
       </c>
-      <c r="Y7" s="6" t="s">
+      <c r="Y7" s="4"/>
+      <c r="Z7" s="4"/>
+      <c r="AA7" s="4"/>
+      <c r="AB7" s="4"/>
+      <c r="AC7" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="Z7" s="6" t="s">
+      <c r="AD7" s="6" t="s">
         <v>1476</v>
       </c>
-      <c r="AA7" s="8" t="s">
+      <c r="AE7" s="8" t="s">
         <v>673</v>
       </c>
-      <c r="AB7">
+      <c r="AF7">
         <v>1997</v>
       </c>
-      <c r="AD7">
+      <c r="AH7">
         <v>650</v>
       </c>
-      <c r="AG7" t="s">
+      <c r="AK7" t="s">
         <v>717</v>
       </c>
-      <c r="AH7" t="s">
+      <c r="AL7" t="s">
         <v>716</v>
       </c>
-      <c r="AI7" t="s">
+      <c r="AM7" t="s">
         <v>1487</v>
       </c>
-      <c r="AK7" s="36">
+      <c r="AO7" s="36">
         <v>7.5999999999999998E-2</v>
       </c>
-      <c r="AV7" s="36">
+      <c r="AZ7" s="36">
         <v>6.83E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:71" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:75" x14ac:dyDescent="0.2">
       <c r="A8">
         <f t="shared" si="1"/>
         <v>6</v>
@@ -6952,29 +6996,33 @@
       <c r="X8" s="4">
         <v>190628.43056800001</v>
       </c>
-      <c r="Y8" s="6" t="s">
+      <c r="Y8" s="4"/>
+      <c r="Z8" s="4"/>
+      <c r="AA8" s="4"/>
+      <c r="AB8" s="4"/>
+      <c r="AC8" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="Z8" s="6" t="s">
+      <c r="AD8" s="6" t="s">
         <v>939</v>
       </c>
-      <c r="AA8" s="8" t="s">
+      <c r="AE8" s="8" t="s">
         <v>1478</v>
       </c>
-      <c r="AB8">
+      <c r="AF8">
         <v>1998</v>
       </c>
-      <c r="AD8">
+      <c r="AH8">
         <v>573</v>
       </c>
-      <c r="AS8" s="9">
+      <c r="AW8" s="9">
         <v>0.14699999999999999</v>
       </c>
-      <c r="AT8" s="9">
+      <c r="AX8" s="9">
         <v>5.8000000000000003E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:71" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:75" x14ac:dyDescent="0.2">
       <c r="A9">
         <f t="shared" si="1"/>
         <v>7</v>
@@ -7033,29 +7081,33 @@
       <c r="X9" s="4">
         <v>64461.244358000004</v>
       </c>
-      <c r="Y9" s="6" t="s">
+      <c r="Y9" s="4"/>
+      <c r="Z9" s="4"/>
+      <c r="AA9" s="4"/>
+      <c r="AB9" s="4"/>
+      <c r="AC9" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="Z9" s="6" t="s">
+      <c r="AD9" s="6" t="s">
         <v>219</v>
       </c>
-      <c r="AA9" s="8" t="s">
+      <c r="AE9" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="AB9">
+      <c r="AF9">
         <v>1978</v>
       </c>
-      <c r="AD9">
+      <c r="AH9">
         <v>310</v>
       </c>
-      <c r="AY9" s="9">
+      <c r="BC9" s="9">
         <v>0.38</v>
       </c>
-      <c r="BD9" s="9">
+      <c r="BH9" s="9">
         <v>0.25</v>
       </c>
     </row>
-    <row r="10" spans="1:71" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:75" x14ac:dyDescent="0.2">
       <c r="A10">
         <f t="shared" si="1"/>
         <v>8</v>
@@ -7114,20 +7166,24 @@
       <c r="X10" s="4">
         <v>868031.75397900003</v>
       </c>
-      <c r="Y10" s="6" t="s">
+      <c r="Y10" s="4"/>
+      <c r="Z10" s="4"/>
+      <c r="AA10" s="4"/>
+      <c r="AB10" s="4"/>
+      <c r="AC10" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="Z10" s="6" t="s">
+      <c r="AD10" s="6" t="s">
         <v>1130</v>
       </c>
-      <c r="AA10" s="8" t="s">
+      <c r="AE10" s="8" t="s">
         <v>664</v>
       </c>
-      <c r="AD10">
+      <c r="AH10">
         <v>3000</v>
       </c>
     </row>
-    <row r="11" spans="1:71" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:75" x14ac:dyDescent="0.2">
       <c r="A11">
         <f t="shared" si="1"/>
         <v>9</v>
@@ -7165,17 +7221,21 @@
       <c r="X11" s="4">
         <v>98444.689024000007</v>
       </c>
-      <c r="Y11" s="6" t="s">
+      <c r="Y11" s="4"/>
+      <c r="Z11" s="4"/>
+      <c r="AA11" s="4"/>
+      <c r="AB11" s="4"/>
+      <c r="AC11" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="Z11" s="6" t="s">
+      <c r="AD11" s="6" t="s">
         <v>219</v>
       </c>
-      <c r="AD11">
+      <c r="AH11">
         <v>1100</v>
       </c>
     </row>
-    <row r="12" spans="1:71" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:75" x14ac:dyDescent="0.2">
       <c r="A12">
         <f t="shared" si="1"/>
         <v>10</v>
@@ -7225,39 +7285,43 @@
       <c r="X12" s="4">
         <v>51433.080634999998</v>
       </c>
-      <c r="Y12" s="6" t="s">
+      <c r="Y12" s="4"/>
+      <c r="Z12" s="4"/>
+      <c r="AA12" s="4"/>
+      <c r="AB12" s="4"/>
+      <c r="AC12" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="Z12" s="6" t="s">
+      <c r="AD12" s="6" t="s">
         <v>219</v>
       </c>
-      <c r="AA12" s="8" t="s">
+      <c r="AE12" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="AB12">
+      <c r="AF12">
         <v>2001</v>
       </c>
-      <c r="AD12">
+      <c r="AH12">
         <v>2100</v>
       </c>
-      <c r="AK12" s="9">
+      <c r="AO12" s="9">
         <v>0.12</v>
       </c>
-      <c r="AS12" s="9">
+      <c r="AW12" s="9">
         <v>0.15</v>
       </c>
-      <c r="AT12" s="9">
+      <c r="AX12" s="9">
         <v>0.10100000000000001</v>
       </c>
-      <c r="AY12" s="9">
+      <c r="BC12" s="9">
         <v>0.20230000000000001</v>
       </c>
-      <c r="AZ12" s="9"/>
-      <c r="BA12" s="9"/>
-      <c r="BB12" s="9"/>
-      <c r="BC12" s="9"/>
-    </row>
-    <row r="13" spans="1:71" x14ac:dyDescent="0.2">
+      <c r="BD12" s="9"/>
+      <c r="BE12" s="9"/>
+      <c r="BF12" s="9"/>
+      <c r="BG12" s="9"/>
+    </row>
+    <row r="13" spans="1:75" x14ac:dyDescent="0.2">
       <c r="A13">
         <f t="shared" si="1"/>
         <v>11</v>
@@ -7310,42 +7374,46 @@
       <c r="X13" s="4">
         <v>182424.02489299999</v>
       </c>
-      <c r="Y13" s="6" t="s">
+      <c r="Y13" s="4"/>
+      <c r="Z13" s="4"/>
+      <c r="AA13" s="4"/>
+      <c r="AB13" s="4"/>
+      <c r="AC13" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="Z13" s="6" t="s">
+      <c r="AD13" s="6" t="s">
         <v>219</v>
       </c>
-      <c r="AA13" s="8" t="s">
+      <c r="AE13" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="AD13">
+      <c r="AH13">
         <v>2500</v>
       </c>
-      <c r="AK13" s="9">
+      <c r="AO13" s="9">
         <v>9.6000000000000002E-2</v>
       </c>
-      <c r="AM13" s="9">
+      <c r="AQ13" s="9">
         <v>0.185</v>
       </c>
-      <c r="AS13" s="9">
+      <c r="AW13" s="9">
         <v>0.14299999999999999</v>
       </c>
-      <c r="AT13" s="9">
+      <c r="AX13" s="9">
         <v>0.16400000000000001</v>
       </c>
-      <c r="AY13" s="9"/>
-      <c r="AZ13" s="9"/>
-      <c r="BA13" s="9">
+      <c r="BC13" s="9"/>
+      <c r="BD13" s="9"/>
+      <c r="BE13" s="9">
         <v>7.3999999999999996E-2</v>
       </c>
-      <c r="BB13" s="9"/>
-      <c r="BC13" s="9"/>
-      <c r="BS13" t="s">
+      <c r="BF13" s="9"/>
+      <c r="BG13" s="9"/>
+      <c r="BW13" t="s">
         <v>1499</v>
       </c>
     </row>
-    <row r="14" spans="1:71" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:75" x14ac:dyDescent="0.2">
       <c r="A14">
         <f t="shared" si="1"/>
         <v>12</v>
@@ -7384,52 +7452,56 @@
       <c r="X14" s="4">
         <v>53648.816253999998</v>
       </c>
-      <c r="Y14" s="6" t="s">
+      <c r="Y14" s="4"/>
+      <c r="Z14" s="4"/>
+      <c r="AA14" s="4"/>
+      <c r="AB14" s="4"/>
+      <c r="AC14" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="Z14" s="6" t="s">
+      <c r="AD14" s="6" t="s">
         <v>1546</v>
       </c>
-      <c r="AA14" s="8" t="s">
+      <c r="AE14" s="8" t="s">
         <v>673</v>
       </c>
-      <c r="AD14">
+      <c r="AH14">
         <v>82</v>
       </c>
-      <c r="AJ14" s="9">
+      <c r="AN14" s="9">
         <v>0.15</v>
       </c>
-      <c r="AK14" s="9">
+      <c r="AO14" s="9">
         <v>0.33</v>
       </c>
-      <c r="AL14" s="9">
+      <c r="AP14" s="9">
         <v>-0.18</v>
       </c>
-      <c r="AM14" s="9"/>
-      <c r="AR14" s="9">
+      <c r="AQ14" s="9"/>
+      <c r="AV14" s="9">
         <v>0.13500000000000001</v>
       </c>
-      <c r="AS14" s="9">
+      <c r="AW14" s="9">
         <v>0.14399999999999999</v>
       </c>
-      <c r="AT14" s="9">
+      <c r="AX14" s="9">
         <v>8.1000000000000003E-2</v>
       </c>
-      <c r="AU14" s="9">
+      <c r="AY14" s="9">
         <v>0.47220000000000001</v>
       </c>
-      <c r="AV14" s="9">
+      <c r="AZ14" s="9">
         <v>0.29520000000000002</v>
       </c>
-      <c r="AY14" s="9"/>
-      <c r="AZ14" s="9">
+      <c r="BC14" s="9"/>
+      <c r="BD14" s="9">
         <v>-0.43</v>
       </c>
-      <c r="BA14" s="9"/>
-      <c r="BB14" s="9"/>
-      <c r="BC14" s="9"/>
-    </row>
-    <row r="15" spans="1:71" x14ac:dyDescent="0.2">
+      <c r="BE14" s="9"/>
+      <c r="BF14" s="9"/>
+      <c r="BG14" s="9"/>
+    </row>
+    <row r="15" spans="1:75" x14ac:dyDescent="0.2">
       <c r="A15">
         <f t="shared" si="1"/>
         <v>13</v>
@@ -7476,33 +7548,37 @@
       <c r="X15" s="4">
         <v>78776.702306000007</v>
       </c>
-      <c r="Y15" s="6" t="s">
+      <c r="Y15" s="4"/>
+      <c r="Z15" s="4"/>
+      <c r="AA15" s="4"/>
+      <c r="AB15" s="4"/>
+      <c r="AC15" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="Z15" s="6" t="s">
+      <c r="AD15" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="AA15" s="8" t="s">
+      <c r="AE15" s="8" t="s">
         <v>223</v>
       </c>
-      <c r="AD15">
+      <c r="AH15">
         <v>1900</v>
       </c>
-      <c r="AM15" s="9">
+      <c r="AQ15" s="9">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="AU15" s="9"/>
-      <c r="AY15" s="9">
+      <c r="AY15" s="9"/>
+      <c r="BC15" s="9">
         <v>8.6400000000000005E-2</v>
       </c>
-      <c r="AZ15" s="9">
+      <c r="BD15" s="9">
         <v>4.5999999999999999E-3</v>
       </c>
-      <c r="BA15" s="9"/>
-      <c r="BB15" s="9"/>
-      <c r="BC15" s="9"/>
-    </row>
-    <row r="16" spans="1:71" x14ac:dyDescent="0.2">
+      <c r="BE15" s="9"/>
+      <c r="BF15" s="9"/>
+      <c r="BG15" s="9"/>
+    </row>
+    <row r="16" spans="1:75" x14ac:dyDescent="0.2">
       <c r="A16">
         <f t="shared" si="1"/>
         <v>14</v>
@@ -7534,27 +7610,31 @@
       <c r="X16" s="4">
         <v>58828.069125000002</v>
       </c>
-      <c r="Y16" s="6" t="s">
+      <c r="Y16" s="4"/>
+      <c r="Z16" s="4"/>
+      <c r="AA16" s="4"/>
+      <c r="AB16" s="4"/>
+      <c r="AC16" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="Z16" s="6" t="s">
+      <c r="AD16" s="6" t="s">
         <v>1559</v>
       </c>
-      <c r="AD16">
+      <c r="AH16">
         <v>1787</v>
       </c>
-      <c r="AU16" s="10" t="s">
+      <c r="AY16" s="10" t="s">
         <v>1496</v>
       </c>
-      <c r="AY16" s="9"/>
-      <c r="AZ16" s="9" t="s">
+      <c r="BC16" s="9"/>
+      <c r="BD16" s="9" t="s">
         <v>1501</v>
       </c>
-      <c r="BA16" s="9"/>
-      <c r="BB16" s="9"/>
-      <c r="BC16" s="9"/>
-    </row>
-    <row r="17" spans="1:68" x14ac:dyDescent="0.2">
+      <c r="BE16" s="9"/>
+      <c r="BF16" s="9"/>
+      <c r="BG16" s="9"/>
+    </row>
+    <row r="17" spans="1:72" x14ac:dyDescent="0.2">
       <c r="A17">
         <f t="shared" si="1"/>
         <v>15</v>
@@ -7610,50 +7690,54 @@
       <c r="X17" s="4">
         <v>89421.368730999995</v>
       </c>
-      <c r="Y17" s="6" t="s">
+      <c r="Y17" s="4"/>
+      <c r="Z17" s="4"/>
+      <c r="AA17" s="4"/>
+      <c r="AB17" s="4"/>
+      <c r="AC17" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="Z17" s="6" t="s">
+      <c r="AD17" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="AA17" s="8" t="s">
+      <c r="AE17" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="AB17">
+      <c r="AF17">
         <v>1992</v>
       </c>
-      <c r="AD17">
+      <c r="AH17">
         <v>2800</v>
       </c>
-      <c r="AJ17" s="9">
+      <c r="AN17" s="9">
         <v>0.19</v>
       </c>
-      <c r="AK17" s="9">
+      <c r="AO17" s="9">
         <v>0.106</v>
       </c>
-      <c r="AL17" s="9">
+      <c r="AP17" s="9">
         <v>0.1</v>
       </c>
-      <c r="AM17" s="9">
+      <c r="AQ17" s="9">
         <v>0.09</v>
-      </c>
-      <c r="AU17" s="9"/>
-      <c r="AV17" s="9">
-        <v>0.14000000000000001</v>
       </c>
       <c r="AY17" s="9"/>
       <c r="AZ17" s="9">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="BC17" s="9"/>
+      <c r="BD17" s="9">
         <v>-0.18529999999999999</v>
       </c>
-      <c r="BA17" s="9">
+      <c r="BE17" s="9">
         <v>0.13</v>
       </c>
-      <c r="BB17" s="9">
+      <c r="BF17" s="9">
         <v>0.34</v>
       </c>
-      <c r="BC17" s="9"/>
-    </row>
-    <row r="18" spans="1:68" x14ac:dyDescent="0.2">
+      <c r="BG17" s="9"/>
+    </row>
+    <row r="18" spans="1:72" x14ac:dyDescent="0.2">
       <c r="A18">
         <f t="shared" si="1"/>
         <v>16</v>
@@ -7694,23 +7778,27 @@
       <c r="X18" s="4">
         <v>28451.166436</v>
       </c>
-      <c r="Y18" s="6" t="s">
+      <c r="Y18" s="4"/>
+      <c r="Z18" s="4"/>
+      <c r="AA18" s="4"/>
+      <c r="AB18" s="4"/>
+      <c r="AC18" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="AD18">
+      <c r="AH18">
         <v>119</v>
       </c>
-      <c r="AF18">
+      <c r="AJ18">
         <v>2009</v>
       </c>
-      <c r="AU18" s="9"/>
       <c r="AY18" s="9"/>
-      <c r="AZ18" s="9"/>
-      <c r="BA18" s="9"/>
-      <c r="BB18" s="9"/>
       <c r="BC18" s="9"/>
-    </row>
-    <row r="19" spans="1:68" x14ac:dyDescent="0.2">
+      <c r="BD18" s="9"/>
+      <c r="BE18" s="9"/>
+      <c r="BF18" s="9"/>
+      <c r="BG18" s="9"/>
+    </row>
+    <row r="19" spans="1:72" x14ac:dyDescent="0.2">
       <c r="A19">
         <f t="shared" si="1"/>
         <v>17</v>
@@ -7769,38 +7857,42 @@
       <c r="X19" s="4">
         <v>37677.848897999997</v>
       </c>
-      <c r="Y19" s="6" t="s">
+      <c r="Y19" s="4"/>
+      <c r="Z19" s="4"/>
+      <c r="AA19" s="4"/>
+      <c r="AB19" s="4"/>
+      <c r="AC19" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="Z19" s="6" t="s">
+      <c r="AD19" s="6" t="s">
         <v>220</v>
       </c>
-      <c r="AA19" s="8" t="s">
+      <c r="AE19" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="AD19">
+      <c r="AH19">
         <v>275</v>
       </c>
-      <c r="AK19" s="9">
+      <c r="AO19" s="9">
         <v>0.13800000000000001</v>
       </c>
-      <c r="AL19" s="9">
+      <c r="AP19" s="9">
         <v>-2.4E-2</v>
       </c>
-      <c r="AU19" s="9">
+      <c r="AY19" s="9">
         <v>0.22500000000000001</v>
       </c>
-      <c r="AY19" s="9">
+      <c r="BC19" s="9">
         <v>0.18890000000000001</v>
       </c>
-      <c r="AZ19" s="9">
+      <c r="BD19" s="9">
         <v>0.1</v>
       </c>
-      <c r="BA19" s="9"/>
-      <c r="BB19" s="9"/>
-      <c r="BC19" s="9"/>
-    </row>
-    <row r="20" spans="1:68" x14ac:dyDescent="0.2">
+      <c r="BE19" s="9"/>
+      <c r="BF19" s="9"/>
+      <c r="BG19" s="9"/>
+    </row>
+    <row r="20" spans="1:72" x14ac:dyDescent="0.2">
       <c r="A20">
         <f t="shared" si="1"/>
         <v>18</v>
@@ -7871,30 +7963,34 @@
       <c r="X20" s="4">
         <v>39962.643006999999</v>
       </c>
-      <c r="Y20" s="6" t="s">
+      <c r="Y20" s="4"/>
+      <c r="Z20" s="4"/>
+      <c r="AA20" s="4"/>
+      <c r="AB20" s="4"/>
+      <c r="AC20" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="Z20" s="6" t="s">
+      <c r="AD20" s="6" t="s">
         <v>220</v>
       </c>
-      <c r="AA20" s="8" t="s">
+      <c r="AE20" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="AD20">
+      <c r="AH20">
         <v>157</v>
       </c>
-      <c r="AK20" s="9">
+      <c r="AO20" s="9">
         <v>0.215</v>
       </c>
-      <c r="AS20" s="9">
+      <c r="AW20" s="9">
         <v>0.111</v>
       </c>
-      <c r="AT20" s="9">
+      <c r="AX20" s="9">
         <v>-2.4E-2</v>
       </c>
-      <c r="AU20" s="9"/>
-    </row>
-    <row r="21" spans="1:68" x14ac:dyDescent="0.2">
+      <c r="AY20" s="9"/>
+    </row>
+    <row r="21" spans="1:72" x14ac:dyDescent="0.2">
       <c r="A21">
         <f t="shared" si="1"/>
         <v>19</v>
@@ -7944,29 +8040,33 @@
       <c r="X21" s="4">
         <v>29714.313269999999</v>
       </c>
-      <c r="Y21" s="6" t="s">
+      <c r="Y21" s="4"/>
+      <c r="Z21" s="4"/>
+      <c r="AA21" s="4"/>
+      <c r="AB21" s="4"/>
+      <c r="AC21" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="Z21" s="6" t="s">
+      <c r="AD21" s="6" t="s">
         <v>220</v>
       </c>
-      <c r="AA21" s="8" t="s">
+      <c r="AE21" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="AD21">
+      <c r="AH21">
         <v>162</v>
       </c>
-      <c r="AK21" s="9">
+      <c r="AO21" s="9">
         <v>0.28499999999999998</v>
       </c>
-      <c r="AL21" s="9">
+      <c r="AP21" s="9">
         <v>-0.56000000000000005</v>
       </c>
-      <c r="AU21" s="9">
+      <c r="AY21" s="9">
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="22" spans="1:68" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:72" x14ac:dyDescent="0.2">
       <c r="A22">
         <f t="shared" si="1"/>
         <v>20</v>
@@ -8023,62 +8123,66 @@
       <c r="X22" s="4">
         <v>27421.613829999998</v>
       </c>
-      <c r="Y22" s="6" t="s">
+      <c r="Y22" s="4"/>
+      <c r="Z22" s="4"/>
+      <c r="AA22" s="4"/>
+      <c r="AB22" s="4"/>
+      <c r="AC22" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="AA22" s="8" t="s">
+      <c r="AE22" s="8" t="s">
         <v>238</v>
       </c>
-      <c r="AD22">
+      <c r="AH22">
         <v>1300</v>
       </c>
-      <c r="AF22">
+      <c r="AJ22">
         <v>1975</v>
       </c>
-      <c r="AI22" t="s">
+      <c r="AM22" t="s">
         <v>1486</v>
       </c>
-      <c r="AJ22" s="9">
+      <c r="AN22" s="9">
         <v>-0.14000000000000001</v>
       </c>
-      <c r="AK22" s="9" t="s">
+      <c r="AO22" s="9" t="s">
         <v>1500</v>
       </c>
-      <c r="AL22" s="9">
+      <c r="AP22" s="9">
         <v>0.1</v>
       </c>
-      <c r="AM22" s="9">
+      <c r="AQ22" s="9">
         <v>-0.05</v>
       </c>
-      <c r="AN22" s="9">
+      <c r="AR22" s="9">
         <v>-0.05</v>
       </c>
-      <c r="AO22" s="9">
+      <c r="AS22" s="9">
         <v>0</v>
       </c>
-      <c r="AP22" s="27">
+      <c r="AT22" s="27">
         <v>0.14599999999999999</v>
       </c>
-      <c r="AR22" t="s">
+      <c r="AV22" t="s">
         <v>1505</v>
       </c>
-      <c r="AS22" t="s">
+      <c r="AW22" t="s">
         <v>1503</v>
       </c>
-      <c r="AT22" t="s">
+      <c r="AX22" t="s">
         <v>1504</v>
       </c>
-      <c r="AV22" t="s">
+      <c r="AZ22" t="s">
         <v>1502</v>
       </c>
-      <c r="AZ22" s="27">
+      <c r="BD22" s="27">
         <v>9.4E-2</v>
       </c>
-      <c r="BA22" t="s">
+      <c r="BE22" t="s">
         <v>1497</v>
       </c>
     </row>
-    <row r="23" spans="1:68" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:72" x14ac:dyDescent="0.2">
       <c r="A23">
         <f t="shared" si="1"/>
         <v>21</v>
@@ -8113,17 +8217,21 @@
       <c r="X23" s="4">
         <v>25469.090312</v>
       </c>
-      <c r="Y23" s="6" t="s">
+      <c r="Y23" s="4"/>
+      <c r="Z23" s="4"/>
+      <c r="AA23" s="4"/>
+      <c r="AB23" s="4"/>
+      <c r="AC23" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="Z23" s="6" t="s">
+      <c r="AD23" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="AD23">
+      <c r="AH23">
         <v>350</v>
       </c>
     </row>
-    <row r="24" spans="1:68" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:72" x14ac:dyDescent="0.2">
       <c r="A24">
         <f t="shared" si="1"/>
         <v>22</v>
@@ -8164,17 +8272,21 @@
       <c r="X24" s="4">
         <v>35403.796805999998</v>
       </c>
-      <c r="Y24" s="6" t="s">
+      <c r="Y24" s="4"/>
+      <c r="Z24" s="4"/>
+      <c r="AA24" s="4"/>
+      <c r="AB24" s="4"/>
+      <c r="AC24" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="Z24" s="6" t="s">
+      <c r="AD24" s="6" t="s">
         <v>1559</v>
       </c>
-      <c r="AD24">
+      <c r="AH24">
         <v>56</v>
       </c>
     </row>
-    <row r="25" spans="1:68" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:72" x14ac:dyDescent="0.2">
       <c r="A25">
         <f t="shared" si="1"/>
         <v>23</v>
@@ -8215,20 +8327,24 @@
       <c r="X25" s="4">
         <v>20722.385988999999</v>
       </c>
-      <c r="Y25" s="6" t="s">
+      <c r="Y25" s="4"/>
+      <c r="Z25" s="4"/>
+      <c r="AA25" s="4"/>
+      <c r="AB25" s="4"/>
+      <c r="AC25" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="Z25" s="6" t="s">
+      <c r="AD25" s="6" t="s">
         <v>1560</v>
       </c>
-      <c r="AD25">
+      <c r="AH25">
         <v>230</v>
       </c>
-      <c r="BA25" s="36">
+      <c r="BE25" s="36">
         <v>0.14799999999999999</v>
       </c>
     </row>
-    <row r="26" spans="1:68" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:72" x14ac:dyDescent="0.2">
       <c r="A26">
         <f t="shared" si="1"/>
         <v>24</v>
@@ -8269,17 +8385,21 @@
       <c r="X26" s="4">
         <v>30340.662734000001</v>
       </c>
-      <c r="Y26" s="6" t="s">
+      <c r="Y26" s="4"/>
+      <c r="Z26" s="4"/>
+      <c r="AA26" s="4"/>
+      <c r="AB26" s="4"/>
+      <c r="AC26" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="AD26">
+      <c r="AH26">
         <v>241</v>
       </c>
-      <c r="AM26" s="9">
+      <c r="AQ26" s="9">
         <v>0.13500000000000001</v>
       </c>
     </row>
-    <row r="27" spans="1:68" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:72" x14ac:dyDescent="0.2">
       <c r="A27">
         <f t="shared" si="1"/>
         <v>25</v>
@@ -8317,26 +8437,30 @@
       <c r="X27" s="4">
         <v>57.616042</v>
       </c>
-      <c r="Y27" s="6" t="s">
+      <c r="Y27" s="4"/>
+      <c r="Z27" s="4"/>
+      <c r="AA27" s="4"/>
+      <c r="AB27" s="4"/>
+      <c r="AC27" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="Z27" s="6" t="s">
+      <c r="AD27" s="6" t="s">
         <v>220</v>
       </c>
-      <c r="AB27">
+      <c r="AF27">
         <v>2006</v>
       </c>
-      <c r="AS27" s="9">
+      <c r="AW27" s="9">
         <v>0.16200000000000001</v>
       </c>
-      <c r="AT27" s="9">
+      <c r="AX27" s="9">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="AU27" s="9">
+      <c r="AY27" s="9">
         <v>0.56000000000000005</v>
       </c>
     </row>
-    <row r="28" spans="1:68" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:72" x14ac:dyDescent="0.2">
       <c r="A28">
         <f t="shared" si="1"/>
         <v>26</v>
@@ -8392,119 +8516,123 @@
       <c r="X28" s="4">
         <v>13611.137640000001</v>
       </c>
-      <c r="Y28" s="6" t="s">
+      <c r="Y28" s="4"/>
+      <c r="Z28" s="4"/>
+      <c r="AA28" s="4"/>
+      <c r="AB28" s="4"/>
+      <c r="AC28" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="Z28" s="6" t="s">
+      <c r="AD28" s="6" t="s">
         <v>220</v>
       </c>
-      <c r="AA28" s="8" t="s">
+      <c r="AE28" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="AB28">
+      <c r="AF28">
         <v>1997</v>
       </c>
-      <c r="AC28" t="s">
+      <c r="AG28" t="s">
         <v>227</v>
       </c>
-      <c r="AE28" s="9">
+      <c r="AI28" s="9">
         <f>RATE(2022-1998,0,-1,13.71)</f>
         <v>0.11526111596972678</v>
       </c>
-      <c r="AF28" s="9">
-        <f>1*(1+BJ$28)*(1+BI28)*(1+BH28)*(1+BG28)*(1+BF28)*(1+BE28)*(1+BD28)*(1+BC28)*(1+BB28)*(1+BA28)*(1+AZ28)*(1+AY28)*(1+AX28)*(1+AW28)*(1+AV28)*(1+AU28)*(1+AT28)*(1+AS28)*(1+AR28)*(1+AQ28)*(1+AP28)*(1+AO28)*(1+AN28)*(1+AM28)*(1+AL28)-1</f>
+      <c r="AJ28" s="9">
+        <f>1*(1+BN$28)*(1+BM28)*(1+BL28)*(1+BK28)*(1+BJ28)*(1+BI28)*(1+BH28)*(1+BG28)*(1+BF28)*(1+BE28)*(1+BD28)*(1+BC28)*(1+BB28)*(1+BA28)*(1+AZ28)*(1+AY28)*(1+AX28)*(1+AW28)*(1+AV28)*(1+AU28)*(1+AT28)*(1+AS28)*(1+AR28)*(1+AQ28)*(1+AP28)-1</f>
         <v>13.713492129281141</v>
       </c>
-      <c r="AG28" s="9"/>
-      <c r="AH28" s="9"/>
-      <c r="AI28" s="9"/>
-      <c r="AJ28" s="9"/>
-      <c r="AK28" s="9">
+      <c r="AK28" s="9"/>
+      <c r="AL28" s="9"/>
+      <c r="AM28" s="9"/>
+      <c r="AN28" s="9"/>
+      <c r="AO28" s="9">
         <v>0.19</v>
       </c>
-      <c r="AL28" s="10">
+      <c r="AP28" s="10">
         <v>-0.33</v>
       </c>
-      <c r="AM28" s="9">
+      <c r="AQ28" s="9">
         <v>-7.0000000000000007E-2</v>
       </c>
-      <c r="AN28" s="9">
+      <c r="AR28" s="9">
         <v>0.23</v>
       </c>
-      <c r="AO28" s="9">
+      <c r="AS28" s="9">
         <v>0.29899999999999999</v>
       </c>
-      <c r="AP28" s="9">
+      <c r="AT28" s="9">
         <v>-0.05</v>
       </c>
-      <c r="AQ28" s="9">
+      <c r="AU28" s="9">
         <v>8.2000000000000003E-2</v>
       </c>
-      <c r="AR28" s="9">
+      <c r="AV28" s="9">
         <v>-2.7E-2</v>
       </c>
-      <c r="AS28" s="9">
+      <c r="AW28" s="9">
         <v>8.7999999999999995E-2</v>
       </c>
-      <c r="AT28" s="9">
+      <c r="AX28" s="9">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="AU28" s="9">
+      <c r="AY28" s="9">
         <v>0.14199999999999999</v>
       </c>
-      <c r="AV28" s="9">
+      <c r="AZ28" s="9">
         <v>0.193</v>
       </c>
-      <c r="AW28" s="9">
+      <c r="BA28" s="9">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="AX28" s="9">
+      <c r="BB28" s="9">
         <v>0.126</v>
       </c>
-      <c r="AY28" s="9">
+      <c r="BC28" s="9">
         <v>0.14000000000000001</v>
       </c>
-      <c r="AZ28" s="9">
+      <c r="BD28" s="9">
         <v>-0.32900000000000001</v>
       </c>
-      <c r="BA28" s="9">
+      <c r="BE28" s="9">
         <v>0.46200000000000002</v>
       </c>
-      <c r="BB28" s="9">
+      <c r="BF28" s="9">
         <v>0.13700000000000001</v>
       </c>
-      <c r="BC28" s="9">
+      <c r="BG28" s="9">
         <v>0.25900000000000001</v>
       </c>
-      <c r="BD28" s="9">
+      <c r="BH28" s="9">
         <v>0.14599999999999999</v>
       </c>
-      <c r="BE28" s="9">
+      <c r="BI28" s="9">
         <v>8.2000000000000003E-2</v>
       </c>
-      <c r="BF28" s="9">
+      <c r="BJ28" s="9">
         <v>0.14599999999999999</v>
       </c>
-      <c r="BG28" s="9">
+      <c r="BK28" s="9">
         <v>0.40400000000000003</v>
       </c>
-      <c r="BH28" s="9">
+      <c r="BL28" s="9">
         <v>0.73399999999999999</v>
       </c>
-      <c r="BI28" s="9">
+      <c r="BM28" s="9">
         <v>0.46800000000000003</v>
       </c>
-      <c r="BJ28" s="9">
+      <c r="BN28" s="9">
         <v>7.5999999999999998E-2</v>
       </c>
-      <c r="BK28" s="9"/>
-      <c r="BL28" s="9"/>
-      <c r="BM28" s="9"/>
-      <c r="BN28" s="9"/>
       <c r="BO28" s="9"/>
       <c r="BP28" s="9"/>
-    </row>
-    <row r="29" spans="1:68" x14ac:dyDescent="0.2">
+      <c r="BQ28" s="9"/>
+      <c r="BR28" s="9"/>
+      <c r="BS28" s="9"/>
+      <c r="BT28" s="9"/>
+    </row>
+    <row r="29" spans="1:72" x14ac:dyDescent="0.2">
       <c r="A29">
         <f t="shared" si="1"/>
         <v>27</v>
@@ -8545,16 +8673,20 @@
       <c r="X29" s="4">
         <v>25809.366483000002</v>
       </c>
-      <c r="Y29" s="6" t="s">
+      <c r="Y29" s="4"/>
+      <c r="Z29" s="4"/>
+      <c r="AA29" s="4"/>
+      <c r="AB29" s="4"/>
+      <c r="AC29" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="Z29" s="6" t="s">
+      <c r="AD29" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="AZ29" s="9"/>
-      <c r="BA29" s="9"/>
-    </row>
-    <row r="30" spans="1:68" x14ac:dyDescent="0.2">
+      <c r="BD29" s="9"/>
+      <c r="BE29" s="9"/>
+    </row>
+    <row r="30" spans="1:72" x14ac:dyDescent="0.2">
       <c r="A30">
         <f t="shared" si="1"/>
         <v>28</v>
@@ -8598,27 +8730,31 @@
       <c r="X30" s="4">
         <v>15526.737802</v>
       </c>
-      <c r="Y30" s="6" t="s">
+      <c r="Y30" s="4"/>
+      <c r="Z30" s="4"/>
+      <c r="AA30" s="4"/>
+      <c r="AB30" s="4"/>
+      <c r="AC30" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="AH30" t="s">
+      <c r="AL30" t="s">
         <v>1562</v>
       </c>
-      <c r="AK30" s="9">
+      <c r="AO30" s="9">
         <v>0.26300000000000001</v>
       </c>
-      <c r="AL30" s="9">
+      <c r="AP30" s="9">
         <v>-8.7999999999999995E-2</v>
       </c>
-      <c r="AY30" s="9">
+      <c r="BC30" s="9">
         <v>0.41210000000000002</v>
       </c>
-      <c r="AZ30" s="9">
+      <c r="BD30" s="9">
         <v>-0.11899999999999999</v>
       </c>
-      <c r="BA30" s="9"/>
-    </row>
-    <row r="31" spans="1:68" x14ac:dyDescent="0.2">
+      <c r="BE30" s="9"/>
+    </row>
+    <row r="31" spans="1:72" x14ac:dyDescent="0.2">
       <c r="A31">
         <f t="shared" si="1"/>
         <v>29</v>
@@ -8662,36 +8798,40 @@
       <c r="X31" s="4">
         <v>22594.232626000001</v>
       </c>
-      <c r="Y31" s="6" t="s">
+      <c r="Y31" s="4"/>
+      <c r="Z31" s="4"/>
+      <c r="AA31" s="4"/>
+      <c r="AB31" s="4"/>
+      <c r="AC31" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="Z31" s="6" t="s">
+      <c r="AD31" s="6" t="s">
         <v>1305</v>
       </c>
-      <c r="AA31" s="8" t="s">
+      <c r="AE31" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="AB31">
+      <c r="AF31">
         <v>1977</v>
       </c>
-      <c r="AK31" s="9">
+      <c r="AO31" s="9">
         <v>4.7E-2</v>
       </c>
-      <c r="AR31" s="9">
+      <c r="AV31" s="9">
         <v>0.13100000000000001</v>
       </c>
-      <c r="AS31" s="9">
+      <c r="AW31" s="9">
         <v>2.7E-2</v>
       </c>
-      <c r="AY31" s="9">
+      <c r="BC31" s="9">
         <v>0.307</v>
       </c>
-      <c r="AZ31" s="9">
+      <c r="BD31" s="9">
         <v>-0.03</v>
       </c>
-      <c r="BA31" s="9"/>
-    </row>
-    <row r="32" spans="1:68" x14ac:dyDescent="0.2">
+      <c r="BE31" s="9"/>
+    </row>
+    <row r="32" spans="1:72" x14ac:dyDescent="0.2">
       <c r="A32">
         <f t="shared" si="1"/>
         <v>30</v>
@@ -8726,20 +8866,24 @@
       <c r="V32" s="4"/>
       <c r="W32" s="4"/>
       <c r="X32" s="4"/>
-      <c r="Y32" s="6" t="s">
+      <c r="Y32" s="4"/>
+      <c r="Z32" s="4"/>
+      <c r="AA32" s="4"/>
+      <c r="AB32" s="4"/>
+      <c r="AC32" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="Z32" s="6" t="s">
+      <c r="AD32" s="6" t="s">
         <v>1559</v>
       </c>
-      <c r="AM32" s="9">
+      <c r="AQ32" s="9">
         <v>5.5E-2</v>
       </c>
-      <c r="AY32" s="9"/>
-      <c r="AZ32" s="9"/>
-      <c r="BA32" s="9"/>
-    </row>
-    <row r="33" spans="1:53" x14ac:dyDescent="0.2">
+      <c r="BC32" s="9"/>
+      <c r="BD32" s="9"/>
+      <c r="BE32" s="9"/>
+    </row>
+    <row r="33" spans="1:57" x14ac:dyDescent="0.2">
       <c r="A33">
         <f t="shared" si="1"/>
         <v>31</v>
@@ -8774,14 +8918,18 @@
       <c r="V33" s="4"/>
       <c r="W33" s="4"/>
       <c r="X33" s="4"/>
-      <c r="Y33" s="6" t="s">
+      <c r="Y33" s="4"/>
+      <c r="Z33" s="4"/>
+      <c r="AA33" s="4"/>
+      <c r="AB33" s="4"/>
+      <c r="AC33" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="AY33" s="9"/>
-      <c r="AZ33" s="9"/>
-      <c r="BA33" s="9"/>
-    </row>
-    <row r="34" spans="1:53" x14ac:dyDescent="0.2">
+      <c r="BC33" s="9"/>
+      <c r="BD33" s="9"/>
+      <c r="BE33" s="9"/>
+    </row>
+    <row r="34" spans="1:57" x14ac:dyDescent="0.2">
       <c r="A34">
         <f t="shared" si="1"/>
         <v>32</v>
@@ -8822,23 +8970,27 @@
       <c r="V34" s="4"/>
       <c r="W34" s="4"/>
       <c r="X34" s="4"/>
-      <c r="Y34" s="6" t="s">
+      <c r="Y34" s="4"/>
+      <c r="Z34" s="4"/>
+      <c r="AA34" s="4"/>
+      <c r="AB34" s="4"/>
+      <c r="AC34" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Z34" s="6" t="s">
+      <c r="AD34" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="AA34" s="8" t="s">
+      <c r="AE34" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="AB34">
+      <c r="AF34">
         <v>2000</v>
       </c>
-      <c r="AY34" s="9"/>
-      <c r="AZ34" s="9"/>
-      <c r="BA34" s="9"/>
-    </row>
-    <row r="35" spans="1:53" x14ac:dyDescent="0.2">
+      <c r="BC34" s="9"/>
+      <c r="BD34" s="9"/>
+      <c r="BE34" s="9"/>
+    </row>
+    <row r="35" spans="1:57" x14ac:dyDescent="0.2">
       <c r="A35">
         <f t="shared" si="1"/>
         <v>33</v>
@@ -8873,21 +9025,25 @@
       <c r="V35" s="4"/>
       <c r="W35" s="4"/>
       <c r="X35" s="4"/>
-      <c r="Y35" s="6" t="s">
+      <c r="Y35" s="4"/>
+      <c r="Z35" s="4"/>
+      <c r="AA35" s="4"/>
+      <c r="AB35" s="4"/>
+      <c r="AC35" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="Z35" s="6" t="s">
+      <c r="AD35" s="6" t="s">
         <v>1564</v>
       </c>
-      <c r="AA35" s="8" t="s">
+      <c r="AE35" s="8" t="s">
         <v>1206</v>
       </c>
-      <c r="AB35">
+      <c r="AF35">
         <v>2008</v>
       </c>
-      <c r="AY35" s="9"/>
-    </row>
-    <row r="36" spans="1:53" x14ac:dyDescent="0.2">
+      <c r="BC35" s="9"/>
+    </row>
+    <row r="36" spans="1:57" x14ac:dyDescent="0.2">
       <c r="A36">
         <f t="shared" si="1"/>
         <v>34</v>
@@ -8913,15 +9069,19 @@
       <c r="V36" s="4"/>
       <c r="W36" s="4"/>
       <c r="X36" s="4"/>
-      <c r="Y36" s="6" t="s">
+      <c r="Y36" s="4"/>
+      <c r="Z36" s="4"/>
+      <c r="AA36" s="4"/>
+      <c r="AB36" s="4"/>
+      <c r="AC36" s="6" t="s">
         <v>1267</v>
       </c>
-      <c r="AA36" s="8" t="s">
+      <c r="AE36" s="8" t="s">
         <v>223</v>
       </c>
-      <c r="AY36" s="9"/>
-    </row>
-    <row r="37" spans="1:53" x14ac:dyDescent="0.2">
+      <c r="BC36" s="9"/>
+    </row>
+    <row r="37" spans="1:57" x14ac:dyDescent="0.2">
       <c r="A37">
         <f t="shared" si="1"/>
         <v>35</v>
@@ -8956,20 +9116,24 @@
       <c r="V37" s="4"/>
       <c r="W37" s="4"/>
       <c r="X37" s="4"/>
-      <c r="Y37" s="6" t="s">
+      <c r="Y37" s="4"/>
+      <c r="Z37" s="4"/>
+      <c r="AA37" s="4"/>
+      <c r="AB37" s="4"/>
+      <c r="AC37" s="6" t="s">
         <v>1566</v>
       </c>
-      <c r="Z37" s="6" t="s">
+      <c r="AD37" s="6" t="s">
         <v>1565</v>
       </c>
-      <c r="AY37" s="9">
+      <c r="BC37" s="9">
         <v>0.29020000000000001</v>
       </c>
-      <c r="AZ37" s="9">
+      <c r="BD37" s="9">
         <v>0.08</v>
       </c>
     </row>
-    <row r="38" spans="1:53" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:57" x14ac:dyDescent="0.2">
       <c r="A38">
         <f t="shared" si="1"/>
         <v>36</v>
@@ -8999,17 +9163,21 @@
       <c r="V38" s="4"/>
       <c r="W38" s="4"/>
       <c r="X38" s="4"/>
-      <c r="Y38" s="6" t="s">
+      <c r="Y38" s="4"/>
+      <c r="Z38" s="4"/>
+      <c r="AA38" s="4"/>
+      <c r="AB38" s="4"/>
+      <c r="AC38" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Z38" s="6" t="s">
+      <c r="AD38" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="AA38" s="8" t="s">
+      <c r="AE38" s="8" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="39" spans="1:53" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:57" x14ac:dyDescent="0.2">
       <c r="A39">
         <f t="shared" si="1"/>
         <v>37</v>
@@ -9035,17 +9203,21 @@
       <c r="V39" s="4"/>
       <c r="W39" s="4"/>
       <c r="X39" s="4"/>
-      <c r="Y39" s="6" t="s">
+      <c r="Y39" s="4"/>
+      <c r="Z39" s="4"/>
+      <c r="AA39" s="4"/>
+      <c r="AB39" s="4"/>
+      <c r="AC39" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Z39" s="6" t="s">
+      <c r="AD39" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="AA39" s="8" t="s">
+      <c r="AE39" s="8" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="40" spans="1:53" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:57" x14ac:dyDescent="0.2">
       <c r="A40">
         <f t="shared" si="1"/>
         <v>38</v>
@@ -9068,8 +9240,12 @@
       <c r="V40" s="4"/>
       <c r="W40" s="4"/>
       <c r="X40" s="4"/>
-    </row>
-    <row r="41" spans="1:53" x14ac:dyDescent="0.2">
+      <c r="Y40" s="4"/>
+      <c r="Z40" s="4"/>
+      <c r="AA40" s="4"/>
+      <c r="AB40" s="4"/>
+    </row>
+    <row r="41" spans="1:57" x14ac:dyDescent="0.2">
       <c r="A41">
         <f t="shared" si="1"/>
         <v>39</v>
@@ -9092,8 +9268,12 @@
       <c r="V41" s="4"/>
       <c r="W41" s="4"/>
       <c r="X41" s="4"/>
-    </row>
-    <row r="42" spans="1:53" x14ac:dyDescent="0.2">
+      <c r="Y41" s="4"/>
+      <c r="Z41" s="4"/>
+      <c r="AA41" s="4"/>
+      <c r="AB41" s="4"/>
+    </row>
+    <row r="42" spans="1:57" x14ac:dyDescent="0.2">
       <c r="A42">
         <f t="shared" si="1"/>
         <v>40</v>
@@ -9122,23 +9302,27 @@
       <c r="V42" s="4"/>
       <c r="W42" s="4"/>
       <c r="X42" s="4"/>
-      <c r="Y42" s="6" t="s">
+      <c r="Y42" s="4"/>
+      <c r="Z42" s="4"/>
+      <c r="AA42" s="4"/>
+      <c r="AB42" s="4"/>
+      <c r="AC42" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="Z42" s="6" t="s">
+      <c r="AD42" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="AA42" s="8" t="s">
+      <c r="AE42" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="AU42" s="36">
+      <c r="AY42" s="36">
         <v>0.2525</v>
       </c>
-      <c r="AV42" s="36">
+      <c r="AZ42" s="36">
         <v>0.215</v>
       </c>
     </row>
-    <row r="43" spans="1:53" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:57" x14ac:dyDescent="0.2">
       <c r="A43">
         <f t="shared" si="1"/>
         <v>41</v>
@@ -9167,14 +9351,18 @@
       <c r="V43" s="4"/>
       <c r="W43" s="4"/>
       <c r="X43" s="4"/>
-      <c r="Y43" s="6" t="s">
+      <c r="Y43" s="4"/>
+      <c r="Z43" s="4"/>
+      <c r="AA43" s="4"/>
+      <c r="AB43" s="4"/>
+      <c r="AC43" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="AA43" s="8" t="s">
+      <c r="AE43" s="8" t="s">
         <v>1206</v>
       </c>
     </row>
-    <row r="44" spans="1:53" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:57" x14ac:dyDescent="0.2">
       <c r="A44">
         <f t="shared" si="1"/>
         <v>42</v>
@@ -9194,14 +9382,18 @@
       <c r="V44" s="4"/>
       <c r="W44" s="4"/>
       <c r="X44" s="4"/>
-      <c r="AB44">
+      <c r="Y44" s="4"/>
+      <c r="Z44" s="4"/>
+      <c r="AA44" s="4"/>
+      <c r="AB44" s="4"/>
+      <c r="AF44">
         <v>2007</v>
       </c>
-      <c r="AK44" s="9">
+      <c r="AO44" s="9">
         <v>0.254</v>
       </c>
     </row>
-    <row r="45" spans="1:53" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:57" x14ac:dyDescent="0.2">
       <c r="A45">
         <f t="shared" si="1"/>
         <v>43</v>
@@ -9230,17 +9422,21 @@
       <c r="V45" s="4"/>
       <c r="W45" s="4"/>
       <c r="X45" s="4"/>
-      <c r="Y45" s="6" t="s">
+      <c r="Y45" s="4"/>
+      <c r="Z45" s="4"/>
+      <c r="AA45" s="4"/>
+      <c r="AB45" s="4"/>
+      <c r="AC45" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Z45" s="6" t="s">
+      <c r="AD45" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="AA45" s="8" t="s">
+      <c r="AE45" s="8" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="46" spans="1:53" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:57" x14ac:dyDescent="0.2">
       <c r="A46">
         <f t="shared" si="1"/>
         <v>44</v>
@@ -9263,11 +9459,15 @@
       <c r="V46" s="4"/>
       <c r="W46" s="4"/>
       <c r="X46" s="4"/>
-      <c r="Y46" s="6" t="s">
+      <c r="Y46" s="4"/>
+      <c r="Z46" s="4"/>
+      <c r="AA46" s="4"/>
+      <c r="AB46" s="4"/>
+      <c r="AC46" s="6" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="47" spans="1:53" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:57" x14ac:dyDescent="0.2">
       <c r="A47">
         <f t="shared" si="1"/>
         <v>45</v>
@@ -9284,8 +9484,12 @@
       <c r="V47" s="4"/>
       <c r="W47" s="4"/>
       <c r="X47" s="4"/>
-    </row>
-    <row r="48" spans="1:53" x14ac:dyDescent="0.2">
+      <c r="Y47" s="4"/>
+      <c r="Z47" s="4"/>
+      <c r="AA47" s="4"/>
+      <c r="AB47" s="4"/>
+    </row>
+    <row r="48" spans="1:57" x14ac:dyDescent="0.2">
       <c r="A48">
         <f t="shared" si="1"/>
         <v>46</v>
@@ -9302,8 +9506,12 @@
       <c r="V48" s="4"/>
       <c r="W48" s="4"/>
       <c r="X48" s="4"/>
-    </row>
-    <row r="49" spans="1:48" x14ac:dyDescent="0.2">
+      <c r="Y48" s="4"/>
+      <c r="Z48" s="4"/>
+      <c r="AA48" s="4"/>
+      <c r="AB48" s="4"/>
+    </row>
+    <row r="49" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A49">
         <f t="shared" si="1"/>
         <v>47</v>
@@ -9329,22 +9537,26 @@
       <c r="V49" s="4"/>
       <c r="W49" s="4"/>
       <c r="X49" s="4"/>
-      <c r="AJ49" s="9"/>
-      <c r="AK49" s="9">
+      <c r="Y49" s="4"/>
+      <c r="Z49" s="4"/>
+      <c r="AA49" s="4"/>
+      <c r="AB49" s="4"/>
+      <c r="AN49" s="9"/>
+      <c r="AO49" s="9">
         <v>0.18</v>
       </c>
-      <c r="AS49" s="9">
+      <c r="AW49" s="9">
         <v>0.11</v>
       </c>
-      <c r="AT49" s="9">
+      <c r="AX49" s="9">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="AU49" s="9"/>
-      <c r="AV49" s="9">
+      <c r="AY49" s="9"/>
+      <c r="AZ49" s="9">
         <v>0.29270000000000002</v>
       </c>
     </row>
-    <row r="50" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A50">
         <f t="shared" si="1"/>
         <v>48</v>
@@ -9367,8 +9579,12 @@
       <c r="V50" s="4"/>
       <c r="W50" s="4"/>
       <c r="X50" s="4"/>
-    </row>
-    <row r="51" spans="1:48" x14ac:dyDescent="0.2">
+      <c r="Y50" s="4"/>
+      <c r="Z50" s="4"/>
+      <c r="AA50" s="4"/>
+      <c r="AB50" s="4"/>
+    </row>
+    <row r="51" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A51">
         <f t="shared" si="1"/>
         <v>49</v>
@@ -9391,8 +9607,12 @@
       <c r="V51" s="4"/>
       <c r="W51" s="4"/>
       <c r="X51" s="4"/>
-    </row>
-    <row r="52" spans="1:48" x14ac:dyDescent="0.2">
+      <c r="Y51" s="4"/>
+      <c r="Z51" s="4"/>
+      <c r="AA51" s="4"/>
+      <c r="AB51" s="4"/>
+    </row>
+    <row r="52" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A52">
         <f t="shared" si="1"/>
         <v>50</v>
@@ -9412,11 +9632,15 @@
       <c r="V52" s="4"/>
       <c r="W52" s="4"/>
       <c r="X52" s="4"/>
-      <c r="Y52" s="6" t="s">
+      <c r="Y52" s="4"/>
+      <c r="Z52" s="4"/>
+      <c r="AA52" s="4"/>
+      <c r="AB52" s="4"/>
+      <c r="AC52" s="6" t="s">
         <v>1326</v>
       </c>
     </row>
-    <row r="53" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A53">
         <f t="shared" si="1"/>
         <v>51</v>
@@ -9442,11 +9666,15 @@
       <c r="V53" s="4"/>
       <c r="W53" s="4"/>
       <c r="X53" s="4"/>
-      <c r="Y53" s="6" t="s">
+      <c r="Y53" s="4"/>
+      <c r="Z53" s="4"/>
+      <c r="AA53" s="4"/>
+      <c r="AB53" s="4"/>
+      <c r="AC53" s="6" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="54" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A54">
         <f t="shared" si="1"/>
         <v>52</v>
@@ -9475,14 +9703,18 @@
       <c r="V54" s="4"/>
       <c r="W54" s="4"/>
       <c r="X54" s="4"/>
-      <c r="Y54" s="6" t="s">
+      <c r="Y54" s="4"/>
+      <c r="Z54" s="4"/>
+      <c r="AA54" s="4"/>
+      <c r="AB54" s="4"/>
+      <c r="AC54" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="Z54" s="6" t="s">
+      <c r="AD54" s="6" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="55" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A55">
         <f t="shared" si="1"/>
         <v>53</v>
@@ -9511,14 +9743,18 @@
       <c r="V55" s="4"/>
       <c r="W55" s="4"/>
       <c r="X55" s="4"/>
-      <c r="Y55" s="6" t="s">
+      <c r="Y55" s="4"/>
+      <c r="Z55" s="4"/>
+      <c r="AA55" s="4"/>
+      <c r="AB55" s="4"/>
+      <c r="AC55" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="Z55" s="6" t="s">
+      <c r="AD55" s="6" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="56" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A56">
         <f t="shared" si="1"/>
         <v>54</v>
@@ -9550,14 +9786,18 @@
       <c r="V56" s="4"/>
       <c r="W56" s="4"/>
       <c r="X56" s="4"/>
-      <c r="Y56" s="6" t="s">
+      <c r="Y56" s="4"/>
+      <c r="Z56" s="4"/>
+      <c r="AA56" s="4"/>
+      <c r="AB56" s="4"/>
+      <c r="AC56" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="Z56" s="6" t="s">
+      <c r="AD56" s="6" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="57" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A57">
         <f t="shared" si="1"/>
         <v>55</v>
@@ -9580,8 +9820,12 @@
       <c r="V57" s="4"/>
       <c r="W57" s="4"/>
       <c r="X57" s="4"/>
-    </row>
-    <row r="58" spans="1:48" x14ac:dyDescent="0.2">
+      <c r="Y57" s="4"/>
+      <c r="Z57" s="4"/>
+      <c r="AA57" s="4"/>
+      <c r="AB57" s="4"/>
+    </row>
+    <row r="58" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A58">
         <f t="shared" si="1"/>
         <v>56</v>
@@ -9601,17 +9845,21 @@
       <c r="V58" s="4"/>
       <c r="W58" s="4"/>
       <c r="X58" s="4"/>
-      <c r="AK58" s="36">
+      <c r="Y58" s="4"/>
+      <c r="Z58" s="4"/>
+      <c r="AA58" s="4"/>
+      <c r="AB58" s="4"/>
+      <c r="AO58" s="36">
         <v>0.17399999999999999</v>
       </c>
-      <c r="AU58" s="9">
+      <c r="AY58" s="9">
         <v>1.0174000000000001</v>
       </c>
-      <c r="AV58" s="9">
+      <c r="AZ58" s="9">
         <v>0.53800000000000003</v>
       </c>
     </row>
-    <row r="59" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A59">
         <f t="shared" si="1"/>
         <v>57</v>
@@ -9640,11 +9888,15 @@
       <c r="V59" s="4"/>
       <c r="W59" s="4"/>
       <c r="X59" s="4"/>
-      <c r="Y59" s="6" t="s">
+      <c r="Y59" s="4"/>
+      <c r="Z59" s="4"/>
+      <c r="AA59" s="4"/>
+      <c r="AB59" s="4"/>
+      <c r="AC59" s="6" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="60" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A60">
         <f>+A63+1</f>
         <v>61</v>
@@ -9667,8 +9919,12 @@
       <c r="V60" s="4"/>
       <c r="W60" s="4"/>
       <c r="X60" s="4"/>
-    </row>
-    <row r="61" spans="1:48" x14ac:dyDescent="0.2">
+      <c r="Y60" s="4"/>
+      <c r="Z60" s="4"/>
+      <c r="AA60" s="4"/>
+      <c r="AB60" s="4"/>
+    </row>
+    <row r="61" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A61">
         <f>+A59+1</f>
         <v>58</v>
@@ -9685,8 +9941,12 @@
       <c r="V61" s="4"/>
       <c r="W61" s="4"/>
       <c r="X61" s="4"/>
-    </row>
-    <row r="62" spans="1:48" x14ac:dyDescent="0.2">
+      <c r="Y61" s="4"/>
+      <c r="Z61" s="4"/>
+      <c r="AA61" s="4"/>
+      <c r="AB61" s="4"/>
+    </row>
+    <row r="62" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A62">
         <f t="shared" si="1"/>
         <v>59</v>
@@ -9712,8 +9972,12 @@
       <c r="V62" s="4"/>
       <c r="W62" s="4"/>
       <c r="X62" s="4"/>
-    </row>
-    <row r="63" spans="1:48" x14ac:dyDescent="0.2">
+      <c r="Y62" s="4"/>
+      <c r="Z62" s="4"/>
+      <c r="AA62" s="4"/>
+      <c r="AB62" s="4"/>
+    </row>
+    <row r="63" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A63">
         <f t="shared" si="1"/>
         <v>60</v>
@@ -9741,14 +10005,18 @@
       <c r="X63" s="4">
         <v>5278.59</v>
       </c>
-      <c r="Y63" s="6" t="s">
+      <c r="Y63" s="4"/>
+      <c r="Z63" s="4"/>
+      <c r="AA63" s="4"/>
+      <c r="AB63" s="4"/>
+      <c r="AC63" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="Z63" s="6" t="s">
+      <c r="AD63" s="6" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="64" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A64">
         <f>+A60+1</f>
         <v>62</v>
@@ -9777,29 +10045,33 @@
       <c r="V64" s="4"/>
       <c r="W64" s="4"/>
       <c r="X64" s="4"/>
-      <c r="Y64" s="6" t="s">
+      <c r="Y64" s="4"/>
+      <c r="Z64" s="4"/>
+      <c r="AA64" s="4"/>
+      <c r="AB64" s="4"/>
+      <c r="AC64" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Z64" s="6" t="s">
+      <c r="AD64" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="AK64" s="9">
+      <c r="AO64" s="9">
         <v>0.26</v>
       </c>
-      <c r="AL64" s="9">
+      <c r="AP64" s="9">
         <v>-0.26</v>
       </c>
-      <c r="AM64" s="9">
+      <c r="AQ64" s="9">
         <v>-0.21</v>
       </c>
-      <c r="AS64" s="9">
+      <c r="AW64" s="9">
         <v>0.51800000000000002</v>
       </c>
-      <c r="AT64" s="9">
+      <c r="AX64" s="9">
         <v>0.189</v>
       </c>
     </row>
-    <row r="65" spans="1:52" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:56" x14ac:dyDescent="0.2">
       <c r="A65">
         <f t="shared" si="1"/>
         <v>63</v>
@@ -9822,8 +10094,12 @@
       <c r="V65" s="4"/>
       <c r="W65" s="4"/>
       <c r="X65" s="4"/>
-    </row>
-    <row r="66" spans="1:52" x14ac:dyDescent="0.2">
+      <c r="Y65" s="4"/>
+      <c r="Z65" s="4"/>
+      <c r="AA65" s="4"/>
+      <c r="AB65" s="4"/>
+    </row>
+    <row r="66" spans="1:56" x14ac:dyDescent="0.2">
       <c r="A66">
         <f t="shared" si="1"/>
         <v>64</v>
@@ -9849,11 +10125,15 @@
       <c r="V66" s="4"/>
       <c r="W66" s="4"/>
       <c r="X66" s="4"/>
-      <c r="Y66" s="6" t="s">
+      <c r="Y66" s="4"/>
+      <c r="Z66" s="4"/>
+      <c r="AA66" s="4"/>
+      <c r="AB66" s="4"/>
+      <c r="AC66" s="6" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="67" spans="1:52" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:56" x14ac:dyDescent="0.2">
       <c r="A67">
         <f t="shared" si="1"/>
         <v>65</v>
@@ -9876,11 +10156,15 @@
       <c r="V67" s="4"/>
       <c r="W67" s="4"/>
       <c r="X67" s="4"/>
-      <c r="Y67" s="6" t="s">
+      <c r="Y67" s="4"/>
+      <c r="Z67" s="4"/>
+      <c r="AA67" s="4"/>
+      <c r="AB67" s="4"/>
+      <c r="AC67" s="6" t="s">
         <v>1305</v>
       </c>
     </row>
-    <row r="68" spans="1:52" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:56" x14ac:dyDescent="0.2">
       <c r="A68">
         <f t="shared" si="1"/>
         <v>66</v>
@@ -9906,14 +10190,18 @@
       <c r="V68" s="4"/>
       <c r="W68" s="4"/>
       <c r="X68" s="4"/>
-      <c r="Y68" s="6" t="s">
+      <c r="Y68" s="4"/>
+      <c r="Z68" s="4"/>
+      <c r="AA68" s="4"/>
+      <c r="AB68" s="4"/>
+      <c r="AC68" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="AK68" s="36">
+      <c r="AO68" s="36">
         <v>8.7999999999999995E-2</v>
       </c>
     </row>
-    <row r="69" spans="1:52" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:56" x14ac:dyDescent="0.2">
       <c r="A69">
         <f t="shared" si="1"/>
         <v>67</v>
@@ -9930,8 +10218,12 @@
       <c r="V69" s="4"/>
       <c r="W69" s="4"/>
       <c r="X69" s="4"/>
-    </row>
-    <row r="70" spans="1:52" x14ac:dyDescent="0.2">
+      <c r="Y69" s="4"/>
+      <c r="Z69" s="4"/>
+      <c r="AA69" s="4"/>
+      <c r="AB69" s="4"/>
+    </row>
+    <row r="70" spans="1:56" x14ac:dyDescent="0.2">
       <c r="A70">
         <f t="shared" si="1"/>
         <v>68</v>
@@ -9946,8 +10238,12 @@
       <c r="V70" s="4"/>
       <c r="W70" s="4"/>
       <c r="X70" s="4"/>
-    </row>
-    <row r="71" spans="1:52" x14ac:dyDescent="0.2">
+      <c r="Y70" s="4"/>
+      <c r="Z70" s="4"/>
+      <c r="AA70" s="4"/>
+      <c r="AB70" s="4"/>
+    </row>
+    <row r="71" spans="1:56" x14ac:dyDescent="0.2">
       <c r="A71">
         <f t="shared" si="1"/>
         <v>69</v>
@@ -9965,8 +10261,12 @@
       <c r="V71" s="4"/>
       <c r="W71" s="4"/>
       <c r="X71" s="4"/>
-    </row>
-    <row r="72" spans="1:52" x14ac:dyDescent="0.2">
+      <c r="Y71" s="4"/>
+      <c r="Z71" s="4"/>
+      <c r="AA71" s="4"/>
+      <c r="AB71" s="4"/>
+    </row>
+    <row r="72" spans="1:56" x14ac:dyDescent="0.2">
       <c r="A72">
         <f t="shared" si="1"/>
         <v>70</v>
@@ -9989,11 +10289,15 @@
       <c r="V72" s="4"/>
       <c r="W72" s="4"/>
       <c r="X72" s="4"/>
-      <c r="Y72" s="6" t="s">
+      <c r="Y72" s="4"/>
+      <c r="Z72" s="4"/>
+      <c r="AA72" s="4"/>
+      <c r="AB72" s="4"/>
+      <c r="AC72" s="6" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="73" spans="1:52" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:56" x14ac:dyDescent="0.2">
       <c r="A73">
         <f t="shared" si="1"/>
         <v>71</v>
@@ -10013,8 +10317,12 @@
       <c r="V73" s="4"/>
       <c r="W73" s="4"/>
       <c r="X73" s="4"/>
-    </row>
-    <row r="74" spans="1:52" x14ac:dyDescent="0.2">
+      <c r="Y73" s="4"/>
+      <c r="Z73" s="4"/>
+      <c r="AA73" s="4"/>
+      <c r="AB73" s="4"/>
+    </row>
+    <row r="74" spans="1:56" x14ac:dyDescent="0.2">
       <c r="A74">
         <f t="shared" si="1"/>
         <v>72</v>
@@ -10040,11 +10348,15 @@
       <c r="V74" s="4"/>
       <c r="W74" s="4"/>
       <c r="X74" s="4"/>
-      <c r="Y74" s="6" t="s">
+      <c r="Y74" s="4"/>
+      <c r="Z74" s="4"/>
+      <c r="AA74" s="4"/>
+      <c r="AB74" s="4"/>
+      <c r="AC74" s="6" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="75" spans="1:52" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:56" x14ac:dyDescent="0.2">
       <c r="A75">
         <f t="shared" si="1"/>
         <v>73</v>
@@ -10070,8 +10382,12 @@
       <c r="V75" s="4"/>
       <c r="W75" s="4"/>
       <c r="X75" s="4"/>
-    </row>
-    <row r="76" spans="1:52" x14ac:dyDescent="0.2">
+      <c r="Y75" s="4"/>
+      <c r="Z75" s="4"/>
+      <c r="AA75" s="4"/>
+      <c r="AB75" s="4"/>
+    </row>
+    <row r="76" spans="1:56" x14ac:dyDescent="0.2">
       <c r="A76">
         <f t="shared" si="1"/>
         <v>74</v>
@@ -10097,11 +10413,15 @@
       <c r="V76" s="4"/>
       <c r="W76" s="4"/>
       <c r="X76" s="4"/>
-      <c r="Y76" s="6" t="s">
+      <c r="Y76" s="4"/>
+      <c r="Z76" s="4"/>
+      <c r="AA76" s="4"/>
+      <c r="AB76" s="4"/>
+      <c r="AC76" s="6" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="77" spans="1:52" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:56" x14ac:dyDescent="0.2">
       <c r="A77">
         <f t="shared" si="1"/>
         <v>75</v>
@@ -10118,8 +10438,12 @@
       <c r="V77" s="4"/>
       <c r="W77" s="4"/>
       <c r="X77" s="4"/>
-    </row>
-    <row r="78" spans="1:52" x14ac:dyDescent="0.2">
+      <c r="Y77" s="4"/>
+      <c r="Z77" s="4"/>
+      <c r="AA77" s="4"/>
+      <c r="AB77" s="4"/>
+    </row>
+    <row r="78" spans="1:56" x14ac:dyDescent="0.2">
       <c r="A78">
         <f t="shared" si="1"/>
         <v>76</v>
@@ -10136,8 +10460,12 @@
       <c r="V78" s="4"/>
       <c r="W78" s="4"/>
       <c r="X78" s="4"/>
-    </row>
-    <row r="79" spans="1:52" x14ac:dyDescent="0.2">
+      <c r="Y78" s="4"/>
+      <c r="Z78" s="4"/>
+      <c r="AA78" s="4"/>
+      <c r="AB78" s="4"/>
+    </row>
+    <row r="79" spans="1:56" x14ac:dyDescent="0.2">
       <c r="A79">
         <f t="shared" si="1"/>
         <v>77</v>
@@ -10157,11 +10485,15 @@
       <c r="V79" s="4"/>
       <c r="W79" s="4"/>
       <c r="X79" s="4"/>
-      <c r="AB79">
+      <c r="Y79" s="4"/>
+      <c r="Z79" s="4"/>
+      <c r="AA79" s="4"/>
+      <c r="AB79" s="4"/>
+      <c r="AF79">
         <v>2011</v>
       </c>
     </row>
-    <row r="80" spans="1:52" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:56" x14ac:dyDescent="0.2">
       <c r="A80">
         <f t="shared" si="1"/>
         <v>78</v>
@@ -10190,20 +10522,24 @@
       <c r="X80" s="4">
         <v>2047.9987269999999</v>
       </c>
-      <c r="Y80" s="6" t="s">
+      <c r="Y80" s="4"/>
+      <c r="Z80" s="4"/>
+      <c r="AA80" s="4"/>
+      <c r="AB80" s="4"/>
+      <c r="AC80" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="Z80" s="6" t="s">
+      <c r="AD80" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="AS80" s="9">
+      <c r="AW80" s="9">
         <v>-0.2</v>
       </c>
-      <c r="AZ80" s="9">
+      <c r="BD80" s="9">
         <v>-0.23</v>
       </c>
     </row>
-    <row r="81" spans="1:52" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:56" x14ac:dyDescent="0.2">
       <c r="A81">
         <f t="shared" si="1"/>
         <v>79</v>
@@ -10226,11 +10562,15 @@
       <c r="V81" s="4"/>
       <c r="W81" s="4"/>
       <c r="X81" s="4"/>
-      <c r="Y81" s="6" t="s">
+      <c r="Y81" s="4"/>
+      <c r="Z81" s="4"/>
+      <c r="AA81" s="4"/>
+      <c r="AB81" s="4"/>
+      <c r="AC81" s="6" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="82" spans="1:52" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:56" x14ac:dyDescent="0.2">
       <c r="A82">
         <f t="shared" si="1"/>
         <v>80</v>
@@ -10247,8 +10587,12 @@
       <c r="V82" s="4"/>
       <c r="W82" s="4"/>
       <c r="X82" s="4"/>
-    </row>
-    <row r="83" spans="1:52" x14ac:dyDescent="0.2">
+      <c r="Y82" s="4"/>
+      <c r="Z82" s="4"/>
+      <c r="AA82" s="4"/>
+      <c r="AB82" s="4"/>
+    </row>
+    <row r="83" spans="1:56" x14ac:dyDescent="0.2">
       <c r="A83">
         <f t="shared" si="1"/>
         <v>81</v>
@@ -10265,8 +10609,12 @@
       <c r="V83" s="4"/>
       <c r="W83" s="4"/>
       <c r="X83" s="4"/>
-    </row>
-    <row r="84" spans="1:52" x14ac:dyDescent="0.2">
+      <c r="Y83" s="4"/>
+      <c r="Z83" s="4"/>
+      <c r="AA83" s="4"/>
+      <c r="AB83" s="4"/>
+    </row>
+    <row r="84" spans="1:56" x14ac:dyDescent="0.2">
       <c r="A84">
         <f t="shared" si="1"/>
         <v>82</v>
@@ -10289,8 +10637,12 @@
       <c r="V84" s="4"/>
       <c r="W84" s="4"/>
       <c r="X84" s="4"/>
-    </row>
-    <row r="85" spans="1:52" x14ac:dyDescent="0.2">
+      <c r="Y84" s="4"/>
+      <c r="Z84" s="4"/>
+      <c r="AA84" s="4"/>
+      <c r="AB84" s="4"/>
+    </row>
+    <row r="85" spans="1:56" x14ac:dyDescent="0.2">
       <c r="A85">
         <f t="shared" ref="A85:A120" si="2">+A84+1</f>
         <v>83</v>
@@ -10313,8 +10665,12 @@
       <c r="V85" s="4"/>
       <c r="W85" s="4"/>
       <c r="X85" s="4"/>
-    </row>
-    <row r="86" spans="1:52" x14ac:dyDescent="0.2">
+      <c r="Y85" s="4"/>
+      <c r="Z85" s="4"/>
+      <c r="AA85" s="4"/>
+      <c r="AB85" s="4"/>
+    </row>
+    <row r="86" spans="1:56" x14ac:dyDescent="0.2">
       <c r="A86">
         <f t="shared" si="2"/>
         <v>84</v>
@@ -10340,11 +10696,15 @@
       <c r="V86" s="4"/>
       <c r="W86" s="4"/>
       <c r="X86" s="4"/>
-      <c r="Y86" s="6" t="s">
+      <c r="Y86" s="4"/>
+      <c r="Z86" s="4"/>
+      <c r="AA86" s="4"/>
+      <c r="AB86" s="4"/>
+      <c r="AC86" s="6" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="87" spans="1:52" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:56" x14ac:dyDescent="0.2">
       <c r="A87">
         <f t="shared" si="2"/>
         <v>85</v>
@@ -10367,11 +10727,15 @@
       <c r="V87" s="4"/>
       <c r="W87" s="4"/>
       <c r="X87" s="4"/>
-      <c r="AA87" s="8" t="s">
+      <c r="Y87" s="4"/>
+      <c r="Z87" s="4"/>
+      <c r="AA87" s="4"/>
+      <c r="AB87" s="4"/>
+      <c r="AE87" s="8" t="s">
         <v>671</v>
       </c>
     </row>
-    <row r="88" spans="1:52" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:56" x14ac:dyDescent="0.2">
       <c r="A88">
         <f t="shared" si="2"/>
         <v>86</v>
@@ -10400,14 +10764,18 @@
       <c r="V88" s="4"/>
       <c r="W88" s="4"/>
       <c r="X88" s="4"/>
-      <c r="Y88" s="6" t="s">
+      <c r="Y88" s="4"/>
+      <c r="Z88" s="4"/>
+      <c r="AA88" s="4"/>
+      <c r="AB88" s="4"/>
+      <c r="AC88" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Z88" s="6" t="s">
+      <c r="AD88" s="6" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="89" spans="1:52" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:56" x14ac:dyDescent="0.2">
       <c r="A89">
         <f t="shared" si="2"/>
         <v>87</v>
@@ -10433,11 +10801,15 @@
       <c r="V89" s="4"/>
       <c r="W89" s="4"/>
       <c r="X89" s="4"/>
-      <c r="Y89" s="6" t="s">
+      <c r="Y89" s="4"/>
+      <c r="Z89" s="4"/>
+      <c r="AA89" s="4"/>
+      <c r="AB89" s="4"/>
+      <c r="AC89" s="6" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="90" spans="1:52" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:56" x14ac:dyDescent="0.2">
       <c r="A90">
         <f t="shared" si="2"/>
         <v>88</v>
@@ -10454,8 +10826,12 @@
       <c r="V90" s="4"/>
       <c r="W90" s="4"/>
       <c r="X90" s="4"/>
-    </row>
-    <row r="91" spans="1:52" x14ac:dyDescent="0.2">
+      <c r="Y90" s="4"/>
+      <c r="Z90" s="4"/>
+      <c r="AA90" s="4"/>
+      <c r="AB90" s="4"/>
+    </row>
+    <row r="91" spans="1:56" x14ac:dyDescent="0.2">
       <c r="A91">
         <f t="shared" si="2"/>
         <v>89</v>
@@ -10481,11 +10857,15 @@
       <c r="V91" s="4"/>
       <c r="W91" s="4"/>
       <c r="X91" s="4"/>
-      <c r="Y91" s="6" t="s">
+      <c r="Y91" s="4"/>
+      <c r="Z91" s="4"/>
+      <c r="AA91" s="4"/>
+      <c r="AB91" s="4"/>
+      <c r="AC91" s="6" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="92" spans="1:52" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:56" x14ac:dyDescent="0.2">
       <c r="A92">
         <f t="shared" si="2"/>
         <v>90</v>
@@ -10508,8 +10888,12 @@
       <c r="V92" s="4"/>
       <c r="W92" s="4"/>
       <c r="X92" s="4"/>
-    </row>
-    <row r="93" spans="1:52" x14ac:dyDescent="0.2">
+      <c r="Y92" s="4"/>
+      <c r="Z92" s="4"/>
+      <c r="AA92" s="4"/>
+      <c r="AB92" s="4"/>
+    </row>
+    <row r="93" spans="1:56" x14ac:dyDescent="0.2">
       <c r="A93">
         <f t="shared" si="2"/>
         <v>91</v>
@@ -10526,8 +10910,12 @@
       <c r="V93" s="4"/>
       <c r="W93" s="4"/>
       <c r="X93" s="4"/>
-    </row>
-    <row r="94" spans="1:52" x14ac:dyDescent="0.2">
+      <c r="Y93" s="4"/>
+      <c r="Z93" s="4"/>
+      <c r="AA93" s="4"/>
+      <c r="AB93" s="4"/>
+    </row>
+    <row r="94" spans="1:56" x14ac:dyDescent="0.2">
       <c r="A94">
         <f t="shared" si="2"/>
         <v>92</v>
@@ -10547,17 +10935,21 @@
       <c r="V94" s="4"/>
       <c r="W94" s="4"/>
       <c r="X94" s="4"/>
-      <c r="AJ94" s="9">
+      <c r="Y94" s="4"/>
+      <c r="Z94" s="4"/>
+      <c r="AA94" s="4"/>
+      <c r="AB94" s="4"/>
+      <c r="AN94" s="9">
         <v>0.52</v>
       </c>
-      <c r="AK94" s="9">
+      <c r="AO94" s="9">
         <v>0.48</v>
       </c>
-      <c r="AZ94" s="36">
+      <c r="BD94" s="36">
         <v>-0.33300000000000002</v>
       </c>
     </row>
-    <row r="95" spans="1:52" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:56" x14ac:dyDescent="0.2">
       <c r="A95">
         <f t="shared" si="2"/>
         <v>93</v>
@@ -10583,11 +10975,15 @@
       <c r="V95" s="4"/>
       <c r="W95" s="4"/>
       <c r="X95" s="4"/>
-      <c r="Y95" s="6" t="s">
+      <c r="Y95" s="4"/>
+      <c r="Z95" s="4"/>
+      <c r="AA95" s="4"/>
+      <c r="AB95" s="4"/>
+      <c r="AC95" s="6" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="96" spans="1:52" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:56" x14ac:dyDescent="0.2">
       <c r="A96">
         <f t="shared" si="2"/>
         <v>94</v>
@@ -10604,8 +11000,12 @@
       <c r="V96" s="4"/>
       <c r="W96" s="4"/>
       <c r="X96" s="4"/>
-    </row>
-    <row r="97" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="Y96" s="4"/>
+      <c r="Z96" s="4"/>
+      <c r="AA96" s="4"/>
+      <c r="AB96" s="4"/>
+    </row>
+    <row r="97" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A97">
         <f t="shared" si="2"/>
         <v>95</v>
@@ -10628,8 +11028,12 @@
       <c r="V97" s="4"/>
       <c r="W97" s="4"/>
       <c r="X97" s="4"/>
-    </row>
-    <row r="98" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="Y97" s="4"/>
+      <c r="Z97" s="4"/>
+      <c r="AA97" s="4"/>
+      <c r="AB97" s="4"/>
+    </row>
+    <row r="98" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A98">
         <f t="shared" si="2"/>
         <v>96</v>
@@ -10657,11 +11061,15 @@
         <v>1381.1980759999999</v>
       </c>
       <c r="X98" s="4"/>
-      <c r="Y98" s="6" t="s">
+      <c r="Y98" s="4"/>
+      <c r="Z98" s="4"/>
+      <c r="AA98" s="4"/>
+      <c r="AB98" s="4"/>
+      <c r="AC98" s="6" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="99" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A99">
         <f t="shared" si="2"/>
         <v>97</v>
@@ -10680,8 +11088,12 @@
       <c r="V99" s="4"/>
       <c r="W99" s="4"/>
       <c r="X99" s="4"/>
-    </row>
-    <row r="100" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="Y99" s="4"/>
+      <c r="Z99" s="4"/>
+      <c r="AA99" s="4"/>
+      <c r="AB99" s="4"/>
+    </row>
+    <row r="100" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A100">
         <f t="shared" si="2"/>
         <v>98</v>
@@ -10700,11 +11112,15 @@
       <c r="V100" s="4"/>
       <c r="W100" s="4"/>
       <c r="X100" s="4"/>
-      <c r="Y100" s="6" t="s">
+      <c r="Y100" s="4"/>
+      <c r="Z100" s="4"/>
+      <c r="AA100" s="4"/>
+      <c r="AB100" s="4"/>
+      <c r="AC100" s="6" t="s">
         <v>663</v>
       </c>
     </row>
-    <row r="101" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A101">
         <f t="shared" si="2"/>
         <v>99</v>
@@ -10729,17 +11145,21 @@
       <c r="V101" s="4"/>
       <c r="W101" s="4"/>
       <c r="X101" s="4"/>
-      <c r="Y101" s="6" t="s">
+      <c r="Y101" s="4"/>
+      <c r="Z101" s="4"/>
+      <c r="AA101" s="4"/>
+      <c r="AB101" s="4"/>
+      <c r="AC101" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="Z101" s="6" t="s">
+      <c r="AD101" s="6" t="s">
         <v>220</v>
       </c>
-      <c r="AA101" s="8" t="s">
+      <c r="AE101" s="8" t="s">
         <v>654</v>
       </c>
     </row>
-    <row r="102" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A102">
         <f t="shared" si="2"/>
         <v>100</v>
@@ -10758,8 +11178,12 @@
       <c r="V102" s="4"/>
       <c r="W102" s="4"/>
       <c r="X102" s="4"/>
-    </row>
-    <row r="103" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="Y102" s="4"/>
+      <c r="Z102" s="4"/>
+      <c r="AA102" s="4"/>
+      <c r="AB102" s="4"/>
+    </row>
+    <row r="103" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A103">
         <f t="shared" si="2"/>
         <v>101</v>
@@ -10767,11 +11191,11 @@
       <c r="B103" t="s">
         <v>61</v>
       </c>
-      <c r="Y103" s="6" t="s">
+      <c r="AC103" s="6" t="s">
         <v>657</v>
       </c>
     </row>
-    <row r="104" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A104">
         <f t="shared" si="2"/>
         <v>102</v>
@@ -10780,7 +11204,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="105" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A105">
         <f t="shared" si="2"/>
         <v>103</v>
@@ -10789,7 +11213,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="106" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A106">
         <f t="shared" si="2"/>
         <v>104</v>
@@ -10798,7 +11222,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="107" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A107">
         <f t="shared" si="2"/>
         <v>105</v>
@@ -10810,7 +11234,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="108" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A108">
         <f t="shared" si="2"/>
         <v>106</v>
@@ -10819,7 +11243,7 @@
         <v>1327</v>
       </c>
     </row>
-    <row r="109" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A109">
         <f>+A107+1</f>
         <v>106</v>
@@ -10828,7 +11252,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="110" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A110">
         <f t="shared" si="2"/>
         <v>107</v>
@@ -10837,7 +11261,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="111" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A111">
         <f t="shared" si="2"/>
         <v>108</v>
@@ -10846,7 +11270,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="112" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A112">
         <f t="shared" si="2"/>
         <v>109</v>
@@ -11581,7 +12005,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="193" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A193">
         <f t="shared" si="4"/>
         <v>189</v>
@@ -11590,7 +12014,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="194" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A194">
         <f t="shared" si="4"/>
         <v>190</v>
@@ -11599,7 +12023,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="195" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A195">
         <f t="shared" si="4"/>
         <v>191</v>
@@ -11608,7 +12032,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="196" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A196">
         <f t="shared" si="4"/>
         <v>192</v>
@@ -11617,7 +12041,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="197" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A197">
         <f t="shared" si="4"/>
         <v>193</v>
@@ -11631,11 +12055,15 @@
       <c r="X197" s="4">
         <v>3612.1441329999998</v>
       </c>
-      <c r="Y197" s="6" t="s">
+      <c r="Y197" s="4"/>
+      <c r="Z197" s="4"/>
+      <c r="AA197" s="4"/>
+      <c r="AB197" s="4"/>
+      <c r="AC197" s="6" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="198" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A198">
         <f t="shared" si="4"/>
         <v>194</v>
@@ -11644,7 +12072,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="199" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A199">
         <f t="shared" si="4"/>
         <v>195</v>
@@ -11653,7 +12081,7 @@
         <v>1123</v>
       </c>
     </row>
-    <row r="200" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A200">
         <f t="shared" si="4"/>
         <v>196</v>
@@ -11662,7 +12090,7 @@
         <v>1124</v>
       </c>
     </row>
-    <row r="201" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A201">
         <f t="shared" si="4"/>
         <v>197</v>
@@ -11671,7 +12099,7 @@
         <v>1321</v>
       </c>
     </row>
-    <row r="202" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A202">
         <f t="shared" si="4"/>
         <v>198</v>
@@ -11680,7 +12108,7 @@
         <v>1209</v>
       </c>
     </row>
-    <row r="203" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A203">
         <f t="shared" si="4"/>
         <v>199</v>
@@ -11689,7 +12117,7 @@
         <v>1490</v>
       </c>
     </row>
-    <row r="204" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A204">
         <f t="shared" si="4"/>
         <v>200</v>
@@ -11701,7 +12129,7 @@
         <v>1571</v>
       </c>
     </row>
-    <row r="205" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A205">
         <f t="shared" si="4"/>
         <v>201</v>
@@ -11713,7 +12141,7 @@
         <v>1576</v>
       </c>
     </row>
-    <row r="206" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A206">
         <f t="shared" si="4"/>
         <v>202</v>
@@ -11725,7 +12153,7 @@
         <v>1577</v>
       </c>
     </row>
-    <row r="207" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A207">
         <f t="shared" si="4"/>
         <v>203</v>
@@ -11737,7 +12165,7 @@
         <v>1579</v>
       </c>
     </row>
-    <row r="208" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A208">
         <f t="shared" si="4"/>
         <v>204</v>
@@ -11749,7 +12177,7 @@
         <v>1580</v>
       </c>
     </row>
-    <row r="209" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A209">
         <f t="shared" si="4"/>
         <v>205</v>
@@ -11761,7 +12189,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="210" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A210">
         <f t="shared" si="4"/>
         <v>206</v>
@@ -11775,17 +12203,21 @@
       <c r="X210" s="4">
         <v>5516.7583439999999</v>
       </c>
-      <c r="Z210" s="6" t="s">
+      <c r="Y210" s="4"/>
+      <c r="Z210" s="4"/>
+      <c r="AA210" s="4"/>
+      <c r="AB210" s="4"/>
+      <c r="AD210" s="6" t="s">
         <v>1585</v>
       </c>
-      <c r="AA210" s="8" t="s">
+      <c r="AE210" s="8" t="s">
         <v>1584</v>
       </c>
-      <c r="AH210" t="s">
+      <c r="AL210" t="s">
         <v>1586</v>
       </c>
     </row>
-    <row r="212" spans="1:34" s="22" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:38" s="22" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B212" s="22" t="s">
         <v>1211</v>
       </c>
@@ -11810,11 +12242,15 @@
       <c r="V212" s="23"/>
       <c r="W212" s="23"/>
       <c r="X212" s="23"/>
-      <c r="Y212" s="25"/>
-      <c r="Z212" s="25"/>
-      <c r="AA212" s="26"/>
-    </row>
-    <row r="213" spans="1:34" s="22" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="Y212" s="23"/>
+      <c r="Z212" s="23"/>
+      <c r="AA212" s="23"/>
+      <c r="AB212" s="23"/>
+      <c r="AC212" s="25"/>
+      <c r="AD212" s="25"/>
+      <c r="AE212" s="26"/>
+    </row>
+    <row r="213" spans="1:38" s="22" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B213" s="22" t="s">
         <v>62</v>
       </c>
@@ -11839,33 +12275,37 @@
       <c r="V213" s="23"/>
       <c r="W213" s="23"/>
       <c r="X213" s="23"/>
-      <c r="Y213" s="25" t="s">
+      <c r="Y213" s="23"/>
+      <c r="Z213" s="23"/>
+      <c r="AA213" s="23"/>
+      <c r="AB213" s="23"/>
+      <c r="AC213" s="25" t="s">
         <v>654</v>
       </c>
-      <c r="Z213" s="25"/>
-      <c r="AA213" s="26"/>
-    </row>
-    <row r="214" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AD213" s="25"/>
+      <c r="AE213" s="26"/>
+    </row>
+    <row r="214" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B214" s="22" t="s">
         <v>1269</v>
       </c>
     </row>
-    <row r="215" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B215" s="22" t="s">
         <v>1270</v>
       </c>
     </row>
-    <row r="216" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B216" s="22" t="s">
         <v>1271</v>
       </c>
     </row>
-    <row r="217" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B217" s="22" t="s">
         <v>1272</v>
       </c>
     </row>
-    <row r="218" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B218" s="22" t="s">
         <v>1273</v>
       </c>
@@ -11873,32 +12313,32 @@
         <v>1320</v>
       </c>
     </row>
-    <row r="219" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B219" s="22" t="s">
         <v>1274</v>
       </c>
     </row>
-    <row r="220" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B220" s="22" t="s">
         <v>1275</v>
       </c>
     </row>
-    <row r="221" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B221" s="22" t="s">
         <v>1276</v>
       </c>
     </row>
-    <row r="222" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B222" s="22" t="s">
         <v>1277</v>
       </c>
     </row>
-    <row r="223" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B223" s="22" t="s">
         <v>1278</v>
       </c>
     </row>
-    <row r="224" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B224" s="22" t="s">
         <v>724</v>
       </c>

--- a/Hedge Funds (1).xlsx
+++ b/Hedge Funds (1).xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23A95E28-C37C-4404-93CD-A8F36AFD3391}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D9691AE-02BA-48B1-9EA6-427E503FEF71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="225" yWindow="2340" windowWidth="38175" windowHeight="15240" xr2:uid="{18689D26-F1F3-46B4-82BE-041D095397EB}"/>
   </bookViews>
@@ -36,7 +36,7 @@
     <definedName name="JPY">[1]FX!$C$7</definedName>
     <definedName name="KRW">[1]FX!$C$9</definedName>
   </definedNames>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -6478,7 +6478,9 @@
         <v>274160.08670099999</v>
       </c>
       <c r="Y3" s="4"/>
-      <c r="Z3" s="4"/>
+      <c r="Z3" s="4">
+        <v>299253.55624599999</v>
+      </c>
       <c r="AA3" s="4"/>
       <c r="AB3" s="4"/>
       <c r="AC3" s="6" t="s">
@@ -6505,7 +6507,7 @@
       <c r="C4" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="4">
         <v>67467</v>
       </c>
       <c r="I4" s="4">
@@ -12056,8 +12058,9 @@
         <v>3612.1441329999998</v>
       </c>
       <c r="Y197" s="4"/>
-      <c r="Z197" s="4"/>
-      <c r="AA197" s="4"/>
+      <c r="Z197" s="4">
+        <v>3093.4721610000001</v>
+      </c>
       <c r="AB197" s="4"/>
       <c r="AC197" s="6" t="s">
         <v>104</v>
@@ -12204,8 +12207,9 @@
         <v>5516.7583439999999</v>
       </c>
       <c r="Y210" s="4"/>
-      <c r="Z210" s="4"/>
-      <c r="AA210" s="4"/>
+      <c r="Z210" s="4">
+        <v>20242.292227999998</v>
+      </c>
       <c r="AB210" s="4"/>
       <c r="AD210" s="6" t="s">
         <v>1585</v>
@@ -13108,10 +13112,14 @@
     <hyperlink ref="X197" r:id="rId641" display="https://www.sec.gov/Archives/edgar/data/1960830/000091957426001016/0000919574-26-001016-index.htm" xr:uid="{6361078E-F13D-4E19-A00E-CCBE2355774B}"/>
     <hyperlink ref="B210" r:id="rId642" xr:uid="{E772CE81-C0A7-40B7-A0F7-0B990343273E}"/>
     <hyperlink ref="X210" r:id="rId643" display="https://www.sec.gov/Archives/edgar/data/2045724/000204572426000002/0002045724-26-000002-index.htm" xr:uid="{52D0C669-28FD-4B4C-A951-7B9DB3938C6E}"/>
+    <hyperlink ref="D4" r:id="rId644" display="https://adviserinfo.sec.gov/firm/summary/158117" xr:uid="{E834FCC4-DFE7-46C4-841F-8DDE5896246A}"/>
+    <hyperlink ref="Z197" r:id="rId645" display="https://www.sec.gov/Archives/edgar/data/1960830/000091957426005191/0000919574-26-005191-index.htm" xr:uid="{50699F22-8CBD-48D2-814C-7EA8EF736B62}"/>
+    <hyperlink ref="Z210" r:id="rId646" display="https://www.sec.gov/Archives/edgar/data/2045724/000093583626000418/0000935836-26-000418-index.htm" xr:uid="{A0567215-8EDA-4AC2-A419-5010CD7BBF44}"/>
+    <hyperlink ref="Z3" r:id="rId647" display="https://www.sec.gov/Archives/edgar/data/1067983/000119312526352200/0001193125-26-352200-index.htm" xr:uid="{449E1FB0-DCC1-4DC3-BBCB-8B49A8241DEA}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId644"/>
-  <legacyDrawing r:id="rId645"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId648"/>
+  <legacyDrawing r:id="rId649"/>
 </worksheet>
 </file>
 
